--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -2598,43 +2598,43 @@
         </is>
       </c>
       <c r="E75" s="16">
-        <f>MAX(0,E68-E74-E84)</f>
+        <f>MAX(0,E68-E74-E85)</f>
         <v/>
       </c>
       <c r="F75" s="16">
-        <f>MAX(0,F68-F74-F84)</f>
+        <f>MAX(0,F68-F74-F85)</f>
         <v/>
       </c>
       <c r="G75" s="16">
-        <f>MAX(0,G68-G74-G84)</f>
+        <f>MAX(0,G68-G74-G85)</f>
         <v/>
       </c>
       <c r="H75" s="16">
-        <f>MAX(0,H68-H74-H84)</f>
+        <f>MAX(0,H68-H74-H85)</f>
         <v/>
       </c>
       <c r="I75" s="16">
-        <f>MAX(0,I68-I74-I84)</f>
+        <f>MAX(0,I68-I74-I85)</f>
         <v/>
       </c>
       <c r="J75" s="16">
-        <f>MAX(0,J68-J74-J84)</f>
+        <f>MAX(0,J68-J74-J85)</f>
         <v/>
       </c>
       <c r="K75" s="16">
-        <f>MAX(0,K68-K74-K84)</f>
+        <f>MAX(0,K68-K74-K85)</f>
         <v/>
       </c>
       <c r="L75" s="16">
-        <f>MAX(0,L68-L74-L84)</f>
+        <f>MAX(0,L68-L74-L85)</f>
         <v/>
       </c>
       <c r="M75" s="16">
-        <f>MAX(0,M68-M74-M84)</f>
+        <f>MAX(0,M68-M74-M85)</f>
         <v/>
       </c>
       <c r="N75" s="16">
-        <f>MAX(0,N68-N74-N84)</f>
+        <f>MAX(0,N68-N74-N85)</f>
         <v/>
       </c>
     </row>
@@ -2866,91 +2866,87 @@
         <v/>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled DS (for DSRA)</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Based on straight-line amort, no sweep</t>
+        </is>
+      </c>
+      <c r="E80" s="16">
+        <f>MAX(0,$D$50-(1-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="F80" s="16">
+        <f>MAX(0,$D$50-(2-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="G80" s="16">
+        <f>MAX(0,$D$50-(3-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="H80" s="16">
+        <f>MAX(0,$D$50-(4-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="I80" s="16">
+        <f>MAX(0,$D$50-(5-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="J80" s="16">
+        <f>MAX(0,$D$50-(6-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="K80" s="16">
+        <f>MAX(0,$D$50-(7-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="L80" s="16">
+        <f>MAX(0,$D$50-(8-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="M80" s="16">
+        <f>MAX(0,$D$50-(9-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+      <c r="N80" s="16">
+        <f>MAX(0,$D$50-(10-1)*$D$52)*$D$38+$D$52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>DSRA (Debt Service Reserve Account)</t>
         </is>
       </c>
-      <c r="B81" s="4" t="n"/>
-      <c r="C81" s="4" t="n"/>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
-      <c r="J81" s="4" t="n"/>
-      <c r="K81" s="4" t="n"/>
-      <c r="L81" s="4" t="n"/>
-      <c r="M81" s="4" t="n"/>
-      <c r="N81" s="4" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Target</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D82" s="16">
-        <f>E74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="E82" s="16">
-        <f>F74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="F82" s="16">
-        <f>G74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="G82" s="16">
-        <f>H74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="H82" s="16">
-        <f>I74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="I82" s="16">
-        <f>J74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="J82" s="16">
-        <f>K74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="K82" s="16">
-        <f>L74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="L82" s="16">
-        <f>M74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="M82" s="16">
-        <f>N74*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="N82" s="16">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="n"/>
+      <c r="H82" s="4" t="n"/>
+      <c r="I82" s="4" t="n"/>
+      <c r="J82" s="4" t="n"/>
+      <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Target</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -2958,56 +2954,60 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr"/>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
+        </is>
+      </c>
       <c r="D83" s="16">
+        <f>E80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="E83" s="16">
+        <f>F80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="F83" s="16">
+        <f>G80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="G83" s="16">
+        <f>H80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="H83" s="16">
+        <f>I80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="I83" s="16">
+        <f>J80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="J83" s="16">
+        <f>K80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="K83" s="16">
+        <f>L80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="L83" s="16">
+        <f>M80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="M83" s="16">
+        <f>N80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="N83" s="16">
         <f>0</f>
-        <v/>
-      </c>
-      <c r="E83" s="16">
-        <f>D85</f>
-        <v/>
-      </c>
-      <c r="F83" s="16">
-        <f>E85</f>
-        <v/>
-      </c>
-      <c r="G83" s="16">
-        <f>F85</f>
-        <v/>
-      </c>
-      <c r="H83" s="16">
-        <f>G85</f>
-        <v/>
-      </c>
-      <c r="I83" s="16">
-        <f>H85</f>
-        <v/>
-      </c>
-      <c r="J83" s="16">
-        <f>I85</f>
-        <v/>
-      </c>
-      <c r="K83" s="16">
-        <f>J85</f>
-        <v/>
-      </c>
-      <c r="L83" s="16">
-        <f>K85</f>
-        <v/>
-      </c>
-      <c r="M83" s="16">
-        <f>L85</f>
-        <v/>
-      </c>
-      <c r="N83" s="16">
-        <f>M85</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -3015,114 +3015,171 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Target - Beginning</t>
-        </is>
-      </c>
+      <c r="C84" s="6" t="inlineStr"/>
       <c r="D84" s="16">
-        <f>D82-D83</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E84" s="16">
-        <f>E82-E83</f>
+        <f>D86</f>
         <v/>
       </c>
       <c r="F84" s="16">
-        <f>F82-F83</f>
+        <f>E86</f>
         <v/>
       </c>
       <c r="G84" s="16">
-        <f>G82-G83</f>
+        <f>F86</f>
         <v/>
       </c>
       <c r="H84" s="16">
-        <f>H82-H83</f>
+        <f>G86</f>
         <v/>
       </c>
       <c r="I84" s="16">
-        <f>I82-I83</f>
+        <f>H86</f>
         <v/>
       </c>
       <c r="J84" s="16">
-        <f>J82-J83</f>
+        <f>I86</f>
         <v/>
       </c>
       <c r="K84" s="16">
-        <f>K82-K83</f>
+        <f>J86</f>
         <v/>
       </c>
       <c r="L84" s="16">
-        <f>L82-L83</f>
+        <f>K86</f>
         <v/>
       </c>
       <c r="M84" s="16">
-        <f>M82-M83</f>
+        <f>L86</f>
         <v/>
       </c>
       <c r="N84" s="16">
-        <f>N82-N83</f>
+        <f>M86</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
+          <t>DSRA Funding/(Release)</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
+      <c r="D85" s="16">
+        <f>D83-D84</f>
+        <v/>
+      </c>
+      <c r="E85" s="16">
+        <f>E83-E84</f>
+        <v/>
+      </c>
+      <c r="F85" s="16">
+        <f>F83-F84</f>
+        <v/>
+      </c>
+      <c r="G85" s="16">
+        <f>G83-G84</f>
+        <v/>
+      </c>
+      <c r="H85" s="16">
+        <f>H83-H84</f>
+        <v/>
+      </c>
+      <c r="I85" s="16">
+        <f>I83-I84</f>
+        <v/>
+      </c>
+      <c r="J85" s="16">
+        <f>J83-J84</f>
+        <v/>
+      </c>
+      <c r="K85" s="16">
+        <f>K83-K84</f>
+        <v/>
+      </c>
+      <c r="L85" s="16">
+        <f>L83-L84</f>
+        <v/>
+      </c>
+      <c r="M85" s="16">
+        <f>M83-M84</f>
+        <v/>
+      </c>
+      <c r="N85" s="16">
+        <f>N83-N84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
           <t>DSRA Ending</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>Beginning + Funding</t>
         </is>
       </c>
-      <c r="D85" s="16">
-        <f>D83+D84</f>
-        <v/>
-      </c>
-      <c r="E85" s="16">
-        <f>E83+E84</f>
-        <v/>
-      </c>
-      <c r="F85" s="16">
-        <f>F83+F84</f>
-        <v/>
-      </c>
-      <c r="G85" s="16">
-        <f>G83+G84</f>
-        <v/>
-      </c>
-      <c r="H85" s="16">
-        <f>H83+H84</f>
-        <v/>
-      </c>
-      <c r="I85" s="16">
-        <f>I83+I84</f>
-        <v/>
-      </c>
-      <c r="J85" s="16">
-        <f>J83+J84</f>
-        <v/>
-      </c>
-      <c r="K85" s="16">
-        <f>K83+K84</f>
-        <v/>
-      </c>
-      <c r="L85" s="16">
-        <f>L83+L84</f>
-        <v/>
-      </c>
-      <c r="M85" s="16">
-        <f>M83+M84</f>
-        <v/>
-      </c>
-      <c r="N85" s="16">
-        <f>N83+N84</f>
+      <c r="D86" s="16">
+        <f>D84+D85</f>
+        <v/>
+      </c>
+      <c r="E86" s="16">
+        <f>E84+E85</f>
+        <v/>
+      </c>
+      <c r="F86" s="16">
+        <f>F84+F85</f>
+        <v/>
+      </c>
+      <c r="G86" s="16">
+        <f>G84+G85</f>
+        <v/>
+      </c>
+      <c r="H86" s="16">
+        <f>H84+H85</f>
+        <v/>
+      </c>
+      <c r="I86" s="16">
+        <f>I84+I85</f>
+        <v/>
+      </c>
+      <c r="J86" s="16">
+        <f>J84+J85</f>
+        <v/>
+      </c>
+      <c r="K86" s="16">
+        <f>K84+K85</f>
+        <v/>
+      </c>
+      <c r="L86" s="16">
+        <f>L84+L85</f>
+        <v/>
+      </c>
+      <c r="M86" s="16">
+        <f>M84+M85</f>
+        <v/>
+      </c>
+      <c r="N86" s="16">
+        <f>N84+N85</f>
         <v/>
       </c>
     </row>
@@ -3163,43 +3220,43 @@
         </is>
       </c>
       <c r="E88" s="16">
-        <f>E68-(E72+E77)-E84</f>
+        <f>E68-(E72+E77)-E85</f>
         <v/>
       </c>
       <c r="F88" s="16">
-        <f>F68-(F72+F77)-F84</f>
+        <f>F68-(F72+F77)-F85</f>
         <v/>
       </c>
       <c r="G88" s="16">
-        <f>G68-(G72+G77)-G84</f>
+        <f>G68-(G72+G77)-G85</f>
         <v/>
       </c>
       <c r="H88" s="16">
-        <f>H68-(H72+H77)-H84</f>
+        <f>H68-(H72+H77)-H85</f>
         <v/>
       </c>
       <c r="I88" s="16">
-        <f>I68-(I72+I77)-I84</f>
+        <f>I68-(I72+I77)-I85</f>
         <v/>
       </c>
       <c r="J88" s="16">
-        <f>J68-(J72+J77)-J84</f>
+        <f>J68-(J72+J77)-J85</f>
         <v/>
       </c>
       <c r="K88" s="16">
-        <f>K68-(K72+K77)-K84</f>
+        <f>K68-(K72+K77)-K85</f>
         <v/>
       </c>
       <c r="L88" s="16">
-        <f>L68-(L72+L77)-L84</f>
+        <f>L68-(L72+L77)-L85</f>
         <v/>
       </c>
       <c r="M88" s="16">
-        <f>M68-(M72+M77)-M84</f>
+        <f>M68-(M72+M77)-M85</f>
         <v/>
       </c>
       <c r="N88" s="16">
-        <f>N68-(N72+N77)-N84</f>
+        <f>N68-(N72+N77)-N85</f>
         <v/>
       </c>
     </row>
@@ -3389,7 +3446,7 @@
       </c>
       <c r="C96" s="6" t="inlineStr"/>
       <c r="D96" s="16">
-        <f>D82</f>
+        <f>D83</f>
         <v/>
       </c>
     </row>
@@ -3566,7 +3623,7 @@
         </is>
       </c>
       <c r="K108" s="16">
-        <f>K85</f>
+        <f>K86</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -230,6 +230,51 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lotus Infrastructure</author>
+  </authors>
+  <commentList>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Fee-for-service revenue. Predictable but volume-dependent. Check MVC terms.</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0" shapeId="0">
+      <text>
+        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0">
+      <text>
+        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -521,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -587,6 +632,11 @@
           <t>Revenue = Volume × Fee ($/Mcf). No commodity exposure - you're paid to move gas, not sell it.</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>$/Mcf gathering fee</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
@@ -598,6 +648,10 @@
         <is>
           <t>Key risk is producer activity. If drilling slows, volumes decline. Hence the growth-then-decline profile.</t>
         </is>
+      </c>
+      <c r="C8">
+        <f> Growth then Decline</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -611,6 +665,10 @@
         </is>
       </c>
       <c r="B10" s="25" t="n"/>
+      <c r="C10">
+        <f> Growth then Decline</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="21" t="inlineStr">
@@ -646,6 +704,10 @@
         <is>
           <t>Y1 Volume × (1.03)^4 = peak. Then Y6 = Peak × (0.95), Y7 = Peak × (0.95)^2, etc.</t>
         </is>
+      </c>
+      <c r="C13">
+        <f> Growth then Decline</f>
+        <v/>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
@@ -683,6 +745,11 @@
           <t>Maximize paydown during growth phase. Every dollar of sweep reduces refinancing risk.</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>% of excess cash to prepay</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
@@ -693,6 +760,11 @@
       <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Basin/producer risk. More conservative than contracted assets. Single counterparty exposure.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Debt / EV</t>
         </is>
       </c>
     </row>
@@ -743,6 +815,10 @@
           <t>Capex reduces CFADS and thus available cash for debt paydown. Factor into covenant analysis.</t>
         </is>
       </c>
+      <c r="C23">
+        <f> EBITDA − Taxes</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="21" t="inlineStr"/>
@@ -840,8 +916,135 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -238,39 +238,9 @@
     <author>Lotus Infrastructure</author>
   </authors>
   <commentList>
-    <comment ref="C7" authorId="0" shapeId="0">
-      <text>
-        <t>Fee-for-service revenue. Predictable but volume-dependent. Check MVC terms.</t>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="0" shapeId="0">
-      <text>
-        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
-      </text>
-    </comment>
-    <comment ref="C10" authorId="0" shapeId="0">
-      <text>
-        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
-      </text>
-    </comment>
-    <comment ref="C13" authorId="0" shapeId="0">
-      <text>
-        <t>Growth phase (Y1-5) as wells connect, then decline (Y6+) as reservoir depletes. Model inflection carefully.</t>
-      </text>
-    </comment>
-    <comment ref="C17" authorId="0" shapeId="0">
-      <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
-      </text>
-    </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
-      <text>
-        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
-      </text>
-    </comment>
     <comment ref="C23" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
   </commentList>
@@ -632,11 +602,6 @@
           <t>Revenue = Volume × Fee ($/Mcf). No commodity exposure - you're paid to move gas, not sell it.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>$/Mcf gathering fee</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
@@ -648,10 +613,6 @@
         <is>
           <t>Key risk is producer activity. If drilling slows, volumes decline. Hence the growth-then-decline profile.</t>
         </is>
-      </c>
-      <c r="C8">
-        <f> Growth then Decline</f>
-        <v/>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -665,10 +626,6 @@
         </is>
       </c>
       <c r="B10" s="25" t="n"/>
-      <c r="C10">
-        <f> Growth then Decline</f>
-        <v/>
-      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="21" t="inlineStr">
@@ -704,10 +661,6 @@
         <is>
           <t>Y1 Volume × (1.03)^4 = peak. Then Y6 = Peak × (0.95), Y7 = Peak × (0.95)^2, etc.</t>
         </is>
-      </c>
-      <c r="C13">
-        <f> Growth then Decline</f>
-        <v/>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
@@ -745,11 +698,6 @@
           <t>Maximize paydown during growth phase. Every dollar of sweep reduces refinancing risk.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>% of excess cash to prepay</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
@@ -760,11 +708,6 @@
       <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Basin/producer risk. More conservative than contracted assets. Single counterparty exposure.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Debt / EV</t>
         </is>
       </c>
     </row>
@@ -815,9 +758,10 @@
           <t>Capex reduces CFADS and thus available cash for debt paydown. Factor into covenant analysis.</t>
         </is>
       </c>
-      <c r="C23">
-        <f> EBITDA − Taxes</f>
-        <v/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EBITDA minus Taxes</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuition Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +55,13 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000066CC"/>
     </font>
   </fonts>
   <fills count="7">
@@ -111,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -156,6 +165,8 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -860,132 +871,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -993,6 +878,257 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: Midstream ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Time: 4 hours | Deliverables: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>SITUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>500 MMcf/d gathering in Permian at $400mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. What levered IRR at indicative price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Downside DSCR under stress?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Key diligence items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Protections to negotiate?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IC MEMO - COACHING FRAMEWORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>1. EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>Tip: Lead with IRR and recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>2. TRANSACTION OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>Tip: Sources &amp; uses, debt terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>3. INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>Tip: 3-4 bullets on attractiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>4. KEY RISKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>Tip: Market, operational, regulatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>5. MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>Tip: Hedging, contracts, structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>6. SENSITIVITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>Tip: ±10-20% on key inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>7. RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>Tip: Clear yes/no with walk-away price</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1141,7 +1277,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="28">
-        <f>MIN(E79:I79)</f>
+        <f>IF(COUNTIF(E79:I79,"&gt;0")&gt;0,MINIFS(E79:I79,E79:I79,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -2205,6 +2205,7 @@
         <v/>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
@@ -2222,43 +2223,43 @@
         </is>
       </c>
       <c r="E59" s="16">
-        <f>E56*E57*1000</f>
+        <f>E56*E57</f>
         <v/>
       </c>
       <c r="F59" s="16">
-        <f>F56*F57*1000</f>
+        <f>F56*F57</f>
         <v/>
       </c>
       <c r="G59" s="16">
-        <f>G56*G57*1000</f>
+        <f>G56*G57</f>
         <v/>
       </c>
       <c r="H59" s="16">
-        <f>H56*H57*1000</f>
+        <f>H56*H57</f>
         <v/>
       </c>
       <c r="I59" s="16">
-        <f>I56*I57*1000</f>
+        <f>I56*I57</f>
         <v/>
       </c>
       <c r="J59" s="16">
-        <f>J56*J57*1000</f>
+        <f>J56*J57</f>
         <v/>
       </c>
       <c r="K59" s="16">
-        <f>K56*K57*1000</f>
+        <f>K56*K57</f>
         <v/>
       </c>
       <c r="L59" s="16">
-        <f>L56*L57*1000</f>
+        <f>L56*L57</f>
         <v/>
       </c>
       <c r="M59" s="16">
-        <f>M56*M57*1000</f>
+        <f>M56*M57</f>
         <v/>
       </c>
       <c r="N59" s="16">
-        <f>N56*N57*1000</f>
+        <f>N56*N57</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuition Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,6 +167,12 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -241,21 +247,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Lotus Infrastructure</author>
-  </authors>
-  <commentList>
-    <comment ref="C23" authorId="0" shapeId="0">
-      <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -547,333 +538,653 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:A111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>MIDSTREAM MODEL - INTUITION GUIDE</t>
-        </is>
-      </c>
-      <c r="B1" s="22" t="inlineStr"/>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="21" t="inlineStr"/>
-      <c r="B2" s="22" t="inlineStr"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>SECTION</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>WHY IT MATTERS / KEY LOGIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="21" t="inlineStr"/>
-      <c r="B4" s="22" t="inlineStr"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
-        <is>
-          <t>═══ BUSINESS CONTEXT ═══</t>
-        </is>
-      </c>
-      <c r="B5" s="25" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>What is Midstream?</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>Gas gathering systems collect production from wellheads and deliver to processing plants/pipelines. Fee-for-service model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Fee-for-Service</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>Revenue = Volume × Fee ($/Mcf). No commodity exposure - you're paid to move gas, not sell it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Volume Risk</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>Key risk is producer activity. If drilling slows, volumes decline. Hence the growth-then-decline profile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="21" t="inlineStr"/>
-      <c r="B9" s="22" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>═══ VOLUME PROFILE ═══</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>Growth Phase (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>Active drilling - new wells connected. Volume grows 3%/year as producer develops acreage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Decline Phase (Y6-Y10)</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>Wells deplete naturally. 5%/year decline as production tails off. No new drilling assumed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Y5 Peak Volume</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>Y1 Volume × (1.03)^4 = peak. Then Y6 = Peak × (0.95), Y7 = Peak × (0.95)^2, etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="21" t="inlineStr"/>
-      <c r="B14" s="22" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>═══ FINANCING RATIONALE ═══</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>Short Tenor (5 years)</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>Must pay off debt BEFORE decline phase. Can't service debt with declining cash flows. De-risk early.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>Aggressive Sweep (75%)</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>Maximize paydown during growth phase. Every dollar of sweep reduces refinancing risk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>Lower Leverage (30%)</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>Basin/producer risk. More conservative than contracted assets. Single counterparty exposure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>Higher Rate (7%)</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>Basin-specific risk premium. Smaller asset, producer concentration, decline exposure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="21" t="inlineStr"/>
-      <c r="B20" s="22" t="inlineStr"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>═══ GROWTH CAPEX ═══</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>Y1-Y5 Only ($2mm/yr)</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>Compression, looping to handle growing volumes. Stops in Y6 when growth ends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>Impact on CFADS</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>Capex reduces CFADS and thus available cash for debt paydown. Factor into covenant analysis.</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>EBITDA minus Taxes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="21" t="inlineStr"/>
-      <c r="B24" s="22" t="inlineStr"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>═══ EXIT CONSIDERATIONS ═══</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>Compressed Multiple (6.5x)</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>Declining asset commands lower multiple than stable/growing assets. Reflects PDP-like value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>Exit at Y7 (Not Y10)</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>Better exit in early decline (Y7) when volumes still meaningful, vs late decline (Y10) with lower EBITDA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>Buyer Universe</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>Producer looking for vertical integration, larger midstream looking for bolt-on, PE doing roll-up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="21" t="inlineStr"/>
-      <c r="B29" s="22" t="inlineStr"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>═══ COMMON IC QUESTIONS ═══</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
-        <is>
-          <t>Q: What if producer goes bankrupt?</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="inlineStr">
-        <is>
-          <t>Volume risk - gatherer has no MVC protection typically. Counter: producer needs gatherer to monetize gas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
-        <is>
-          <t>Q: Why not longer hold period?</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="inlineStr">
-        <is>
-          <t>Exit before steep decline. Y7 EBITDA &gt; Y10 EBITDA. Don't ride declining asset down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>Q: Commodity exposure?</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>Fee-for-service = no direct commodity risk. But indirectly: low gas prices = less drilling = lower volumes.</t>
+    <row r="1">
+      <c r="A1">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LOTUS INFRASTRUCTURE PARTNERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: NATURAL GAS GATHERING SYSTEM ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIME: 4 Hours | DATE: January 2026 | DELIVERABLES: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>--- MODEL TIMELINE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Year 0 (2025): Transaction close Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Year 1-5 (2026-2030): Growth phase; volumes increase with new connections</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Year 5 (2030): Anchor shipper contract expires; recontracting risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Year 6-10 (2031-2035): Potential decline phase if no new drilling</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>--- SITUATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>Lotus Infrastructure Partners is evaluating a natural gas gathering
+system in the Permian Basin (Delaware sub-basin). Nameplate capacity is
+500 MMcf/d with current throughput of ~80 MMcf/d from 15 producer connections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>The anchor shipper contract covers 50 MMcf/d at $0.55/Mcf through 2030
+(5 years remaining) with 80% take-or-pay. Remaining ~30 MMcf/d is under
+short-term (1-2 year) gathering agreements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>Basin activity is strong with rig counts up 15% YoY. However, producer
+economics are sensitive to WTI and Henry Hub prices. The system has
+expansion capacity without major capex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>The seller (PE fund approaching end of fund life) is asking $85mm with
+bids due by February 10, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>--- KEY VALUE DRIVERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>* Volume Trajectory: Producer drilling activity drives throughput</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>* Take-or-Pay: 80% MVC provides revenue floor on contracted volumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>* Recontracting Risk: Anchor contract expiry in 2030 is key risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>* Basin Economics: WTI/HH prices drive producer drilling decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>--- STEP-BY-STEP MODEL BUILDING GUIDE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="inlineStr">
+        <is>
+          <t>STEP-BY-STEP MODEL BUILDING GUIDE FOR MIDSTREAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
+          <t>KEY DIFFERENCES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>- Volume-based revenue (not capacity x price)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>- Producer counterparty credit risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="inlineStr">
+        <is>
+          <t>- Volume decline curves for existing wells</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>- Recontracting risk at contract expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>- Gathering fee is $/Mcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>1. SET UP INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Y1 Volume: 80 MMcf/d (current throughput)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Gathering Fee: $0.55/Mcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Growth Rate Y1-5: 3%/year</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Decline Rate Y6-10: 5%/year</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - O&amp;M: $3.5mm/year base</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="35" t="inlineStr">
+        <is>
+          <t>2. BUILD VOLUME TRAJECTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Daily Volume Y1 = 80 MMcf/d</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Daily Volume Yn = Y(n-1) x (1 + Growth/Decline Rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Annual Volume (Bcf) = Daily Volume x 365 / 1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="35" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="35" t="inlineStr">
+        <is>
+          <t>3. BUILD REVENUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Revenue ($mm) = Annual Volume (Bcf) x Fee ($/Mcf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="35" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Why this works:</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 1 Bcf = 1,000,000 Mcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Revenue ($) = Bcf x 1,000,000 x $/Mcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Revenue ($mm) = Revenue ($) / 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Therefore: Revenue ($mm) = Bcf x $/Mcf (factors cancel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="35" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   NO *1000 multiplier needed!</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="35" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sanity Check: 29 Bcf x $0.55/Mcf = ~$16mm revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   This is reasonable for $85mm EV (5x EV/Revenue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="35" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="35" t="inlineStr">
+        <is>
+          <t>4. BUILD CFADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   CFADS = Revenue - O&amp;M - Taxes - Growth Capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Growth capex (wellhead connections) is BEFORE CFADS for midstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="35" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="35" t="inlineStr">
+        <is>
+          <t>5. DEBT STRUCTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   75% cash sweep (volume uncertainty warrants sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Shorter tenor (5 years) due to recontracting risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>--- HOW TO AVOID CIRCULARITY ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Same as CCGT - use Scheduled DS for DSRA Target to avoid circularity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="32" t="inlineStr">
+        <is>
+          <t>--- ALTERNATIVE SCENARIOS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A. Processing vs Gathering:</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - If system includes processing plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Processing revenue is $/MMBtu (different unit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B. Commodity Exposure:</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - If fee has commodity-linked component</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Must model WTI/HH price scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>C. Acreage Dedication:</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - If contract includes acreage dedication</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Provides volume upside if producer drills more</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="32" t="inlineStr">
+        <is>
+          <t>--- QA CHECKS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>QA CHECKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1. Revenue formula does NOT have erroneous *1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2. Y1 Revenue / Entry EV = reasonable multiple (4-6x typical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3. Volume trajectory makes sense (growth then decline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>4. Take-or-pay floor revenue = MVC x Fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>5. Recontracting scenario modeled for Year 5+</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>6. DSCR &gt;= 1.25x during debt tenor</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="32" t="inlineStr">
+        <is>
+          <t>--- HINTS &amp; PITFALLS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="33" t="inlineStr">
+        <is>
+          <t>* Revenue = Bcf x $/Mcf (NO conversion factor - they cancel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="33" t="inlineStr">
+        <is>
+          <t>* Y1 Revenue of ~$16mm on $85mm EV is ~5.3x, reasonable</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="33" t="inlineStr">
+        <is>
+          <t>* Recontracting at Year 5 is THE key risk - show sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="33" t="inlineStr">
+        <is>
+          <t>* Take-or-pay provides 80% floor on contracted volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="32" t="inlineStr">
+        <is>
+          <t>--- INTERVIEW QUESTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Q: Walk me through how you modeled volume decline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Q: What's your recontracting assumption when anchor expires?</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Q: How would a $10/bbl drop in WTI affect volume projections?</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Q: What producer credit diligence would you conduct?</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1159,38 +1470,60 @@
           <t>Midstream Model - Lotus Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>10</v>
+      <c r="D1" s="34" t="inlineStr">
+        <is>
+          <t>Y0 (2025)</t>
+        </is>
+      </c>
+      <c r="E1" s="34" t="inlineStr">
+        <is>
+          <t>Y1 (2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="34" t="inlineStr">
+        <is>
+          <t>Y2 (2027)</t>
+        </is>
+      </c>
+      <c r="G1" s="34" t="inlineStr">
+        <is>
+          <t>Y3 (2028)</t>
+        </is>
+      </c>
+      <c r="H1" s="34" t="inlineStr">
+        <is>
+          <t>Y4 (2029)</t>
+        </is>
+      </c>
+      <c r="I1" s="34" t="inlineStr">
+        <is>
+          <t>Y5 (2030)</t>
+        </is>
+      </c>
+      <c r="J1" s="34" t="inlineStr">
+        <is>
+          <t>Y6 (2031)</t>
+        </is>
+      </c>
+      <c r="K1" s="34" t="inlineStr">
+        <is>
+          <t>Y7 (2032)</t>
+        </is>
+      </c>
+      <c r="L1" s="34" t="inlineStr">
+        <is>
+          <t>Y8 (2033)</t>
+        </is>
+      </c>
+      <c r="M1" s="34" t="inlineStr">
+        <is>
+          <t>Y9 (2034)</t>
+        </is>
+      </c>
+      <c r="N1" s="34" t="inlineStr">
+        <is>
+          <t>Y10 (2035)</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -2205,7 +2538,6 @@
         <v/>
       </c>
     </row>
-    <row r="58"/>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,6 +86,12 @@
       <color rgb="001F4E79"/>
       <sz val="12"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -143,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -207,6 +213,14 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3189,196 +3203,196 @@
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="47" t="n"/>
+      <c r="B6" s="47" t="n"/>
+      <c r="C6" s="47" t="n"/>
+      <c r="D6" s="47" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="45" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="n"/>
+      <c r="C7" s="47" t="n"/>
+      <c r="D7" s="47" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="32" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="47" t="n"/>
+      <c r="B10" s="47" t="n"/>
+      <c r="C10" s="47" t="n"/>
+      <c r="D10" s="47" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="n"/>
+      <c r="C11" s="47" t="n"/>
+      <c r="D11" s="47" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="47" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="47" t="n"/>
+      <c r="B14" s="47" t="n"/>
+      <c r="C14" s="47" t="n"/>
+      <c r="D14" s="47" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="n"/>
+      <c r="C15" s="47" t="n"/>
+      <c r="D15" s="49" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="B16" s="47" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="B17" s="47" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="47" t="n"/>
+      <c r="B18" s="47" t="n"/>
+      <c r="C18" s="47" t="n"/>
+      <c r="D18" s="50" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="47" t="n"/>
+      <c r="C19" s="47" t="n"/>
+      <c r="D19" s="51" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="52" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="47" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D20" s="45" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="7">
-        <f>AVERAGE(E68:I68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="28">
-        <f>IF(COUNTIF(E79:I79,"&gt;0")&gt;0,MINIFS(E79:I79,E79:I79,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="29">
-        <f>D113</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="28">
-        <f>D114</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="29">
-        <f>D118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -3391,9 +3405,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
@@ -6327,196 +6341,196 @@
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="47" t="n"/>
+      <c r="B6" s="47" t="n"/>
+      <c r="C6" s="47" t="n"/>
+      <c r="D6" s="47" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="45" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="n"/>
+      <c r="C7" s="47" t="n"/>
+      <c r="D7" s="47" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="32" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="47" t="n"/>
+      <c r="B10" s="47" t="n"/>
+      <c r="C10" s="47" t="n"/>
+      <c r="D10" s="47" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="n"/>
+      <c r="C11" s="47" t="n"/>
+      <c r="D11" s="47" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="47" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="47" t="n"/>
+      <c r="B14" s="47" t="n"/>
+      <c r="C14" s="47" t="n"/>
+      <c r="D14" s="47" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="n"/>
+      <c r="C15" s="47" t="n"/>
+      <c r="D15" s="49" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="B16" s="47" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="B17" s="47" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="47" t="n"/>
+      <c r="B18" s="47" t="n"/>
+      <c r="C18" s="47" t="n"/>
+      <c r="D18" s="50" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="47" t="n"/>
+      <c r="C19" s="47" t="n"/>
+      <c r="D19" s="51" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="52" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="47" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D20" s="45" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="36" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="7">
-        <f>AVERAGE(E68:I68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="28">
-        <f>IF(COUNTIF(E79:I79,"&gt;0")&gt;0,MINIFS(E79:I79,E79:I79,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="29">
-        <f>D113</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="28">
-        <f>D114</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="29">
-        <f>D118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -6529,9 +6543,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +92,11 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -149,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -221,6 +226,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3065,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N128"/>
+  <dimension ref="A1:N129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3147,46 +3153,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE: Key formulas blanked. Rebuild using Formula Logic hints in Column C. ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>═══ AUDIT STRIP ═══</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Entry EV</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="7">
-        <f>$D$17</f>
-        <v/>
-      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Y1 EBITDA</t>
+          <t>Entry EV</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3196,617 +3192,614 @@
       </c>
       <c r="C4" s="6" t="inlineStr"/>
       <c r="D4" s="7">
-        <f>E62</f>
+        <f>$D$17</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Y1 EBITDA</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>═══════════ CONTROL PANEL ═══════════</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n"/>
-      <c r="C5" s="47" t="n"/>
-      <c r="D5" s="47" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="47" t="n"/>
       <c r="B6" s="47" t="n"/>
       <c r="C6" s="47" t="n"/>
       <c r="D6" s="47" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
+      <c r="A7" s="47" t="n"/>
       <c r="B7" s="47" t="n"/>
       <c r="C7" s="47" t="n"/>
       <c r="D7" s="47" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
+      <c r="A8" s="48" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="B8" s="47" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D8" s="45" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="C8" s="47" t="n"/>
+      <c r="D8" s="47" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
-          <t>Contract End Year</t>
+          <t>Revenue Mode</t>
         </is>
       </c>
       <c r="B9" s="47" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
+          <t>Merchant / Contracted / Hybrid</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>0 = pure merchant; else year PPA ends</t>
         </is>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D10" s="45" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="47" t="n"/>
-      <c r="B10" s="47" t="n"/>
-      <c r="C10" s="47" t="n"/>
-      <c r="D10" s="47" t="n"/>
-    </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
-        <is>
-          <t>TIMING</t>
-        </is>
-      </c>
+      <c r="A11" s="47" t="n"/>
       <c r="B11" s="47" t="n"/>
       <c r="C11" s="47" t="n"/>
       <c r="D11" s="47" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>Exit Year</t>
+      <c r="A12" s="48" t="inlineStr">
+        <is>
+          <t>TIMING</t>
         </is>
       </c>
       <c r="B12" s="47" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>5 / 7 / 10</t>
-        </is>
-      </c>
-      <c r="D12" s="45" t="n">
-        <v>7</v>
-      </c>
+      <c r="C12" s="47" t="n"/>
+      <c r="D12" s="47" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="32" t="inlineStr">
         <is>
-          <t>Tax Credit End Year</t>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B13" s="47" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
           <t>0 = N/A; else last year of PTC/ITC</t>
         </is>
       </c>
-      <c r="D13" s="45" t="n">
+      <c r="D14" s="45" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="47" t="n"/>
-      <c r="B14" s="47" t="n"/>
-      <c r="C14" s="47" t="n"/>
-      <c r="D14" s="47" t="n"/>
-    </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
+      <c r="A15" s="47" t="n"/>
       <c r="B15" s="47" t="n"/>
       <c r="C15" s="47" t="n"/>
-      <c r="D15" s="49" t="n"/>
+      <c r="D15" s="47" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t>Debt Sweep</t>
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>DEBT</t>
         </is>
       </c>
       <c r="B16" s="47" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF (for sweep assets)</t>
-        </is>
-      </c>
-      <c r="D16" s="31" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+      <c r="C16" s="47" t="n"/>
+      <c r="D16" s="49" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>Sweep %</t>
+          <t>Debt Sweep</t>
         </is>
       </c>
       <c r="B17" s="47" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>Sweep %</t>
+        </is>
+      </c>
+      <c r="B18" s="47" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
           <t>Active when Sweep = ON</t>
         </is>
       </c>
-      <c r="D17" s="30" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="47" t="n"/>
-      <c r="B18" s="47" t="n"/>
-      <c r="C18" s="47" t="n"/>
-      <c r="D18" s="50" t="n"/>
-    </row>
     <row r="19">
-      <c r="A19" s="48" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
+      <c r="A19" s="47" t="n"/>
       <c r="B19" s="47" t="n"/>
       <c r="C19" s="47" t="n"/>
-      <c r="D19" s="51" t="n"/>
+      <c r="D19" s="50" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="52" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B20" s="47" t="n"/>
+      <c r="C20" s="47" t="n"/>
+      <c r="D20" s="51" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="B21" s="47" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D20" s="45" t="inlineStr">
+      <c r="D21" s="45" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="10">
-        <f>D103</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Debt Payoff Y5</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
       <c r="D22" s="10">
-        <f>IF(I78&lt;1,"PASS","FAIL")</f>
+        <f>D103</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Min DSCR ≥ 1.25x</t>
+          <t>Debt Payoff Y5</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
       <c r="D23" s="10">
-        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+        <f>IF(I78&lt;1,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Min DSCR ≥ 1.25x</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr"/>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>TRANSACTION INPUTS</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Entry EV</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Purchase price</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>85</v>
-      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Transaction Fees</t>
+          <t>Entry EV</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Legal, advisory, financing</t>
-        </is>
-      </c>
-      <c r="D28" s="30" t="n">
-        <v>0.015</v>
+          <t>Purchase price</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Exit Multiple</t>
+          <t>Transaction Fees</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Compressed for decline</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="n">
-        <v>6.5</v>
+          <t>Legal, advisory, financing</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Compressed for decline</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>Exit Year</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Hold period</t>
         </is>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D31" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>VOLUME INPUTS</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Y1 Volume</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>MMcf/d</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Daily throughput</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>80</v>
-      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Growth Rate Y1-Y5</t>
+          <t>Y1 Volume</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>%/yr</t>
+          <t>MMcf/d</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Drilling phase</t>
-        </is>
-      </c>
-      <c r="D34" s="30" t="n">
-        <v>0.03</v>
+          <t>Daily throughput</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>Growth Rate Y1-Y5</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>%/yr</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Drilling phase</t>
+        </is>
+      </c>
+      <c r="D35" s="30" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>Decline Rate Y6-Y10</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>%/yr</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Depletion phase</t>
         </is>
       </c>
-      <c r="D35" s="30" t="n">
+      <c r="D36" s="30" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>PRICING INPUTS</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
-      <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>$/Mcf</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Gathering + compression</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>0.55</v>
-      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t>Total Fee</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>$/Mcf</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Gathering + compression</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
           <t>Fee Escalation</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>%/yr</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Contract escalation</t>
         </is>
       </c>
-      <c r="D39" s="30" t="n">
+      <c r="D40" s="30" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>COST INPUTS</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4" t="n"/>
-      <c r="L41" s="4" t="n"/>
-      <c r="M41" s="4" t="n"/>
-      <c r="N41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>O&amp;M Y1</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Operating costs</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>O&amp;M Escalation</t>
+          <t>O&amp;M Y1</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>%/yr</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Cost escalation</t>
-        </is>
-      </c>
-      <c r="D43" s="30" t="n">
-        <v>0.025</v>
+          <t>Operating costs</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>O&amp;M Escalation</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>%/yr</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Cost escalation</t>
+        </is>
+      </c>
+      <c r="D44" s="30" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>Growth Capex Y1-Y5</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>$mm/yr</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Compression, looping</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="D45" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>FINANCING INPUTS</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Leverage</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Debt / Entry EV</t>
-        </is>
-      </c>
-      <c r="D47" s="30" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Leverage</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -3816,137 +3809,138 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Higher (basin risk)</t>
+          <t>Debt / Entry EV</t>
         </is>
       </c>
       <c r="D48" s="30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Debt Tenor</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Short - pre-decline</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>5</v>
+          <t>Higher (basin risk)</t>
+        </is>
+      </c>
+      <c r="D49" s="30" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>DSRA Months</t>
+          <t>Debt Tenor</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Debt service reserve</t>
+          <t>Short - pre-decline</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep %</t>
+          <t>DSRA Months</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Aggressive paydown</t>
-        </is>
-      </c>
-      <c r="D51" s="30" t="n">
-        <v>0.75</v>
+          <t>Debt service reserve</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>Cash Sweep %</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Aggressive paydown</t>
+        </is>
+      </c>
+      <c r="D52" s="30" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>Lock-up DSCR</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Distribution threshold</t>
         </is>
       </c>
-      <c r="D52" s="31" t="n">
+      <c r="D53" s="31" t="n">
         <v>1.1</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>TAX INPUTS</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="n"/>
-      <c r="L54" s="4" t="n"/>
-      <c r="M54" s="4" t="n"/>
-      <c r="N54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Tax Rate</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Blended federal + state</t>
-        </is>
-      </c>
-      <c r="D55" s="30" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Depreciable Basis</t>
+          <t>Tax Rate</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -3956,78 +3950,78 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>% of EV for depreciation</t>
+          <t>Blended federal + state</t>
         </is>
       </c>
       <c r="D56" s="30" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
+          <t>Depreciable Basis</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>% of EV for depreciation</t>
+        </is>
+      </c>
+      <c r="D57" s="30" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
           <t>Depreciation Life</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>Straight-line</t>
         </is>
       </c>
-      <c r="D57" s="14" t="n">
+      <c r="D58" s="14" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>CALCULATED ITEMS</t>
         </is>
       </c>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="n"/>
-      <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="n"/>
-      <c r="K59" s="4" t="n"/>
-      <c r="L59" s="4" t="n"/>
-      <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>Debt Amount</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Entry EV × Leverage</t>
-        </is>
-      </c>
-      <c r="D60" s="16">
-        <f>$D$17*$D$37</f>
-        <v/>
-      </c>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Annual Depreciation</t>
+          <t>Debt Amount</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -4037,474 +4031,379 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>EV × Basis / Life</t>
+          <t>Entry EV × Leverage</t>
         </is>
       </c>
       <c r="D61" s="16">
-        <f>$D$17*$D$46/$D$47</f>
+        <f>$D$17*$D$37</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
+          <t>Annual Depreciation</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>EV × Basis / Life</t>
+        </is>
+      </c>
+      <c r="D62" s="16">
+        <f>$D$17*$D$46/$D$47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
           <t>Scheduled Principal</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>$mm/yr</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>Debt / Tenor</t>
         </is>
       </c>
-      <c r="D62" s="16">
-        <f>$D$50/$D$39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr"/>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>OPERATING MODEL</t>
         </is>
       </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Daily Volume</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>MMcf/d</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Growth then decline</t>
-        </is>
-      </c>
-      <c r="E65" s="17">
-        <f>$D$23*(1+$D$24)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F65" s="17">
-        <f>$D$23*(1+$D$24)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G65" s="17">
-        <f>$D$23*(1+$D$24)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H65" s="17">
-        <f>$D$23*(1+$D$24)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I65" s="17">
-        <f>$D$23*(1+$D$24)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J65" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(6-5)</f>
-        <v/>
-      </c>
-      <c r="K65" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(7-5)</f>
-        <v/>
-      </c>
-      <c r="L65" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(8-5)</f>
-        <v/>
-      </c>
-      <c r="M65" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(9-5)</f>
-        <v/>
-      </c>
-      <c r="N65" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(10-5)</f>
-        <v/>
-      </c>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="n"/>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="n"/>
+      <c r="J65" s="4" t="n"/>
+      <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Annual Volume</t>
+          <t>Daily Volume</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Bcf</t>
+          <t>MMcf/d</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Daily × 365 / 1000</t>
+          <t>Growth then decline</t>
         </is>
       </c>
       <c r="E66" s="17">
-        <f>E55*365/1000</f>
+        <f>$D$23*(1+$D$24)^(1-1)</f>
         <v/>
       </c>
       <c r="F66" s="17">
-        <f>F55*365/1000</f>
+        <f>$D$23*(1+$D$24)^(2-1)</f>
         <v/>
       </c>
       <c r="G66" s="17">
-        <f>G55*365/1000</f>
+        <f>$D$23*(1+$D$24)^(3-1)</f>
         <v/>
       </c>
       <c r="H66" s="17">
-        <f>H55*365/1000</f>
+        <f>$D$23*(1+$D$24)^(4-1)</f>
         <v/>
       </c>
       <c r="I66" s="17">
-        <f>I55*365/1000</f>
+        <f>$D$23*(1+$D$24)^(5-1)</f>
         <v/>
       </c>
       <c r="J66" s="17">
-        <f>J55*365/1000</f>
+        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(6-5)</f>
         <v/>
       </c>
       <c r="K66" s="17">
-        <f>K55*365/1000</f>
+        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(7-5)</f>
         <v/>
       </c>
       <c r="L66" s="17">
-        <f>L55*365/1000</f>
+        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(8-5)</f>
         <v/>
       </c>
       <c r="M66" s="17">
-        <f>M55*365/1000</f>
+        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(9-5)</f>
         <v/>
       </c>
       <c r="N66" s="17">
-        <f>N55*365/1000</f>
+        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(10-5)</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
+          <t>Annual Volume</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Bcf</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Daily × 365 / 1000</t>
+        </is>
+      </c>
+      <c r="E67" s="17">
+        <f>E55*365/1000</f>
+        <v/>
+      </c>
+      <c r="F67" s="17">
+        <f>F55*365/1000</f>
+        <v/>
+      </c>
+      <c r="G67" s="17">
+        <f>G55*365/1000</f>
+        <v/>
+      </c>
+      <c r="H67" s="17">
+        <f>H55*365/1000</f>
+        <v/>
+      </c>
+      <c r="I67" s="17">
+        <f>I55*365/1000</f>
+        <v/>
+      </c>
+      <c r="J67" s="17">
+        <f>J55*365/1000</f>
+        <v/>
+      </c>
+      <c r="K67" s="17">
+        <f>K55*365/1000</f>
+        <v/>
+      </c>
+      <c r="L67" s="17">
+        <f>L55*365/1000</f>
+        <v/>
+      </c>
+      <c r="M67" s="17">
+        <f>M55*365/1000</f>
+        <v/>
+      </c>
+      <c r="N67" s="17">
+        <f>N55*365/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>$/Mcf</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E67" s="18">
+      <c r="E68" s="18">
         <f>$D$28*(1+$D$29)^(1-1)</f>
         <v/>
       </c>
-      <c r="F67" s="18">
+      <c r="F68" s="18">
         <f>$D$28*(1+$D$29)^(2-1)</f>
         <v/>
       </c>
-      <c r="G67" s="18">
+      <c r="G68" s="18">
         <f>$D$28*(1+$D$29)^(3-1)</f>
         <v/>
       </c>
-      <c r="H67" s="18">
+      <c r="H68" s="18">
         <f>$D$28*(1+$D$29)^(4-1)</f>
         <v/>
       </c>
-      <c r="I67" s="18">
+      <c r="I68" s="18">
         <f>$D$28*(1+$D$29)^(5-1)</f>
         <v/>
       </c>
-      <c r="J67" s="18">
+      <c r="J68" s="18">
         <f>$D$28*(1+$D$29)^(6-1)</f>
         <v/>
       </c>
-      <c r="K67" s="18">
+      <c r="K68" s="18">
         <f>$D$28*(1+$D$29)^(7-1)</f>
         <v/>
       </c>
-      <c r="L67" s="18">
+      <c r="L68" s="18">
         <f>$D$28*(1+$D$29)^(8-1)</f>
         <v/>
       </c>
-      <c r="M67" s="18">
+      <c r="M68" s="18">
         <f>$D$28*(1+$D$29)^(9-1)</f>
         <v/>
       </c>
-      <c r="N67" s="18">
+      <c r="N68" s="18">
         <f>$D$28*(1+$D$29)^(10-1)</f>
         <v/>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Volume(Bcf) × Fee × 1000</t>
-        </is>
-      </c>
-      <c r="E69" s="16">
-        <f>E56*E57</f>
-        <v/>
-      </c>
-      <c r="F69" s="16">
-        <f>F56*F57</f>
-        <v/>
-      </c>
-      <c r="G69" s="16">
-        <f>G56*G57</f>
-        <v/>
-      </c>
-      <c r="H69" s="16">
-        <f>H56*H57</f>
-        <v/>
-      </c>
-      <c r="I69" s="16">
-        <f>I56*I57</f>
-        <v/>
-      </c>
-      <c r="J69" s="16">
-        <f>J56*J57</f>
-        <v/>
-      </c>
-      <c r="K69" s="16">
-        <f>K56*K57</f>
-        <v/>
-      </c>
-      <c r="L69" s="16">
-        <f>L56*L57</f>
-        <v/>
-      </c>
-      <c r="M69" s="16">
-        <f>M56*M57</f>
-        <v/>
-      </c>
-      <c r="N69" s="16">
-        <f>N56*N57</f>
-        <v/>
-      </c>
-    </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Volume(Bcf) × Fee × 1000</t>
+        </is>
+      </c>
+      <c r="E70" s="16" t="inlineStr"/>
+      <c r="F70" s="16" t="inlineStr"/>
+      <c r="G70" s="16" t="inlineStr"/>
+      <c r="H70" s="16" t="inlineStr"/>
+      <c r="I70" s="16" t="inlineStr"/>
+      <c r="J70" s="16" t="inlineStr"/>
+      <c r="K70" s="16" t="inlineStr"/>
+      <c r="L70" s="16" t="inlineStr"/>
+      <c r="M70" s="16" t="inlineStr"/>
+      <c r="N70" s="16" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
           <t>O&amp;M Cost</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E70" s="16">
+      <c r="E71" s="16">
         <f>$D$32*(1+$D$33)^(1-1)</f>
         <v/>
       </c>
-      <c r="F70" s="16">
+      <c r="F71" s="16">
         <f>$D$32*(1+$D$33)^(2-1)</f>
         <v/>
       </c>
-      <c r="G70" s="16">
+      <c r="G71" s="16">
         <f>$D$32*(1+$D$33)^(3-1)</f>
         <v/>
       </c>
-      <c r="H70" s="16">
+      <c r="H71" s="16">
         <f>$D$32*(1+$D$33)^(4-1)</f>
         <v/>
       </c>
-      <c r="I70" s="16">
+      <c r="I71" s="16">
         <f>$D$32*(1+$D$33)^(5-1)</f>
         <v/>
       </c>
-      <c r="J70" s="16">
+      <c r="J71" s="16">
         <f>$D$32*(1+$D$33)^(6-1)</f>
         <v/>
       </c>
-      <c r="K70" s="16">
+      <c r="K71" s="16">
         <f>$D$32*(1+$D$33)^(7-1)</f>
         <v/>
       </c>
-      <c r="L70" s="16">
+      <c r="L71" s="16">
         <f>$D$32*(1+$D$33)^(8-1)</f>
         <v/>
       </c>
-      <c r="M70" s="16">
+      <c r="M71" s="16">
         <f>$D$32*(1+$D$33)^(9-1)</f>
         <v/>
       </c>
-      <c r="N70" s="16">
+      <c r="N71" s="16">
         <f>$D$32*(1+$D$33)^(10-1)</f>
         <v/>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr"/>
-      <c r="E72" s="7">
-        <f>E59-E60</f>
-        <v/>
-      </c>
-      <c r="F72" s="7">
-        <f>F59-F60</f>
-        <v/>
-      </c>
-      <c r="G72" s="7">
-        <f>G59-G60</f>
-        <v/>
-      </c>
-      <c r="H72" s="7">
-        <f>H59-H60</f>
-        <v/>
-      </c>
-      <c r="I72" s="7">
-        <f>I59-I60</f>
-        <v/>
-      </c>
-      <c r="J72" s="7">
-        <f>J59-J60</f>
-        <v/>
-      </c>
-      <c r="K72" s="7">
-        <f>K59-K60</f>
-        <v/>
-      </c>
-      <c r="L72" s="7">
-        <f>L59-L60</f>
-        <v/>
-      </c>
-      <c r="M72" s="7">
-        <f>M59-M60</f>
-        <v/>
-      </c>
-      <c r="N72" s="7">
-        <f>N59-N60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr"/>
+      <c r="E73" s="7" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
+      <c r="K73" s="7" t="inlineStr"/>
+      <c r="L73" s="7" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+      <c r="N73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>CASH FLOW</t>
         </is>
       </c>
-      <c r="B74" s="4" t="n"/>
-      <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n"/>
-      <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="n"/>
-      <c r="J74" s="4" t="n"/>
-      <c r="K74" s="4" t="n"/>
-      <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA - Depreciation</t>
-        </is>
-      </c>
-      <c r="E75" s="16">
-        <f>E62-$D$51</f>
-        <v/>
-      </c>
-      <c r="F75" s="16">
-        <f>F62-$D$51</f>
-        <v/>
-      </c>
-      <c r="G75" s="16">
-        <f>G62-$D$51</f>
-        <v/>
-      </c>
-      <c r="H75" s="16">
-        <f>H62-$D$51</f>
-        <v/>
-      </c>
-      <c r="I75" s="16">
-        <f>I62-$D$51</f>
-        <v/>
-      </c>
-      <c r="J75" s="16">
-        <f>J62-$D$51</f>
-        <v/>
-      </c>
-      <c r="K75" s="16">
-        <f>K62-$D$51</f>
-        <v/>
-      </c>
-      <c r="L75" s="16">
-        <f>L62-$D$51</f>
-        <v/>
-      </c>
-      <c r="M75" s="16">
-        <f>M62-$D$51</f>
-        <v/>
-      </c>
-      <c r="N75" s="16">
-        <f>N62-$D$51</f>
-        <v/>
-      </c>
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>EBIT</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -4514,54 +4413,24 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, EBIT) × Tax Rate</t>
-        </is>
-      </c>
-      <c r="E76" s="16">
-        <f>MAX(0,E65)*$D$45</f>
-        <v/>
-      </c>
-      <c r="F76" s="16">
-        <f>MAX(0,F65)*$D$45</f>
-        <v/>
-      </c>
-      <c r="G76" s="16">
-        <f>MAX(0,G65)*$D$45</f>
-        <v/>
-      </c>
-      <c r="H76" s="16">
-        <f>MAX(0,H65)*$D$45</f>
-        <v/>
-      </c>
-      <c r="I76" s="16">
-        <f>MAX(0,I65)*$D$45</f>
-        <v/>
-      </c>
-      <c r="J76" s="16">
-        <f>MAX(0,J65)*$D$45</f>
-        <v/>
-      </c>
-      <c r="K76" s="16">
-        <f>MAX(0,K65)*$D$45</f>
-        <v/>
-      </c>
-      <c r="L76" s="16">
-        <f>MAX(0,L65)*$D$45</f>
-        <v/>
-      </c>
-      <c r="M76" s="16">
-        <f>MAX(0,M65)*$D$45</f>
-        <v/>
-      </c>
-      <c r="N76" s="16">
-        <f>MAX(0,N65)*$D$45</f>
-        <v/>
-      </c>
+          <t>EBITDA - Depreciation</t>
+        </is>
+      </c>
+      <c r="E76" s="16" t="inlineStr"/>
+      <c r="F76" s="16" t="inlineStr"/>
+      <c r="G76" s="16" t="inlineStr"/>
+      <c r="H76" s="16" t="inlineStr"/>
+      <c r="I76" s="16" t="inlineStr"/>
+      <c r="J76" s="16" t="inlineStr"/>
+      <c r="K76" s="16" t="inlineStr"/>
+      <c r="L76" s="16" t="inlineStr"/>
+      <c r="M76" s="16" t="inlineStr"/>
+      <c r="N76" s="16" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Growth Capex</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -4571,184 +4440,129 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Y1-Y5 only</t>
-        </is>
-      </c>
-      <c r="E77" s="19">
-        <f>IF(1&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="F77" s="19">
-        <f>IF(2&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="G77" s="19">
-        <f>IF(3&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="H77" s="19">
-        <f>IF(4&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="I77" s="19">
-        <f>IF(5&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="J77" s="19">
-        <f>IF(6&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="K77" s="19">
-        <f>IF(7&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="L77" s="19">
-        <f>IF(8&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="M77" s="19">
-        <f>IF(9&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="N77" s="19">
-        <f>IF(10&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
+          <t>MAX(0, EBIT) × Tax Rate</t>
+        </is>
+      </c>
+      <c r="E77" s="16" t="inlineStr"/>
+      <c r="F77" s="16" t="inlineStr"/>
+      <c r="G77" s="16" t="inlineStr"/>
+      <c r="H77" s="16" t="inlineStr"/>
+      <c r="I77" s="16" t="inlineStr"/>
+      <c r="J77" s="16" t="inlineStr"/>
+      <c r="K77" s="16" t="inlineStr"/>
+      <c r="L77" s="16" t="inlineStr"/>
+      <c r="M77" s="16" t="inlineStr"/>
+      <c r="N77" s="16" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
+          <t>Growth Capex</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Y1-Y5 only</t>
+        </is>
+      </c>
+      <c r="E78" s="19">
+        <f>IF(1&lt;=5,$D$34,0)</f>
+        <v/>
+      </c>
+      <c r="F78" s="19">
+        <f>IF(2&lt;=5,$D$34,0)</f>
+        <v/>
+      </c>
+      <c r="G78" s="19">
+        <f>IF(3&lt;=5,$D$34,0)</f>
+        <v/>
+      </c>
+      <c r="H78" s="19">
+        <f>IF(4&lt;=5,$D$34,0)</f>
+        <v/>
+      </c>
+      <c r="I78" s="19">
+        <f>IF(5&lt;=5,$D$34,0)</f>
+        <v/>
+      </c>
+      <c r="J78" s="19">
+        <f>IF(6&lt;=5,$D$34,0)</f>
+        <v/>
+      </c>
+      <c r="K78" s="19">
+        <f>IF(7&lt;=5,$D$34,0)</f>
+        <v/>
+      </c>
+      <c r="L78" s="19">
+        <f>IF(8&lt;=5,$D$34,0)</f>
+        <v/>
+      </c>
+      <c r="M78" s="19">
+        <f>IF(9&lt;=5,$D$34,0)</f>
+        <v/>
+      </c>
+      <c r="N78" s="19">
+        <f>IF(10&lt;=5,$D$34,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
           <t>CFADS</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>EBITDA - Taxes - Capex</t>
         </is>
       </c>
-      <c r="E78" s="7">
-        <f>E62-E66-E67</f>
-        <v/>
-      </c>
-      <c r="F78" s="7">
-        <f>F62-F66-F67</f>
-        <v/>
-      </c>
-      <c r="G78" s="7">
-        <f>G62-G66-G67</f>
-        <v/>
-      </c>
-      <c r="H78" s="7">
-        <f>H62-H66-H67</f>
-        <v/>
-      </c>
-      <c r="I78" s="7">
-        <f>I62-I66-I67</f>
-        <v/>
-      </c>
-      <c r="J78" s="7">
-        <f>J62-J66-J67</f>
-        <v/>
-      </c>
-      <c r="K78" s="7">
-        <f>K62-K66-K67</f>
-        <v/>
-      </c>
-      <c r="L78" s="7">
-        <f>L62-L66-L67</f>
-        <v/>
-      </c>
-      <c r="M78" s="7">
-        <f>M62-M66-M67</f>
-        <v/>
-      </c>
-      <c r="N78" s="7">
-        <f>N62-N66-N67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr"/>
+      <c r="K79" s="7" t="inlineStr"/>
+      <c r="L79" s="7" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+      <c r="N79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>DEBT SCHEDULE (75% Sweep, 5-Year Tenor)</t>
         </is>
       </c>
-      <c r="B80" s="4" t="n"/>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="4" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
-      <c r="J80" s="4" t="n"/>
-      <c r="K80" s="4" t="n"/>
-      <c r="L80" s="4" t="n"/>
-      <c r="M80" s="4" t="n"/>
-      <c r="N80" s="4" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr"/>
-      <c r="E81" s="16">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="F81" s="16">
-        <f>E78</f>
-        <v/>
-      </c>
-      <c r="G81" s="16">
-        <f>F78</f>
-        <v/>
-      </c>
-      <c r="H81" s="16">
-        <f>G78</f>
-        <v/>
-      </c>
-      <c r="I81" s="16">
-        <f>H78</f>
-        <v/>
-      </c>
-      <c r="J81" s="16">
-        <f>I78</f>
-        <v/>
-      </c>
-      <c r="K81" s="16">
-        <f>J78</f>
-        <v/>
-      </c>
-      <c r="L81" s="16">
-        <f>K78</f>
-        <v/>
-      </c>
-      <c r="M81" s="16">
-        <f>L78</f>
-        <v/>
-      </c>
-      <c r="N81" s="16">
-        <f>M78</f>
-        <v/>
-      </c>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="n"/>
+      <c r="J81" s="4" t="n"/>
+      <c r="K81" s="4" t="n"/>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="4" t="n"/>
+      <c r="N81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Beginning Balance</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -4756,56 +4570,52 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Beg Bal × Int Rate</t>
-        </is>
-      </c>
+      <c r="C82" s="6" t="inlineStr"/>
       <c r="E82" s="16">
-        <f>E71*$D$38</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="F82" s="16">
-        <f>F71*$D$38</f>
+        <f>E78</f>
         <v/>
       </c>
       <c r="G82" s="16">
-        <f>G71*$D$38</f>
+        <f>F78</f>
         <v/>
       </c>
       <c r="H82" s="16">
-        <f>H71*$D$38</f>
+        <f>G78</f>
         <v/>
       </c>
       <c r="I82" s="16">
-        <f>I71*$D$38</f>
+        <f>H78</f>
         <v/>
       </c>
       <c r="J82" s="16">
-        <f>J71*$D$38</f>
+        <f>I78</f>
         <v/>
       </c>
       <c r="K82" s="16">
-        <f>K71*$D$38</f>
+        <f>J78</f>
         <v/>
       </c>
       <c r="L82" s="16">
-        <f>L71*$D$38</f>
+        <f>K78</f>
         <v/>
       </c>
       <c r="M82" s="16">
-        <f>M71*$D$38</f>
+        <f>L78</f>
         <v/>
       </c>
       <c r="N82" s="16">
-        <f>N71*$D$38</f>
+        <f>M78</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Scheduled Principal</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -4815,54 +4625,24 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>MIN(Sched, Beg Bal)</t>
-        </is>
-      </c>
-      <c r="E83" s="16">
-        <f>MIN($D$52,E71)</f>
-        <v/>
-      </c>
-      <c r="F83" s="16">
-        <f>MIN($D$52,F71)</f>
-        <v/>
-      </c>
-      <c r="G83" s="16">
-        <f>MIN($D$52,G71)</f>
-        <v/>
-      </c>
-      <c r="H83" s="16">
-        <f>MIN($D$52,H71)</f>
-        <v/>
-      </c>
-      <c r="I83" s="16">
-        <f>MIN($D$52,I71)</f>
-        <v/>
-      </c>
-      <c r="J83" s="16">
-        <f>MIN($D$52,J71)</f>
-        <v/>
-      </c>
-      <c r="K83" s="16">
-        <f>MIN($D$52,K71)</f>
-        <v/>
-      </c>
-      <c r="L83" s="16">
-        <f>MIN($D$52,L71)</f>
-        <v/>
-      </c>
-      <c r="M83" s="16">
-        <f>MIN($D$52,M71)</f>
-        <v/>
-      </c>
-      <c r="N83" s="16">
-        <f>MIN($D$52,N71)</f>
-        <v/>
-      </c>
+          <t>Beg Bal × Int Rate</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="inlineStr"/>
+      <c r="F83" s="16" t="inlineStr"/>
+      <c r="G83" s="16" t="inlineStr"/>
+      <c r="H83" s="16" t="inlineStr"/>
+      <c r="I83" s="16" t="inlineStr"/>
+      <c r="J83" s="16" t="inlineStr"/>
+      <c r="K83" s="16" t="inlineStr"/>
+      <c r="L83" s="16" t="inlineStr"/>
+      <c r="M83" s="16" t="inlineStr"/>
+      <c r="N83" s="16" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Debt Service (Pre-Sweep)</t>
+          <t>Scheduled Principal</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -4872,54 +4652,24 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Interest + Sched Prin</t>
-        </is>
-      </c>
-      <c r="E84" s="16">
-        <f>E72+E73</f>
-        <v/>
-      </c>
-      <c r="F84" s="16">
-        <f>F72+F73</f>
-        <v/>
-      </c>
-      <c r="G84" s="16">
-        <f>G72+G73</f>
-        <v/>
-      </c>
-      <c r="H84" s="16">
-        <f>H72+H73</f>
-        <v/>
-      </c>
-      <c r="I84" s="16">
-        <f>I72+I73</f>
-        <v/>
-      </c>
-      <c r="J84" s="16">
-        <f>J72+J73</f>
-        <v/>
-      </c>
-      <c r="K84" s="16">
-        <f>K72+K73</f>
-        <v/>
-      </c>
-      <c r="L84" s="16">
-        <f>L72+L73</f>
-        <v/>
-      </c>
-      <c r="M84" s="16">
-        <f>M72+M73</f>
-        <v/>
-      </c>
-      <c r="N84" s="16">
-        <f>N72+N73</f>
-        <v/>
-      </c>
+          <t>MIN(Sched, Beg Bal)</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="inlineStr"/>
+      <c r="F84" s="16" t="inlineStr"/>
+      <c r="G84" s="16" t="inlineStr"/>
+      <c r="H84" s="16" t="inlineStr"/>
+      <c r="I84" s="16" t="inlineStr"/>
+      <c r="J84" s="16" t="inlineStr"/>
+      <c r="K84" s="16" t="inlineStr"/>
+      <c r="L84" s="16" t="inlineStr"/>
+      <c r="M84" s="16" t="inlineStr"/>
+      <c r="N84" s="16" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Excess Cash</t>
+          <t>Debt Service (Pre-Sweep)</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -4929,54 +4679,54 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>CFADS - DS - DSRA Funding</t>
+          <t>Interest + Sched Prin</t>
         </is>
       </c>
       <c r="E85" s="16">
-        <f>MAX(0,E68-E74-E85)</f>
+        <f>E72+E73</f>
         <v/>
       </c>
       <c r="F85" s="16">
-        <f>MAX(0,F68-F74-F85)</f>
+        <f>F72+F73</f>
         <v/>
       </c>
       <c r="G85" s="16">
-        <f>MAX(0,G68-G74-G85)</f>
+        <f>G72+G73</f>
         <v/>
       </c>
       <c r="H85" s="16">
-        <f>MAX(0,H68-H74-H85)</f>
+        <f>H72+H73</f>
         <v/>
       </c>
       <c r="I85" s="16">
-        <f>MAX(0,I68-I74-I85)</f>
+        <f>I72+I73</f>
         <v/>
       </c>
       <c r="J85" s="16">
-        <f>MAX(0,J68-J74-J85)</f>
+        <f>J72+J73</f>
         <v/>
       </c>
       <c r="K85" s="16">
-        <f>MAX(0,K68-K74-K85)</f>
+        <f>K72+K73</f>
         <v/>
       </c>
       <c r="L85" s="16">
-        <f>MAX(0,L68-L74-L85)</f>
+        <f>L72+L73</f>
         <v/>
       </c>
       <c r="M85" s="16">
-        <f>MAX(0,M68-M74-M85)</f>
+        <f>M72+M73</f>
         <v/>
       </c>
       <c r="N85" s="16">
-        <f>MAX(0,N68-N74-N85)</f>
+        <f>N72+N73</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep</t>
+          <t>Excess Cash</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -4986,54 +4736,54 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>MIN(Excess×75%, Beg-Sched)</t>
-        </is>
-      </c>
-      <c r="E86" s="19">
-        <f>MIN(MAX(0,E75)*$D$41,MAX(0,E71-E73))</f>
-        <v/>
-      </c>
-      <c r="F86" s="19">
-        <f>MIN(MAX(0,F75)*$D$41,MAX(0,F71-F73))</f>
-        <v/>
-      </c>
-      <c r="G86" s="19">
-        <f>MIN(MAX(0,G75)*$D$41,MAX(0,G71-G73))</f>
-        <v/>
-      </c>
-      <c r="H86" s="19">
-        <f>MIN(MAX(0,H75)*$D$41,MAX(0,H71-H73))</f>
-        <v/>
-      </c>
-      <c r="I86" s="19">
-        <f>MIN(MAX(0,I75)*$D$41,MAX(0,I71-I73))</f>
-        <v/>
-      </c>
-      <c r="J86" s="19">
-        <f>MIN(MAX(0,J75)*$D$41,MAX(0,J71-J73))</f>
-        <v/>
-      </c>
-      <c r="K86" s="19">
-        <f>MIN(MAX(0,K75)*$D$41,MAX(0,K71-K73))</f>
-        <v/>
-      </c>
-      <c r="L86" s="19">
-        <f>MIN(MAX(0,L75)*$D$41,MAX(0,L71-L73))</f>
-        <v/>
-      </c>
-      <c r="M86" s="19">
-        <f>MIN(MAX(0,M75)*$D$41,MAX(0,M71-M73))</f>
-        <v/>
-      </c>
-      <c r="N86" s="19">
-        <f>MIN(MAX(0,N75)*$D$41,MAX(0,N71-N73))</f>
+          <t>CFADS - DS - DSRA Funding</t>
+        </is>
+      </c>
+      <c r="E86" s="16">
+        <f>MAX(0,E68-E74-E85)</f>
+        <v/>
+      </c>
+      <c r="F86" s="16">
+        <f>MAX(0,F68-F74-F85)</f>
+        <v/>
+      </c>
+      <c r="G86" s="16">
+        <f>MAX(0,G68-G74-G85)</f>
+        <v/>
+      </c>
+      <c r="H86" s="16">
+        <f>MAX(0,H68-H74-H85)</f>
+        <v/>
+      </c>
+      <c r="I86" s="16">
+        <f>MAX(0,I68-I74-I85)</f>
+        <v/>
+      </c>
+      <c r="J86" s="16">
+        <f>MAX(0,J68-J74-J85)</f>
+        <v/>
+      </c>
+      <c r="K86" s="16">
+        <f>MAX(0,K68-K74-K85)</f>
+        <v/>
+      </c>
+      <c r="L86" s="16">
+        <f>MAX(0,L68-L74-L85)</f>
+        <v/>
+      </c>
+      <c r="M86" s="16">
+        <f>MAX(0,M68-M74-M85)</f>
+        <v/>
+      </c>
+      <c r="N86" s="16">
+        <f>MAX(0,N68-N74-N85)</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Total Principal</t>
+          <t>Cash Sweep</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -5043,54 +4793,24 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Scheduled + Sweep</t>
-        </is>
-      </c>
-      <c r="E87" s="16">
-        <f>E73+E76</f>
-        <v/>
-      </c>
-      <c r="F87" s="16">
-        <f>F73+F76</f>
-        <v/>
-      </c>
-      <c r="G87" s="16">
-        <f>G73+G76</f>
-        <v/>
-      </c>
-      <c r="H87" s="16">
-        <f>H73+H76</f>
-        <v/>
-      </c>
-      <c r="I87" s="16">
-        <f>I73+I76</f>
-        <v/>
-      </c>
-      <c r="J87" s="16">
-        <f>J73+J76</f>
-        <v/>
-      </c>
-      <c r="K87" s="16">
-        <f>K73+K76</f>
-        <v/>
-      </c>
-      <c r="L87" s="16">
-        <f>L73+L76</f>
-        <v/>
-      </c>
-      <c r="M87" s="16">
-        <f>M73+M76</f>
-        <v/>
-      </c>
-      <c r="N87" s="16">
-        <f>N73+N76</f>
-        <v/>
-      </c>
+          <t>MIN(Excess×75%, Beg-Sched)</t>
+        </is>
+      </c>
+      <c r="E87" s="19" t="inlineStr"/>
+      <c r="F87" s="19" t="inlineStr"/>
+      <c r="G87" s="19" t="inlineStr"/>
+      <c r="H87" s="19" t="inlineStr"/>
+      <c r="I87" s="19" t="inlineStr"/>
+      <c r="J87" s="19" t="inlineStr"/>
+      <c r="K87" s="19" t="inlineStr"/>
+      <c r="L87" s="19" t="inlineStr"/>
+      <c r="M87" s="19" t="inlineStr"/>
+      <c r="N87" s="19" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Ending Balance</t>
+          <t>Total Principal</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -5100,249 +4820,156 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, Beg - Total Prin)</t>
-        </is>
-      </c>
-      <c r="E88" s="16">
-        <f>MAX(0,E71-E77)</f>
-        <v/>
-      </c>
-      <c r="F88" s="16">
-        <f>MAX(0,F71-F77)</f>
-        <v/>
-      </c>
-      <c r="G88" s="16">
-        <f>MAX(0,G71-G77)</f>
-        <v/>
-      </c>
-      <c r="H88" s="16">
-        <f>MAX(0,H71-H77)</f>
-        <v/>
-      </c>
-      <c r="I88" s="16">
-        <f>MAX(0,I71-I77)</f>
-        <v/>
-      </c>
-      <c r="J88" s="16">
-        <f>MAX(0,J71-J77)</f>
-        <v/>
-      </c>
-      <c r="K88" s="16">
-        <f>MAX(0,K71-K77)</f>
-        <v/>
-      </c>
-      <c r="L88" s="16">
-        <f>MAX(0,L71-L77)</f>
-        <v/>
-      </c>
-      <c r="M88" s="16">
-        <f>MAX(0,M71-M77)</f>
-        <v/>
-      </c>
-      <c r="N88" s="16">
-        <f>MAX(0,N71-N77)</f>
-        <v/>
-      </c>
+          <t>Scheduled + Sweep</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="inlineStr"/>
+      <c r="F88" s="16" t="inlineStr"/>
+      <c r="G88" s="16" t="inlineStr"/>
+      <c r="H88" s="16" t="inlineStr"/>
+      <c r="I88" s="16" t="inlineStr"/>
+      <c r="J88" s="16" t="inlineStr"/>
+      <c r="K88" s="16" t="inlineStr"/>
+      <c r="L88" s="16" t="inlineStr"/>
+      <c r="M88" s="16" t="inlineStr"/>
+      <c r="N88" s="16" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>DSCR</t>
+          <t>Ending Balance</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="E89" s="28">
-        <f>IF(E74&gt;0,E68/E74,0)</f>
-        <v/>
-      </c>
-      <c r="F89" s="28">
-        <f>IF(F74&gt;0,F68/F74,0)</f>
-        <v/>
-      </c>
-      <c r="G89" s="28">
-        <f>IF(G74&gt;0,G68/G74,0)</f>
-        <v/>
-      </c>
-      <c r="H89" s="28">
-        <f>IF(H74&gt;0,H68/H74,0)</f>
-        <v/>
-      </c>
-      <c r="I89" s="28">
-        <f>IF(I74&gt;0,I68/I74,0)</f>
-        <v/>
-      </c>
-      <c r="J89" s="28">
-        <f>IF(J74&gt;0,J68/J74,0)</f>
-        <v/>
-      </c>
-      <c r="K89" s="28">
-        <f>IF(K74&gt;0,K68/K74,0)</f>
-        <v/>
-      </c>
-      <c r="L89" s="28">
-        <f>IF(L74&gt;0,L68/L74,0)</f>
-        <v/>
-      </c>
-      <c r="M89" s="28">
-        <f>IF(M74&gt;0,M68/M74,0)</f>
-        <v/>
-      </c>
-      <c r="N89" s="28">
-        <f>IF(N74&gt;0,N68/N74,0)</f>
-        <v/>
-      </c>
+          <t>MAX(0, Beg - Total Prin)</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr"/>
+      <c r="F89" s="16" t="inlineStr"/>
+      <c r="G89" s="16" t="inlineStr"/>
+      <c r="H89" s="16" t="inlineStr"/>
+      <c r="I89" s="16" t="inlineStr"/>
+      <c r="J89" s="16" t="inlineStr"/>
+      <c r="K89" s="16" t="inlineStr"/>
+      <c r="L89" s="16" t="inlineStr"/>
+      <c r="M89" s="16" t="inlineStr"/>
+      <c r="N89" s="16" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
+          <t>DSCR</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
+      <c r="E90" s="28" t="inlineStr"/>
+      <c r="F90" s="28" t="inlineStr"/>
+      <c r="G90" s="28" t="inlineStr"/>
+      <c r="H90" s="28" t="inlineStr"/>
+      <c r="I90" s="28" t="inlineStr"/>
+      <c r="J90" s="28" t="inlineStr"/>
+      <c r="K90" s="28" t="inlineStr"/>
+      <c r="L90" s="28" t="inlineStr"/>
+      <c r="M90" s="28" t="inlineStr"/>
+      <c r="N90" s="28" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
           <t>Scheduled DS (for DSRA)</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>Based on straight-line amort, no sweep</t>
         </is>
       </c>
-      <c r="E90" s="16">
+      <c r="E91" s="16">
         <f>MAX(0,$D$50-(1-1)*$D$52)*$D$38+$D$52</f>
         <v/>
       </c>
-      <c r="F90" s="16">
+      <c r="F91" s="16">
         <f>MAX(0,$D$50-(2-1)*$D$52)*$D$38+$D$52</f>
         <v/>
       </c>
-      <c r="G90" s="16">
+      <c r="G91" s="16">
         <f>MAX(0,$D$50-(3-1)*$D$52)*$D$38+$D$52</f>
         <v/>
       </c>
-      <c r="H90" s="16">
+      <c r="H91" s="16">
         <f>MAX(0,$D$50-(4-1)*$D$52)*$D$38+$D$52</f>
         <v/>
       </c>
-      <c r="I90" s="16">
+      <c r="I91" s="16">
         <f>MAX(0,$D$50-(5-1)*$D$52)*$D$38+$D$52</f>
         <v/>
       </c>
-      <c r="J90" s="16">
+      <c r="J91" s="16">
         <f>MAX(0,$D$50-(6-1)*$D$52)*$D$38+$D$52</f>
         <v/>
       </c>
-      <c r="K90" s="16">
+      <c r="K91" s="16">
         <f>MAX(0,$D$50-(7-1)*$D$52)*$D$38+$D$52</f>
         <v/>
       </c>
-      <c r="L90" s="16">
+      <c r="L91" s="16">
         <f>MAX(0,$D$50-(8-1)*$D$52)*$D$38+$D$52</f>
         <v/>
       </c>
-      <c r="M90" s="16">
+      <c r="M91" s="16">
         <f>MAX(0,$D$50-(9-1)*$D$52)*$D$38+$D$52</f>
         <v/>
       </c>
-      <c r="N90" s="16">
+      <c r="N91" s="16">
         <f>MAX(0,$D$50-(10-1)*$D$52)*$D$38+$D$52</f>
         <v/>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>DSRA (Debt Service Reserve Account)</t>
         </is>
       </c>
-      <c r="B92" s="4" t="n"/>
-      <c r="C92" s="4" t="n"/>
-      <c r="D92" s="4" t="n"/>
-      <c r="E92" s="4" t="n"/>
-      <c r="F92" s="4" t="n"/>
-      <c r="G92" s="4" t="n"/>
-      <c r="H92" s="4" t="n"/>
-      <c r="I92" s="4" t="n"/>
-      <c r="J92" s="4" t="n"/>
-      <c r="K92" s="4" t="n"/>
-      <c r="L92" s="4" t="n"/>
-      <c r="M92" s="4" t="n"/>
-      <c r="N92" s="4" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Target</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D93" s="16">
-        <f>E80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="E93" s="16">
-        <f>F80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="F93" s="16">
-        <f>G80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="G93" s="16">
-        <f>H80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="H93" s="16">
-        <f>I80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="I93" s="16">
-        <f>J80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="J93" s="16">
-        <f>K80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="K93" s="16">
-        <f>L80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="L93" s="16">
-        <f>M80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="M93" s="16">
-        <f>N80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="N93" s="16">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="n"/>
+      <c r="J93" s="4" t="n"/>
+      <c r="K93" s="4" t="n"/>
+      <c r="L93" s="4" t="n"/>
+      <c r="M93" s="4" t="n"/>
+      <c r="N93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Target</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -5350,56 +4977,60 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr"/>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
+        </is>
+      </c>
       <c r="D94" s="16">
+        <f>E80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="E94" s="16">
+        <f>F80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="F94" s="16">
+        <f>G80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="G94" s="16">
+        <f>H80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="H94" s="16">
+        <f>I80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="I94" s="16">
+        <f>J80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="J94" s="16">
+        <f>K80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="K94" s="16">
+        <f>L80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="L94" s="16">
+        <f>M80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="M94" s="16">
+        <f>N80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="N94" s="16">
         <f>0</f>
-        <v/>
-      </c>
-      <c r="E94" s="16">
-        <f>D86</f>
-        <v/>
-      </c>
-      <c r="F94" s="16">
-        <f>E86</f>
-        <v/>
-      </c>
-      <c r="G94" s="16">
-        <f>F86</f>
-        <v/>
-      </c>
-      <c r="H94" s="16">
-        <f>G86</f>
-        <v/>
-      </c>
-      <c r="I94" s="16">
-        <f>H86</f>
-        <v/>
-      </c>
-      <c r="J94" s="16">
-        <f>I86</f>
-        <v/>
-      </c>
-      <c r="K94" s="16">
-        <f>J86</f>
-        <v/>
-      </c>
-      <c r="L94" s="16">
-        <f>K86</f>
-        <v/>
-      </c>
-      <c r="M94" s="16">
-        <f>L86</f>
-        <v/>
-      </c>
-      <c r="N94" s="16">
-        <f>M86</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -5407,354 +5038,365 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>Target - Beginning</t>
-        </is>
-      </c>
+      <c r="C95" s="6" t="inlineStr"/>
       <c r="D95" s="16">
-        <f>D83-D84</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E95" s="16">
-        <f>E83-E84</f>
+        <f>D86</f>
         <v/>
       </c>
       <c r="F95" s="16">
-        <f>F83-F84</f>
+        <f>E86</f>
         <v/>
       </c>
       <c r="G95" s="16">
-        <f>G83-G84</f>
+        <f>F86</f>
         <v/>
       </c>
       <c r="H95" s="16">
-        <f>H83-H84</f>
+        <f>G86</f>
         <v/>
       </c>
       <c r="I95" s="16">
-        <f>I83-I84</f>
+        <f>H86</f>
         <v/>
       </c>
       <c r="J95" s="16">
-        <f>J83-J84</f>
+        <f>I86</f>
         <v/>
       </c>
       <c r="K95" s="16">
-        <f>K83-K84</f>
+        <f>J86</f>
         <v/>
       </c>
       <c r="L95" s="16">
-        <f>L83-L84</f>
+        <f>K86</f>
         <v/>
       </c>
       <c r="M95" s="16">
-        <f>M83-M84</f>
+        <f>L86</f>
         <v/>
       </c>
       <c r="N95" s="16">
-        <f>N83-N84</f>
+        <f>M86</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
+          <t>DSRA Funding/(Release)</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
+      <c r="D96" s="16">
+        <f>D83-D84</f>
+        <v/>
+      </c>
+      <c r="E96" s="16">
+        <f>E83-E84</f>
+        <v/>
+      </c>
+      <c r="F96" s="16">
+        <f>F83-F84</f>
+        <v/>
+      </c>
+      <c r="G96" s="16">
+        <f>G83-G84</f>
+        <v/>
+      </c>
+      <c r="H96" s="16">
+        <f>H83-H84</f>
+        <v/>
+      </c>
+      <c r="I96" s="16">
+        <f>I83-I84</f>
+        <v/>
+      </c>
+      <c r="J96" s="16">
+        <f>J83-J84</f>
+        <v/>
+      </c>
+      <c r="K96" s="16">
+        <f>K83-K84</f>
+        <v/>
+      </c>
+      <c r="L96" s="16">
+        <f>L83-L84</f>
+        <v/>
+      </c>
+      <c r="M96" s="16">
+        <f>M83-M84</f>
+        <v/>
+      </c>
+      <c r="N96" s="16">
+        <f>N83-N84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
           <t>DSRA Ending</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>Beginning + Funding</t>
         </is>
       </c>
-      <c r="D96" s="16">
+      <c r="D97" s="16">
         <f>D84+D85</f>
         <v/>
       </c>
-      <c r="E96" s="16">
+      <c r="E97" s="16">
         <f>E84+E85</f>
         <v/>
       </c>
-      <c r="F96" s="16">
+      <c r="F97" s="16">
         <f>F84+F85</f>
         <v/>
       </c>
-      <c r="G96" s="16">
+      <c r="G97" s="16">
         <f>G84+G85</f>
         <v/>
       </c>
-      <c r="H96" s="16">
+      <c r="H97" s="16">
         <f>H84+H85</f>
         <v/>
       </c>
-      <c r="I96" s="16">
+      <c r="I97" s="16">
         <f>I84+I85</f>
         <v/>
       </c>
-      <c r="J96" s="16">
+      <c r="J97" s="16">
         <f>J84+J85</f>
         <v/>
       </c>
-      <c r="K96" s="16">
+      <c r="K97" s="16">
         <f>K84+K85</f>
         <v/>
       </c>
-      <c r="L96" s="16">
+      <c r="L97" s="16">
         <f>L84+L85</f>
         <v/>
       </c>
-      <c r="M96" s="16">
+      <c r="M97" s="16">
         <f>M84+M85</f>
         <v/>
       </c>
-      <c r="N96" s="16">
+      <c r="N97" s="16">
         <f>N84+N85</f>
         <v/>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>DISTRIBUTION WATERFALL</t>
         </is>
       </c>
-      <c r="B97" s="4" t="n"/>
-      <c r="C97" s="4" t="n"/>
-      <c r="D97" s="4" t="n"/>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="4" t="n"/>
-      <c r="G97" s="4" t="n"/>
-      <c r="H97" s="4" t="n"/>
-      <c r="I97" s="4" t="n"/>
-      <c r="J97" s="4" t="n"/>
-      <c r="K97" s="4" t="n"/>
-      <c r="L97" s="4" t="n"/>
-      <c r="M97" s="4" t="n"/>
-      <c r="N97" s="4" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Cash Available for Distribution</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>CFADS - Total DS - DSRA Fund</t>
-        </is>
-      </c>
-      <c r="E98" s="16">
-        <f>E68-(E72+E77)-E85</f>
-        <v/>
-      </c>
-      <c r="F98" s="16">
-        <f>F68-(F72+F77)-F85</f>
-        <v/>
-      </c>
-      <c r="G98" s="16">
-        <f>G68-(G72+G77)-G85</f>
-        <v/>
-      </c>
-      <c r="H98" s="16">
-        <f>H68-(H72+H77)-H85</f>
-        <v/>
-      </c>
-      <c r="I98" s="16">
-        <f>I68-(I72+I77)-I85</f>
-        <v/>
-      </c>
-      <c r="J98" s="16">
-        <f>J68-(J72+J77)-J85</f>
-        <v/>
-      </c>
-      <c r="K98" s="16">
-        <f>K68-(K72+K77)-K85</f>
-        <v/>
-      </c>
-      <c r="L98" s="16">
-        <f>L68-(L72+L77)-L85</f>
-        <v/>
-      </c>
-      <c r="M98" s="16">
-        <f>M68-(M72+M77)-M85</f>
-        <v/>
-      </c>
-      <c r="N98" s="16">
-        <f>N68-(N72+N77)-N85</f>
-        <v/>
-      </c>
+      <c r="B98" s="4" t="n"/>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="n"/>
+      <c r="G98" s="4" t="n"/>
+      <c r="H98" s="4" t="n"/>
+      <c r="I98" s="4" t="n"/>
+      <c r="J98" s="4" t="n"/>
+      <c r="K98" s="4" t="n"/>
+      <c r="L98" s="4" t="n"/>
+      <c r="M98" s="4" t="n"/>
+      <c r="N98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr"/>
+          <t>Cash Available for Distribution</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>PASS if DSCR ≥ Lock-up</t>
-        </is>
-      </c>
-      <c r="E99" s="20">
-        <f>IF(E79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F99" s="20">
-        <f>IF(F79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="G99" s="20">
-        <f>IF(G79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="H99" s="20">
-        <f>IF(H79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="I99" s="20">
-        <f>IF(I79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="J99" s="20">
-        <f>IF(J79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="K99" s="20">
-        <f>IF(K79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="L99" s="20">
-        <f>IF(L79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="M99" s="20">
-        <f>IF(M79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="N99" s="20">
-        <f>IF(N79&gt;=$D$42,"PASS","LOCKED")</f>
+          <t>CFADS - Total DS - DSRA Fund</t>
+        </is>
+      </c>
+      <c r="E99" s="16">
+        <f>E68-(E72+E77)-E85</f>
+        <v/>
+      </c>
+      <c r="F99" s="16">
+        <f>F68-(F72+F77)-F85</f>
+        <v/>
+      </c>
+      <c r="G99" s="16">
+        <f>G68-(G72+G77)-G85</f>
+        <v/>
+      </c>
+      <c r="H99" s="16">
+        <f>H68-(H72+H77)-H85</f>
+        <v/>
+      </c>
+      <c r="I99" s="16">
+        <f>I68-(I72+I77)-I85</f>
+        <v/>
+      </c>
+      <c r="J99" s="16">
+        <f>J68-(J72+J77)-J85</f>
+        <v/>
+      </c>
+      <c r="K99" s="16">
+        <f>K68-(K72+K77)-K85</f>
+        <v/>
+      </c>
+      <c r="L99" s="16">
+        <f>L68-(L72+L77)-L85</f>
+        <v/>
+      </c>
+      <c r="M99" s="16">
+        <f>M68-(M72+M77)-M85</f>
+        <v/>
+      </c>
+      <c r="N99" s="16">
+        <f>N68-(N72+N77)-N85</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
+          <t>Lock-up Test</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr"/>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>PASS if DSCR ≥ Lock-up</t>
+        </is>
+      </c>
+      <c r="E100" s="20">
+        <f>IF(E79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F100" s="20">
+        <f>IF(F79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G100" s="20">
+        <f>IF(G79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H100" s="20">
+        <f>IF(H79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I100" s="20">
+        <f>IF(I79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J100" s="20">
+        <f>IF(J79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K100" s="20">
+        <f>IF(K79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L100" s="20">
+        <f>IF(L79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M100" s="20">
+        <f>IF(M79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N100" s="20">
+        <f>IF(N79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
           <t>Distributable Cash</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>If PASS, MAX(0, Cash Avail)</t>
         </is>
       </c>
-      <c r="E100" s="7">
-        <f>IF(E89="PASS",MAX(0,E88),0)</f>
-        <v/>
-      </c>
-      <c r="F100" s="7">
-        <f>IF(F89="PASS",MAX(0,F88),0)</f>
-        <v/>
-      </c>
-      <c r="G100" s="7">
-        <f>IF(G89="PASS",MAX(0,G88),0)</f>
-        <v/>
-      </c>
-      <c r="H100" s="7">
-        <f>IF(H89="PASS",MAX(0,H88),0)</f>
-        <v/>
-      </c>
-      <c r="I100" s="7">
-        <f>IF(I89="PASS",MAX(0,I88),0)</f>
-        <v/>
-      </c>
-      <c r="J100" s="7">
-        <f>IF(J89="PASS",MAX(0,J88),0)</f>
-        <v/>
-      </c>
-      <c r="K100" s="7">
-        <f>IF(K89="PASS",MAX(0,K88),0)</f>
-        <v/>
-      </c>
-      <c r="L100" s="7">
-        <f>IF(L89="PASS",MAX(0,L88),0)</f>
-        <v/>
-      </c>
-      <c r="M100" s="7">
-        <f>IF(M89="PASS",MAX(0,M88),0)</f>
-        <v/>
-      </c>
-      <c r="N100" s="7">
-        <f>IF(N89="PASS",MAX(0,N88),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr"/>
+      <c r="F101" s="7" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr"/>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr"/>
+      <c r="J101" s="7" t="inlineStr"/>
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+      <c r="N101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>SOURCES &amp; USES (Year 0)</t>
         </is>
       </c>
-      <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
-      <c r="E102" s="4" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
-      <c r="K102" s="4" t="n"/>
-      <c r="L102" s="4" t="n"/>
-      <c r="M102" s="4" t="n"/>
-      <c r="N102" s="4" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="21" t="inlineStr">
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="inlineStr">
         <is>
           <t>USES</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr"/>
-      <c r="C103" s="6" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Purchase Price</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B104" s="6" t="inlineStr"/>
       <c r="C104" s="6" t="inlineStr"/>
-      <c r="D104" s="16">
-        <f>$D$17</f>
-        <v/>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Transaction Fees</t>
+          <t xml:space="preserve">  Purchase Price</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
@@ -5764,14 +5406,14 @@
       </c>
       <c r="C105" s="6" t="inlineStr"/>
       <c r="D105" s="16">
-        <f>$D$17*$D$18</f>
+        <f>$D$17</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSRA Funding</t>
+          <t xml:space="preserve">  Transaction Fees</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
@@ -5781,57 +5423,58 @@
       </c>
       <c r="C106" s="6" t="inlineStr"/>
       <c r="D106" s="16">
-        <f>D83</f>
+        <f>$D$17*$D$18</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  DSRA Funding</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr"/>
+      <c r="D107" s="16">
+        <f>D83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
           <t>Total Uses</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr"/>
-      <c r="D107" s="7">
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr"/>
+      <c r="D108" s="7">
         <f>D94+D95+D96</f>
         <v/>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="21" t="inlineStr">
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="21" t="inlineStr">
         <is>
           <t>SOURCES</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr"/>
-      <c r="C109" s="6" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Debt</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B110" s="6" t="inlineStr"/>
       <c r="C110" s="6" t="inlineStr"/>
-      <c r="D110" s="16">
-        <f>$D$50</f>
-        <v/>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Equity</t>
+          <t xml:space="preserve">  Debt</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -5839,20 +5482,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>Plug to balance</t>
-        </is>
-      </c>
+      <c r="C111" s="6" t="inlineStr"/>
       <c r="D111" s="16">
-        <f>D97-D100</f>
+        <f>$D$50</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Total Sources</t>
+          <t xml:space="preserve">  Equity</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
@@ -5860,70 +5499,71 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr"/>
-      <c r="D112" s="7">
-        <f>D100+D101</f>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Plug to balance</t>
+        </is>
+      </c>
+      <c r="D112" s="16">
+        <f>D97-D100</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
+          <t>Total Sources</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr"/>
+      <c r="D113" s="7">
+        <f>D100+D101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
           <t>Balance Check</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr"/>
-      <c r="C113" s="6" t="inlineStr"/>
-      <c r="D113" s="10">
+      <c r="B114" s="6" t="inlineStr"/>
+      <c r="C114" s="6" t="inlineStr"/>
+      <c r="D114" s="10">
         <f>IF(ABS(D97-D102)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+    <row r="115"/>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>EXIT CALCULATIONS</t>
         </is>
       </c>
-      <c r="B115" s="4" t="n"/>
-      <c r="C115" s="4" t="n"/>
-      <c r="D115" s="4" t="n"/>
-      <c r="E115" s="4" t="n"/>
-      <c r="F115" s="4" t="n"/>
-      <c r="G115" s="4" t="n"/>
-      <c r="H115" s="4" t="n"/>
-      <c r="I115" s="4" t="n"/>
-      <c r="J115" s="4" t="n"/>
-      <c r="K115" s="4" t="n"/>
-      <c r="L115" s="4" t="n"/>
-      <c r="M115" s="4" t="n"/>
-      <c r="N115" s="4" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>Exit EV</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>Exit Multiple × Exit Yr EBITDA</t>
-        </is>
-      </c>
-      <c r="K116" s="16">
-        <f>$D$19*K62</f>
-        <v/>
-      </c>
+      <c r="B116" s="4" t="n"/>
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="n"/>
+      <c r="G116" s="4" t="n"/>
+      <c r="H116" s="4" t="n"/>
+      <c r="I116" s="4" t="n"/>
+      <c r="J116" s="4" t="n"/>
+      <c r="K116" s="4" t="n"/>
+      <c r="L116" s="4" t="n"/>
+      <c r="M116" s="4" t="n"/>
+      <c r="N116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Exit Debt Payoff</t>
+          <t>Exit EV</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -5933,18 +5573,15 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Ending Bal at Exit</t>
-        </is>
-      </c>
-      <c r="K117" s="16">
-        <f>K78</f>
-        <v/>
-      </c>
+          <t>Exit Multiple × Exit Yr EBITDA</t>
+        </is>
+      </c>
+      <c r="K117" s="16" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>DSRA Release</t>
+          <t>Exit Debt Payoff</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
@@ -5954,232 +5591,210 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>DSRA Ending at Exit</t>
+          <t>Ending Bal at Exit</t>
         </is>
       </c>
       <c r="K118" s="16">
-        <f>K86</f>
+        <f>K78</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
+          <t>DSRA Release</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>DSRA Ending at Exit</t>
+        </is>
+      </c>
+      <c r="K119" s="16">
+        <f>K86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
           <t>Exit Equity Proceeds</t>
         </is>
       </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>Exit EV - Debt + DSRA</t>
         </is>
       </c>
-      <c r="K119" s="7">
-        <f>K106-K107+K108</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="K120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121"/>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>EQUITY RETURNS</t>
         </is>
       </c>
-      <c r="B121" s="4" t="n"/>
-      <c r="C121" s="4" t="n"/>
-      <c r="D121" s="4" t="n"/>
-      <c r="E121" s="4" t="n"/>
-      <c r="F121" s="4" t="n"/>
-      <c r="G121" s="4" t="n"/>
-      <c r="H121" s="4" t="n"/>
-      <c r="I121" s="4" t="n"/>
-      <c r="J121" s="4" t="n"/>
-      <c r="K121" s="4" t="n"/>
-      <c r="L121" s="4" t="n"/>
-      <c r="M121" s="4" t="n"/>
-      <c r="N121" s="4" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Equity Cash Flow</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr"/>
-      <c r="D122" s="16">
-        <f>-D101</f>
-        <v/>
-      </c>
-      <c r="E122" s="16">
-        <f>E90</f>
-        <v/>
-      </c>
-      <c r="F122" s="16">
-        <f>F90</f>
-        <v/>
-      </c>
-      <c r="G122" s="16">
-        <f>G90</f>
-        <v/>
-      </c>
-      <c r="H122" s="16">
-        <f>H90</f>
-        <v/>
-      </c>
-      <c r="I122" s="16">
-        <f>I90</f>
-        <v/>
-      </c>
-      <c r="J122" s="16">
-        <f>J90</f>
-        <v/>
-      </c>
-      <c r="K122" s="16">
-        <f>K90+K109</f>
-        <v/>
-      </c>
-      <c r="L122" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M122" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N122" s="16">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="B122" s="4" t="n"/>
+      <c r="C122" s="4" t="n"/>
+      <c r="D122" s="4" t="n"/>
+      <c r="E122" s="4" t="n"/>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" s="4" t="n"/>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="n"/>
+      <c r="J122" s="4" t="n"/>
+      <c r="K122" s="4" t="n"/>
+      <c r="L122" s="4" t="n"/>
+      <c r="M122" s="4" t="n"/>
+      <c r="N122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
+          <t>Equity Cash Flow</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr"/>
-      <c r="D123" s="29">
-        <f>IRR(D112:K112)</f>
-        <v/>
-      </c>
+      <c r="D123" s="16" t="inlineStr"/>
+      <c r="E123" s="16" t="inlineStr"/>
+      <c r="F123" s="16" t="inlineStr"/>
+      <c r="G123" s="16" t="inlineStr"/>
+      <c r="H123" s="16" t="inlineStr"/>
+      <c r="I123" s="16" t="inlineStr"/>
+      <c r="J123" s="16" t="inlineStr"/>
+      <c r="K123" s="16" t="inlineStr"/>
+      <c r="L123" s="16" t="inlineStr"/>
+      <c r="M123" s="16" t="inlineStr"/>
+      <c r="N123" s="16" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr"/>
+      <c r="D124" s="29" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>Sum inflows / outflow</t>
         </is>
       </c>
-      <c r="D124" s="28">
-        <f>SUMIF(D112:K112,"&gt;0")/ABS(D112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="21" t="inlineStr">
+      <c r="D125" s="28" t="inlineStr"/>
+    </row>
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="21" t="inlineStr">
         <is>
           <t>Unlevered Returns (for reference)</t>
         </is>
       </c>
-      <c r="B126" s="6" t="inlineStr"/>
-      <c r="C126" s="6" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered Cash Flow</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B127" s="6" t="inlineStr"/>
       <c r="C127" s="6" t="inlineStr"/>
-      <c r="D127" s="16">
-        <f>-$D$17-D95</f>
-        <v/>
-      </c>
-      <c r="E127" s="16">
-        <f>E68</f>
-        <v/>
-      </c>
-      <c r="F127" s="16">
-        <f>F68</f>
-        <v/>
-      </c>
-      <c r="G127" s="16">
-        <f>G68</f>
-        <v/>
-      </c>
-      <c r="H127" s="16">
-        <f>H68</f>
-        <v/>
-      </c>
-      <c r="I127" s="16">
-        <f>I68</f>
-        <v/>
-      </c>
-      <c r="J127" s="16">
-        <f>J68</f>
-        <v/>
-      </c>
-      <c r="K127" s="16">
-        <f>K68+K106</f>
-        <v/>
-      </c>
-      <c r="L127" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M127" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N127" s="16">
-        <f>0</f>
-        <v/>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
+          <t>Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr"/>
+      <c r="D128" s="16">
+        <f>-$D$17-D95</f>
+        <v/>
+      </c>
+      <c r="E128" s="16">
+        <f>E68</f>
+        <v/>
+      </c>
+      <c r="F128" s="16">
+        <f>F68</f>
+        <v/>
+      </c>
+      <c r="G128" s="16">
+        <f>G68</f>
+        <v/>
+      </c>
+      <c r="H128" s="16">
+        <f>H68</f>
+        <v/>
+      </c>
+      <c r="I128" s="16">
+        <f>I68</f>
+        <v/>
+      </c>
+      <c r="J128" s="16">
+        <f>J68</f>
+        <v/>
+      </c>
+      <c r="K128" s="16">
+        <f>K68+K106</f>
+        <v/>
+      </c>
+      <c r="L128" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M128" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N128" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
           <t>Unlevered IRR</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr"/>
-      <c r="D128" s="29">
-        <f>IRR(D117:K117)</f>
-        <v/>
-      </c>
+      <c r="C129" s="6" t="inlineStr"/>
+      <c r="D129" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,14 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -154,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,6 +235,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3071,7 +3082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N129"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3153,21 +3164,45 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="53" t="inlineStr">
-        <is>
-          <t>═══ DRILL MODE: Key formulas blanked. Rebuild using Formula Logic hints in Column C. ═══</t>
-        </is>
-      </c>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE - Fill in yellow cells ═══</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>═══ AUDIT STRIP ═══</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Entry EV</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price for asset</t>
+        </is>
+      </c>
+      <c r="D3" s="7">
+        <f>$D$27</f>
+        <v/>
+      </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -3176,13 +3211,17 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
+      <c r="M3" s="54" t="inlineStr">
+        <is>
+          <t>IRR Sensitivity:</t>
+        </is>
+      </c>
       <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Entry EV</t>
+          <t>Y1 EBITDA</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3190,218 +3229,241 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
+      </c>
       <c r="D4" s="7">
-        <f>$D$17</f>
-        <v/>
+        <f>E72</f>
+        <v/>
+      </c>
+      <c r="M4" s="55" t="inlineStr">
+        <is>
+          <t>+/- 5% Entry → ~+/- 1% IRR</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Y1 EBITDA</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="M5" s="55" t="inlineStr">
+        <is>
+          <t>+/- 0.5x Exit → ~+/- 1.5% IRR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
-        <is>
-          <t>═══════════ CONTROL PANEL ═══════════</t>
-        </is>
-      </c>
+      <c r="A6" s="47" t="n"/>
       <c r="B6" s="47" t="n"/>
       <c r="C6" s="47" t="n"/>
       <c r="D6" s="47" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="n"/>
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
       <c r="B7" s="47" t="n"/>
       <c r="C7" s="47" t="n"/>
       <c r="D7" s="47" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Revenue Mode</t>
         </is>
       </c>
       <c r="B8" s="47" t="n"/>
-      <c r="C8" s="47" t="n"/>
-      <c r="D8" s="47" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Merchant / Contracted / Hybrid</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
-          <t>Revenue Mode</t>
+          <t>Contract End Year</t>
         </is>
       </c>
       <c r="B9" s="47" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D9" s="45" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t>Contract End Year</t>
-        </is>
-      </c>
+      <c r="A10" s="47" t="n"/>
       <c r="B10" s="47" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>0 = pure merchant; else year PPA ends</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" s="47" t="n"/>
+      <c r="D10" s="47" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="47" t="n"/>
+      <c r="A11" s="48" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
       <c r="B11" s="47" t="n"/>
       <c r="C11" s="47" t="n"/>
       <c r="D11" s="47" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
-        <is>
-          <t>TIMING</t>
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B12" s="47" t="n"/>
-      <c r="C12" s="47" t="n"/>
-      <c r="D12" s="47" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="32" t="inlineStr">
         <is>
-          <t>Exit Year</t>
+          <t>Tax Credit End Year</t>
         </is>
       </c>
       <c r="B13" s="47" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5 / 7 / 10</t>
+          <t>0 = N/A; else last year of PTC/ITC</t>
         </is>
       </c>
       <c r="D13" s="45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
-        <is>
-          <t>Tax Credit End Year</t>
-        </is>
-      </c>
+      <c r="A14" s="47" t="n"/>
       <c r="B14" s="47" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>0 = N/A; else last year of PTC/ITC</t>
-        </is>
-      </c>
-      <c r="D14" s="45" t="n">
-        <v>0</v>
-      </c>
+      <c r="C14" s="47" t="n"/>
+      <c r="D14" s="47" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="n"/>
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
       <c r="B15" s="47" t="n"/>
       <c r="C15" s="47" t="n"/>
-      <c r="D15" s="47" t="n"/>
+      <c r="D15" s="49" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
-        <is>
-          <t>DEBT</t>
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Debt Sweep</t>
         </is>
       </c>
       <c r="B16" s="47" t="n"/>
-      <c r="C16" s="47" t="n"/>
-      <c r="D16" s="49" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>Debt Sweep</t>
+          <t>Sweep %</t>
         </is>
       </c>
       <c r="B17" s="47" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>ON / OFF (for sweep assets)</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>ON</t>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>Sweep %</t>
-        </is>
-      </c>
+      <c r="A18" s="47" t="n"/>
       <c r="B18" s="47" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Active when Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D18" s="30" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
+      <c r="C18" s="47" t="n"/>
+      <c r="D18" s="50" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="47" t="n"/>
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
       <c r="B19" s="47" t="n"/>
       <c r="C19" s="47" t="n"/>
-      <c r="D19" s="50" t="n"/>
+      <c r="D19" s="51" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+      <c r="A20" s="52" t="inlineStr">
+        <is>
+          <t>Exit Method</t>
         </is>
       </c>
       <c r="B20" s="47" t="n"/>
-      <c r="C20" s="47" t="n"/>
-      <c r="D20" s="51" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Multiple / DCF</t>
+        </is>
+      </c>
+      <c r="D20" s="45" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="52" t="inlineStr">
-        <is>
-          <t>Exit Method</t>
-        </is>
-      </c>
-      <c r="B21" s="47" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Multiple / DCF</t>
-        </is>
-      </c>
-      <c r="D21" s="45" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="10">
+        <f>D103</f>
+        <v/>
       </c>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
@@ -3415,52 +3477,81 @@
       <c r="N21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Debt Payoff Y5</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
       <c r="D22" s="10">
-        <f>D103</f>
+        <f>IF(I78&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Debt Payoff Y5</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr"/>
+          <t>Min DSCR ≥ 1.25x</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
       <c r="D23" s="10">
-        <f>IF(I78&lt;1,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR ≥ 1.25x</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr"/>
-      <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="10" t="n"/>
     </row>
     <row r="25"/>
-    <row r="26"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TRANSACTION INPUTS</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>TRANSACTION INPUTS</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Entry EV</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
@@ -3475,93 +3566,108 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Entry EV</t>
+          <t>Transaction Fees</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Purchase price</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>85</v>
+          <t>Legal, advisory, financing</t>
+        </is>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Transaction Fees</t>
+          <t>Exit Multiple</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Legal, advisory, financing</t>
-        </is>
-      </c>
-      <c r="D29" s="30" t="n">
-        <v>0.015</v>
+          <t>Compressed for decline</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Exit Multiple</t>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Compressed for decline</t>
-        </is>
-      </c>
-      <c r="D30" s="31" t="n">
-        <v>6.5</v>
+          <t>Hold period</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Exit Year</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Hold period</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32"/>
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="14" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>VOLUME INPUTS</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+    </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>VOLUME INPUTS</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Y1 Volume</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>MMcf/d</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Daily throughput</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>80</v>
+      </c>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
@@ -3576,27 +3682,27 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Y1 Volume</t>
+          <t>Growth Rate Y1-Y5</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>MMcf/d</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Daily throughput</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>80</v>
+          <t>Drilling phase</t>
+        </is>
+      </c>
+      <c r="D34" s="30" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Growth Rate Y1-Y5</t>
+          <t>Decline Rate Y6-Y10</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -3606,43 +3712,58 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Drilling phase</t>
+          <t>Depletion phase</t>
         </is>
       </c>
       <c r="D35" s="30" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Decline Rate Y6-Y10</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>%/yr</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Depletion phase</t>
-        </is>
-      </c>
-      <c r="D36" s="30" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="37"/>
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="30" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>PRICING INPUTS</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+    </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>PRICING INPUTS</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Total Fee</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>$/Mcf</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Gathering + compression</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>0.55</v>
+      </c>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
@@ -3657,53 +3778,68 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Fee Escalation</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>$/Mcf</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Gathering + compression</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>0.55</v>
+          <t>Contract escalation</t>
+        </is>
+      </c>
+      <c r="D39" s="30" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Fee Escalation</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>%/yr</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Contract escalation</t>
-        </is>
-      </c>
-      <c r="D40" s="30" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="41"/>
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="30" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>COST INPUTS</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+    </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>COST INPUTS</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>O&amp;M Y1</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Operating costs</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>3.5</v>
+      </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
@@ -3718,73 +3854,88 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>O&amp;M Y1</t>
+          <t>O&amp;M Escalation</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Operating costs</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>3.5</v>
+          <t>Cost escalation</t>
+        </is>
+      </c>
+      <c r="D43" s="30" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>O&amp;M Escalation</t>
+          <t>Growth Capex Y1-Y5</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>%/yr</t>
+          <t>$mm/yr</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Cost escalation</t>
-        </is>
-      </c>
-      <c r="D44" s="30" t="n">
-        <v>0.025</v>
+          <t>Compression, looping</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Growth Capex Y1-Y5</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>$mm/yr</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Compression, looping</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46"/>
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>FINANCING INPUTS</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+    </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>FINANCING INPUTS</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Leverage</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Debt / Entry EV</t>
+        </is>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>0.3</v>
+      </c>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
@@ -3799,7 +3950,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Leverage</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -3809,123 +3960,138 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Debt / Entry EV</t>
+          <t>Higher (basin risk)</t>
         </is>
       </c>
       <c r="D48" s="30" t="n">
-        <v>0.3</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Debt Tenor</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Higher (basin risk)</t>
-        </is>
-      </c>
-      <c r="D49" s="30" t="n">
-        <v>0.07000000000000001</v>
+          <t>Short - pre-decline</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Debt Tenor</t>
+          <t>DSRA Months</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Short - pre-decline</t>
+          <t>Debt service reserve</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>DSRA Months</t>
+          <t>Cash Sweep %</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Debt service reserve</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>6</v>
+          <t>Aggressive paydown</t>
+        </is>
+      </c>
+      <c r="D51" s="30" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep %</t>
+          <t>Lock-up DSCR</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Distribution threshold</t>
+        </is>
+      </c>
+      <c r="D52" s="31" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="31" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TAX INPUTS</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Tax Rate</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Aggressive paydown</t>
-        </is>
-      </c>
-      <c r="D52" s="30" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Lock-up DSCR</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Distribution threshold</t>
-        </is>
-      </c>
-      <c r="D53" s="31" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>TAX INPUTS</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Blended federal + state</t>
+        </is>
+      </c>
+      <c r="D55" s="30" t="n">
+        <v>0.25</v>
+      </c>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
@@ -3940,7 +4106,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Tax Rate</t>
+          <t>Depreciable Basis</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -3950,63 +4116,79 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Blended federal + state</t>
+          <t>% of EV for depreciation</t>
         </is>
       </c>
       <c r="D56" s="30" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Depreciable Basis</t>
+          <t>Depreciation Life</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>% of EV for depreciation</t>
-        </is>
-      </c>
-      <c r="D57" s="30" t="n">
-        <v>0.8</v>
+          <t>Straight-line</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Depreciation Life</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Straight-line</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59"/>
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="14" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>CALCULATED ITEMS</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="4" t="n"/>
+    </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>CALCULATED ITEMS</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Debt Amount</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Entry EV × Leverage</t>
+        </is>
+      </c>
+      <c r="D60" s="16">
+        <f>$D$27*$D$47</f>
+        <v/>
+      </c>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
@@ -4021,7 +4203,7 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Debt Amount</t>
+          <t>Annual Depreciation</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -4031,250 +4213,279 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Entry EV × Leverage</t>
+          <t>EV × Basis / Life</t>
         </is>
       </c>
       <c r="D61" s="16">
-        <f>$D$17*$D$37</f>
+        <f>$D$27*$D$56/$D$57</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Annual Depreciation</t>
+          <t>Scheduled Principal</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>$mm/yr</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>EV × Basis / Life</t>
+          <t>Debt / Tenor</t>
         </is>
       </c>
       <c r="D62" s="16">
-        <f>$D$17*$D$46/$D$47</f>
+        <f>$D$60/$D$49</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Scheduled Principal</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>$mm/yr</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Debt / Tenor</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr"/>
-    </row>
-    <row r="64"/>
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="16" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING MODEL</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4" t="n"/>
+    </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING MODEL</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="4" t="n"/>
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Daily Volume</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>MMcf/d</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Growth then decline</t>
+        </is>
+      </c>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="n"/>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="n"/>
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="4" t="n"/>
-      <c r="N65" s="4" t="n"/>
+      <c r="E65" s="17">
+        <f>$D$33*(1+$D$34)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F65" s="17">
+        <f>$D$33*(1+$D$34)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G65" s="17">
+        <f>$D$33*(1+$D$34)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H65" s="17">
+        <f>$D$33*(1+$D$34)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I65" s="17">
+        <f>$D$33*(1+$D$34)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J65" s="17">
+        <f>$D$33*(1+$D$34)^4*(1-$D$35)^(6-5)</f>
+        <v/>
+      </c>
+      <c r="K65" s="17">
+        <f>$D$33*(1+$D$34)^4*(1-$D$35)^(7-5)</f>
+        <v/>
+      </c>
+      <c r="L65" s="17">
+        <f>$D$33*(1+$D$34)^4*(1-$D$35)^(8-5)</f>
+        <v/>
+      </c>
+      <c r="M65" s="17">
+        <f>$D$33*(1+$D$34)^4*(1-$D$35)^(9-5)</f>
+        <v/>
+      </c>
+      <c r="N65" s="17">
+        <f>$D$33*(1+$D$34)^4*(1-$D$35)^(10-5)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Daily Volume</t>
+          <t>Annual Volume</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>MMcf/d</t>
+          <t>Bcf</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Growth then decline</t>
+          <t>Daily × 365 / 1000</t>
         </is>
       </c>
       <c r="E66" s="17">
-        <f>$D$23*(1+$D$24)^(1-1)</f>
+        <f>E65*365</f>
         <v/>
       </c>
       <c r="F66" s="17">
-        <f>$D$23*(1+$D$24)^(2-1)</f>
+        <f>F65*365</f>
         <v/>
       </c>
       <c r="G66" s="17">
-        <f>$D$23*(1+$D$24)^(3-1)</f>
+        <f>G65*365</f>
         <v/>
       </c>
       <c r="H66" s="17">
-        <f>$D$23*(1+$D$24)^(4-1)</f>
+        <f>H65*365</f>
         <v/>
       </c>
       <c r="I66" s="17">
-        <f>$D$23*(1+$D$24)^(5-1)</f>
+        <f>I65*365</f>
         <v/>
       </c>
       <c r="J66" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(6-5)</f>
+        <f>J65*365</f>
         <v/>
       </c>
       <c r="K66" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(7-5)</f>
+        <f>K65*365</f>
         <v/>
       </c>
       <c r="L66" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(8-5)</f>
+        <f>L65*365</f>
         <v/>
       </c>
       <c r="M66" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(9-5)</f>
+        <f>M65*365</f>
         <v/>
       </c>
       <c r="N66" s="17">
-        <f>$D$23*(1+$D$24)^4*(1-$D$25)^(10-5)</f>
+        <f>N65*365</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Annual Volume</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Bcf</t>
+          <t>$/Mcf</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Daily × 365 / 1000</t>
-        </is>
-      </c>
-      <c r="E67" s="17">
-        <f>E55*365/1000</f>
-        <v/>
-      </c>
-      <c r="F67" s="17">
-        <f>F55*365/1000</f>
-        <v/>
-      </c>
-      <c r="G67" s="17">
-        <f>G55*365/1000</f>
-        <v/>
-      </c>
-      <c r="H67" s="17">
-        <f>H55*365/1000</f>
-        <v/>
-      </c>
-      <c r="I67" s="17">
-        <f>I55*365/1000</f>
-        <v/>
-      </c>
-      <c r="J67" s="17">
-        <f>J55*365/1000</f>
-        <v/>
-      </c>
-      <c r="K67" s="17">
-        <f>K55*365/1000</f>
-        <v/>
-      </c>
-      <c r="L67" s="17">
-        <f>L55*365/1000</f>
-        <v/>
-      </c>
-      <c r="M67" s="17">
-        <f>M55*365/1000</f>
-        <v/>
-      </c>
-      <c r="N67" s="17">
-        <f>N55*365/1000</f>
+          <t>Escalated</t>
+        </is>
+      </c>
+      <c r="E67" s="18">
+        <f>$D$38*(1+$D$39)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F67" s="18">
+        <f>$D$38*(1+$D$39)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G67" s="18">
+        <f>$D$38*(1+$D$39)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H67" s="18">
+        <f>$D$38*(1+$D$39)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I67" s="18">
+        <f>$D$38*(1+$D$39)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J67" s="18">
+        <f>$D$38*(1+$D$39)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K67" s="18">
+        <f>$D$38*(1+$D$39)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L67" s="18">
+        <f>$D$38*(1+$D$39)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M67" s="18">
+        <f>$D$38*(1+$D$39)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N67" s="18">
+        <f>$D$38*(1+$D$39)^(10-1)</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>$/Mcf</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Escalated</t>
-        </is>
-      </c>
-      <c r="E68" s="18">
-        <f>$D$28*(1+$D$29)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F68" s="18">
-        <f>$D$28*(1+$D$29)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G68" s="18">
-        <f>$D$28*(1+$D$29)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H68" s="18">
-        <f>$D$28*(1+$D$29)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I68" s="18">
-        <f>$D$28*(1+$D$29)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J68" s="18">
-        <f>$D$28*(1+$D$29)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K68" s="18">
-        <f>$D$28*(1+$D$29)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L68" s="18">
-        <f>$D$28*(1+$D$29)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M68" s="18">
-        <f>$D$28*(1+$D$29)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N68" s="18">
-        <f>$D$28*(1+$D$29)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69"/>
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="18" t="n"/>
+      <c r="H68" s="18" t="n"/>
+      <c r="I68" s="18" t="n"/>
+      <c r="J68" s="18" t="n"/>
+      <c r="K68" s="18" t="n"/>
+      <c r="L68" s="18" t="n"/>
+      <c r="M68" s="18" t="n"/>
+      <c r="N68" s="18" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Volume(Bcf) × Fee × 1000</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="n"/>
+      <c r="F69" s="16" t="n"/>
+      <c r="G69" s="16" t="n"/>
+      <c r="H69" s="16" t="n"/>
+      <c r="I69" s="16" t="n"/>
+      <c r="J69" s="16" t="n"/>
+      <c r="K69" s="16" t="n"/>
+      <c r="L69" s="16" t="n"/>
+      <c r="M69" s="16" t="n"/>
+      <c r="N69" s="16" t="n"/>
+    </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>O&amp;M Cost</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4284,126 +4495,129 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Volume(Bcf) × Fee × 1000</t>
-        </is>
-      </c>
-      <c r="E70" s="16" t="inlineStr"/>
-      <c r="F70" s="16" t="inlineStr"/>
-      <c r="G70" s="16" t="inlineStr"/>
-      <c r="H70" s="16" t="inlineStr"/>
-      <c r="I70" s="16" t="inlineStr"/>
-      <c r="J70" s="16" t="inlineStr"/>
-      <c r="K70" s="16" t="inlineStr"/>
-      <c r="L70" s="16" t="inlineStr"/>
-      <c r="M70" s="16" t="inlineStr"/>
-      <c r="N70" s="16" t="inlineStr"/>
+          <t>Escalated</t>
+        </is>
+      </c>
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="16" t="n"/>
+      <c r="G70" s="16" t="n"/>
+      <c r="H70" s="16" t="n"/>
+      <c r="I70" s="16" t="n"/>
+      <c r="J70" s="16" t="n"/>
+      <c r="K70" s="16" t="n"/>
+      <c r="L70" s="16" t="n"/>
+      <c r="M70" s="16" t="n"/>
+      <c r="N70" s="16" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>O&amp;M Cost</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="E71" s="16" t="n"/>
+      <c r="F71" s="16" t="n"/>
+      <c r="G71" s="16" t="n"/>
+      <c r="H71" s="16" t="n"/>
+      <c r="I71" s="16" t="n"/>
+      <c r="J71" s="16" t="n"/>
+      <c r="K71" s="16" t="n"/>
+      <c r="L71" s="16" t="n"/>
+      <c r="M71" s="16" t="n"/>
+      <c r="N71" s="16" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Escalated</t>
-        </is>
-      </c>
-      <c r="E71" s="16">
-        <f>$D$32*(1+$D$33)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F71" s="16">
-        <f>$D$32*(1+$D$33)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G71" s="16">
-        <f>$D$32*(1+$D$33)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H71" s="16">
-        <f>$D$32*(1+$D$33)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I71" s="16">
-        <f>$D$32*(1+$D$33)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J71" s="16">
-        <f>$D$32*(1+$D$33)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K71" s="16">
-        <f>$D$32*(1+$D$33)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L71" s="16">
-        <f>$D$32*(1+$D$33)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M71" s="16">
-        <f>$D$32*(1+$D$33)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N71" s="16">
-        <f>$D$32*(1+$D$33)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72"/>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="7" t="n"/>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="7" t="n"/>
+      <c r="I72" s="7" t="n"/>
+      <c r="J72" s="7" t="n"/>
+      <c r="K72" s="7" t="n"/>
+      <c r="L72" s="7" t="n"/>
+      <c r="M72" s="7" t="n"/>
+      <c r="N72" s="7" t="n"/>
+    </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="A73" s="5" t="n"/>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="7" t="n"/>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+      <c r="J73" s="7" t="n"/>
+      <c r="K73" s="7" t="n"/>
+      <c r="L73" s="7" t="n"/>
+      <c r="M73" s="7" t="n"/>
+      <c r="N73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>CASH FLOW</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n"/>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="n"/>
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr"/>
-      <c r="E73" s="7" t="inlineStr"/>
-      <c r="F73" s="7" t="inlineStr"/>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="7" t="inlineStr"/>
-      <c r="I73" s="7" t="inlineStr"/>
-      <c r="J73" s="7" t="inlineStr"/>
-      <c r="K73" s="7" t="inlineStr"/>
-      <c r="L73" s="7" t="inlineStr"/>
-      <c r="M73" s="7" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr"/>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>CASH FLOW</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="n"/>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA - Depreciation</t>
+        </is>
+      </c>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="n"/>
-      <c r="J75" s="4" t="n"/>
-      <c r="K75" s="4" t="n"/>
-      <c r="L75" s="4" t="n"/>
-      <c r="M75" s="4" t="n"/>
-      <c r="N75" s="4" t="n"/>
+      <c r="E75" s="16" t="n"/>
+      <c r="F75" s="16" t="n"/>
+      <c r="G75" s="16" t="n"/>
+      <c r="H75" s="16" t="n"/>
+      <c r="I75" s="16" t="n"/>
+      <c r="J75" s="16" t="n"/>
+      <c r="K75" s="16" t="n"/>
+      <c r="L75" s="16" t="n"/>
+      <c r="M75" s="16" t="n"/>
+      <c r="N75" s="16" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -4413,24 +4627,54 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>EBITDA - Depreciation</t>
-        </is>
-      </c>
-      <c r="E76" s="16" t="inlineStr"/>
-      <c r="F76" s="16" t="inlineStr"/>
-      <c r="G76" s="16" t="inlineStr"/>
-      <c r="H76" s="16" t="inlineStr"/>
-      <c r="I76" s="16" t="inlineStr"/>
-      <c r="J76" s="16" t="inlineStr"/>
-      <c r="K76" s="16" t="inlineStr"/>
-      <c r="L76" s="16" t="inlineStr"/>
-      <c r="M76" s="16" t="inlineStr"/>
-      <c r="N76" s="16" t="inlineStr"/>
+          <t>MAX(0, EBIT) × Tax Rate</t>
+        </is>
+      </c>
+      <c r="E76" s="16">
+        <f>IF(1&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="F76" s="16">
+        <f>IF(2&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="G76" s="16">
+        <f>IF(3&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="H76" s="16">
+        <f>IF(4&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="I76" s="16">
+        <f>IF(5&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="J76" s="16">
+        <f>IF(6&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="K76" s="16">
+        <f>IF(7&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="L76" s="16">
+        <f>IF(8&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="M76" s="16">
+        <f>IF(9&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="N76" s="16">
+        <f>IF(10&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Growth Capex</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -4440,24 +4684,24 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, EBIT) × Tax Rate</t>
-        </is>
-      </c>
-      <c r="E77" s="16" t="inlineStr"/>
-      <c r="F77" s="16" t="inlineStr"/>
-      <c r="G77" s="16" t="inlineStr"/>
-      <c r="H77" s="16" t="inlineStr"/>
-      <c r="I77" s="16" t="inlineStr"/>
-      <c r="J77" s="16" t="inlineStr"/>
-      <c r="K77" s="16" t="inlineStr"/>
-      <c r="L77" s="16" t="inlineStr"/>
-      <c r="M77" s="16" t="inlineStr"/>
-      <c r="N77" s="16" t="inlineStr"/>
+          <t>Y1-Y5 only</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="7" t="n"/>
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
+      <c r="J77" s="7" t="n"/>
+      <c r="K77" s="7" t="n"/>
+      <c r="L77" s="7" t="n"/>
+      <c r="M77" s="7" t="n"/>
+      <c r="N77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Growth Capex</t>
+          <t>CFADS</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -4467,102 +4711,115 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Y1-Y5 only</t>
-        </is>
-      </c>
-      <c r="E78" s="19">
-        <f>IF(1&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="F78" s="19">
-        <f>IF(2&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="G78" s="19">
-        <f>IF(3&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="H78" s="19">
-        <f>IF(4&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="I78" s="19">
-        <f>IF(5&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="J78" s="19">
-        <f>IF(6&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="K78" s="19">
-        <f>IF(7&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="L78" s="19">
-        <f>IF(8&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="M78" s="19">
-        <f>IF(9&lt;=5,$D$34,0)</f>
-        <v/>
-      </c>
-      <c r="N78" s="19">
-        <f>IF(10&lt;=5,$D$34,0)</f>
+          <t>EBITDA - Taxes - Capex</t>
+        </is>
+      </c>
+      <c r="E78" s="7">
+        <f>E62-E66-E67</f>
+        <v/>
+      </c>
+      <c r="F78" s="7">
+        <f>F62-F66-F67</f>
+        <v/>
+      </c>
+      <c r="G78" s="7">
+        <f>G62-G66-G67</f>
+        <v/>
+      </c>
+      <c r="H78" s="7">
+        <f>H62-H66-H67</f>
+        <v/>
+      </c>
+      <c r="I78" s="7">
+        <f>I62-I66-I67</f>
+        <v/>
+      </c>
+      <c r="J78" s="7">
+        <f>J62-J66-J67</f>
+        <v/>
+      </c>
+      <c r="K78" s="7">
+        <f>K62-K66-K67</f>
+        <v/>
+      </c>
+      <c r="L78" s="7">
+        <f>L62-L66-L67</f>
+        <v/>
+      </c>
+      <c r="M78" s="7">
+        <f>M62-M66-M67</f>
+        <v/>
+      </c>
+      <c r="N78" s="7">
+        <f>N62-N66-N67</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>CFADS</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="7" t="n"/>
+      <c r="G79" s="7" t="n"/>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="7" t="n"/>
+      <c r="K79" s="7" t="n"/>
+      <c r="L79" s="7" t="n"/>
+      <c r="M79" s="7" t="n"/>
+      <c r="N79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>DEBT SCHEDULE (75% Sweep, 5-Year Tenor)</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="n"/>
+      <c r="H80" s="4" t="n"/>
+      <c r="I80" s="4" t="n"/>
+      <c r="J80" s="4" t="n"/>
+      <c r="K80" s="4" t="n"/>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA - Taxes - Capex</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr"/>
-      <c r="F79" s="7" t="inlineStr"/>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
-      <c r="I79" s="7" t="inlineStr"/>
-      <c r="J79" s="7" t="inlineStr"/>
-      <c r="K79" s="7" t="inlineStr"/>
-      <c r="L79" s="7" t="inlineStr"/>
-      <c r="M79" s="7" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
-    </row>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>DEBT SCHEDULE (75% Sweep, 5-Year Tenor)</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="n"/>
-      <c r="C81" s="4" t="n"/>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
-      <c r="J81" s="4" t="n"/>
-      <c r="K81" s="4" t="n"/>
-      <c r="L81" s="4" t="n"/>
-      <c r="M81" s="4" t="n"/>
-      <c r="N81" s="4" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="16" t="n"/>
+      <c r="F81" s="16" t="n"/>
+      <c r="G81" s="16" t="n"/>
+      <c r="H81" s="16" t="n"/>
+      <c r="I81" s="16" t="n"/>
+      <c r="J81" s="16" t="n"/>
+      <c r="K81" s="16" t="n"/>
+      <c r="L81" s="16" t="n"/>
+      <c r="M81" s="16" t="n"/>
+      <c r="N81" s="16" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Beginning Balance</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -4570,52 +4827,26 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr"/>
-      <c r="E82" s="16">
-        <f>$D$50</f>
-        <v/>
-      </c>
-      <c r="F82" s="16">
-        <f>E78</f>
-        <v/>
-      </c>
-      <c r="G82" s="16">
-        <f>F78</f>
-        <v/>
-      </c>
-      <c r="H82" s="16">
-        <f>G78</f>
-        <v/>
-      </c>
-      <c r="I82" s="16">
-        <f>H78</f>
-        <v/>
-      </c>
-      <c r="J82" s="16">
-        <f>I78</f>
-        <v/>
-      </c>
-      <c r="K82" s="16">
-        <f>J78</f>
-        <v/>
-      </c>
-      <c r="L82" s="16">
-        <f>K78</f>
-        <v/>
-      </c>
-      <c r="M82" s="16">
-        <f>L78</f>
-        <v/>
-      </c>
-      <c r="N82" s="16">
-        <f>M78</f>
-        <v/>
-      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Beg Bal × Int Rate</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="n"/>
+      <c r="F82" s="16" t="n"/>
+      <c r="G82" s="16" t="n"/>
+      <c r="H82" s="16" t="n"/>
+      <c r="I82" s="16" t="n"/>
+      <c r="J82" s="16" t="n"/>
+      <c r="K82" s="16" t="n"/>
+      <c r="L82" s="16" t="n"/>
+      <c r="M82" s="16" t="n"/>
+      <c r="N82" s="16" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Scheduled Principal</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -4625,24 +4856,24 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Beg Bal × Int Rate</t>
-        </is>
-      </c>
-      <c r="E83" s="16" t="inlineStr"/>
-      <c r="F83" s="16" t="inlineStr"/>
-      <c r="G83" s="16" t="inlineStr"/>
-      <c r="H83" s="16" t="inlineStr"/>
-      <c r="I83" s="16" t="inlineStr"/>
-      <c r="J83" s="16" t="inlineStr"/>
-      <c r="K83" s="16" t="inlineStr"/>
-      <c r="L83" s="16" t="inlineStr"/>
-      <c r="M83" s="16" t="inlineStr"/>
-      <c r="N83" s="16" t="inlineStr"/>
+          <t>MIN(Sched, Beg Bal)</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="n"/>
+      <c r="F83" s="16" t="n"/>
+      <c r="G83" s="16" t="n"/>
+      <c r="H83" s="16" t="n"/>
+      <c r="I83" s="16" t="n"/>
+      <c r="J83" s="16" t="n"/>
+      <c r="K83" s="16" t="n"/>
+      <c r="L83" s="16" t="n"/>
+      <c r="M83" s="16" t="n"/>
+      <c r="N83" s="16" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Scheduled Principal</t>
+          <t>Debt Service (Pre-Sweep)</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -4652,24 +4883,24 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>MIN(Sched, Beg Bal)</t>
-        </is>
-      </c>
-      <c r="E84" s="16" t="inlineStr"/>
-      <c r="F84" s="16" t="inlineStr"/>
-      <c r="G84" s="16" t="inlineStr"/>
-      <c r="H84" s="16" t="inlineStr"/>
-      <c r="I84" s="16" t="inlineStr"/>
-      <c r="J84" s="16" t="inlineStr"/>
-      <c r="K84" s="16" t="inlineStr"/>
-      <c r="L84" s="16" t="inlineStr"/>
-      <c r="M84" s="16" t="inlineStr"/>
-      <c r="N84" s="16" t="inlineStr"/>
+          <t>Interest + Sched Prin</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="n"/>
+      <c r="F84" s="16" t="n"/>
+      <c r="G84" s="16" t="n"/>
+      <c r="H84" s="16" t="n"/>
+      <c r="I84" s="16" t="n"/>
+      <c r="J84" s="16" t="n"/>
+      <c r="K84" s="16" t="n"/>
+      <c r="L84" s="16" t="n"/>
+      <c r="M84" s="16" t="n"/>
+      <c r="N84" s="16" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Debt Service (Pre-Sweep)</t>
+          <t>Excess Cash</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
@@ -4679,54 +4910,54 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Interest + Sched Prin</t>
+          <t>CFADS - DS - DSRA Funding</t>
         </is>
       </c>
       <c r="E85" s="16">
-        <f>E72+E73</f>
+        <f>MAX(0,E77-E84-E96)</f>
         <v/>
       </c>
       <c r="F85" s="16">
-        <f>F72+F73</f>
+        <f>MAX(0,F77-F84-F96)</f>
         <v/>
       </c>
       <c r="G85" s="16">
-        <f>G72+G73</f>
+        <f>MAX(0,G77-G84-G96)</f>
         <v/>
       </c>
       <c r="H85" s="16">
-        <f>H72+H73</f>
+        <f>MAX(0,H77-H84-H96)</f>
         <v/>
       </c>
       <c r="I85" s="16">
-        <f>I72+I73</f>
+        <f>MAX(0,I77-I84-I96)</f>
         <v/>
       </c>
       <c r="J85" s="16">
-        <f>J72+J73</f>
+        <f>MAX(0,J77-J84-J96)</f>
         <v/>
       </c>
       <c r="K85" s="16">
-        <f>K72+K73</f>
+        <f>MAX(0,K77-K84-K96)</f>
         <v/>
       </c>
       <c r="L85" s="16">
-        <f>L72+L73</f>
+        <f>MAX(0,L77-L84-L96)</f>
         <v/>
       </c>
       <c r="M85" s="16">
-        <f>M72+M73</f>
+        <f>MAX(0,M77-M84-M96)</f>
         <v/>
       </c>
       <c r="N85" s="16">
-        <f>N72+N73</f>
+        <f>MAX(0,N77-N84-N96)</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Excess Cash</t>
+          <t>Cash Sweep</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -4736,54 +4967,24 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>CFADS - DS - DSRA Funding</t>
-        </is>
-      </c>
-      <c r="E86" s="16">
-        <f>MAX(0,E68-E74-E85)</f>
-        <v/>
-      </c>
-      <c r="F86" s="16">
-        <f>MAX(0,F68-F74-F85)</f>
-        <v/>
-      </c>
-      <c r="G86" s="16">
-        <f>MAX(0,G68-G74-G85)</f>
-        <v/>
-      </c>
-      <c r="H86" s="16">
-        <f>MAX(0,H68-H74-H85)</f>
-        <v/>
-      </c>
-      <c r="I86" s="16">
-        <f>MAX(0,I68-I74-I85)</f>
-        <v/>
-      </c>
-      <c r="J86" s="16">
-        <f>MAX(0,J68-J74-J85)</f>
-        <v/>
-      </c>
-      <c r="K86" s="16">
-        <f>MAX(0,K68-K74-K85)</f>
-        <v/>
-      </c>
-      <c r="L86" s="16">
-        <f>MAX(0,L68-L74-L85)</f>
-        <v/>
-      </c>
-      <c r="M86" s="16">
-        <f>MAX(0,M68-M74-M85)</f>
-        <v/>
-      </c>
-      <c r="N86" s="16">
-        <f>MAX(0,N68-N74-N85)</f>
-        <v/>
-      </c>
+          <t>MIN(Excess×75%, Beg-Sched)</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="n"/>
+      <c r="F86" s="19" t="n"/>
+      <c r="G86" s="19" t="n"/>
+      <c r="H86" s="19" t="n"/>
+      <c r="I86" s="19" t="n"/>
+      <c r="J86" s="19" t="n"/>
+      <c r="K86" s="19" t="n"/>
+      <c r="L86" s="19" t="n"/>
+      <c r="M86" s="19" t="n"/>
+      <c r="N86" s="19" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep</t>
+          <t>Total Principal</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
@@ -4793,24 +4994,24 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>MIN(Excess×75%, Beg-Sched)</t>
-        </is>
-      </c>
-      <c r="E87" s="19" t="inlineStr"/>
-      <c r="F87" s="19" t="inlineStr"/>
-      <c r="G87" s="19" t="inlineStr"/>
-      <c r="H87" s="19" t="inlineStr"/>
-      <c r="I87" s="19" t="inlineStr"/>
-      <c r="J87" s="19" t="inlineStr"/>
-      <c r="K87" s="19" t="inlineStr"/>
-      <c r="L87" s="19" t="inlineStr"/>
-      <c r="M87" s="19" t="inlineStr"/>
-      <c r="N87" s="19" t="inlineStr"/>
+          <t>Scheduled + Sweep</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="n"/>
+      <c r="F87" s="16" t="n"/>
+      <c r="G87" s="16" t="n"/>
+      <c r="H87" s="16" t="n"/>
+      <c r="I87" s="16" t="n"/>
+      <c r="J87" s="16" t="n"/>
+      <c r="K87" s="16" t="n"/>
+      <c r="L87" s="16" t="n"/>
+      <c r="M87" s="16" t="n"/>
+      <c r="N87" s="16" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Total Principal</t>
+          <t>Ending Balance</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
@@ -4820,156 +5021,208 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Scheduled + Sweep</t>
-        </is>
-      </c>
-      <c r="E88" s="16" t="inlineStr"/>
-      <c r="F88" s="16" t="inlineStr"/>
-      <c r="G88" s="16" t="inlineStr"/>
-      <c r="H88" s="16" t="inlineStr"/>
-      <c r="I88" s="16" t="inlineStr"/>
-      <c r="J88" s="16" t="inlineStr"/>
-      <c r="K88" s="16" t="inlineStr"/>
-      <c r="L88" s="16" t="inlineStr"/>
-      <c r="M88" s="16" t="inlineStr"/>
-      <c r="N88" s="16" t="inlineStr"/>
+          <t>MAX(0, Beg - Total Prin)</t>
+        </is>
+      </c>
+      <c r="D88">
+        <f>$D$60</f>
+        <v/>
+      </c>
+      <c r="E88" s="16" t="n"/>
+      <c r="F88" s="16" t="n"/>
+      <c r="G88" s="16" t="n"/>
+      <c r="H88" s="16" t="n"/>
+      <c r="I88" s="16" t="n"/>
+      <c r="J88" s="16" t="n"/>
+      <c r="K88" s="16" t="n"/>
+      <c r="L88" s="16" t="n"/>
+      <c r="M88" s="16" t="n"/>
+      <c r="N88" s="16" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Ending Balance</t>
+          <t>DSCR</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, Beg - Total Prin)</t>
-        </is>
-      </c>
-      <c r="E89" s="16" t="inlineStr"/>
-      <c r="F89" s="16" t="inlineStr"/>
-      <c r="G89" s="16" t="inlineStr"/>
-      <c r="H89" s="16" t="inlineStr"/>
-      <c r="I89" s="16" t="inlineStr"/>
-      <c r="J89" s="16" t="inlineStr"/>
-      <c r="K89" s="16" t="inlineStr"/>
-      <c r="L89" s="16" t="inlineStr"/>
-      <c r="M89" s="16" t="inlineStr"/>
-      <c r="N89" s="16" t="inlineStr"/>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
+      <c r="E89" s="28" t="n"/>
+      <c r="F89" s="28" t="n"/>
+      <c r="G89" s="28" t="n"/>
+      <c r="H89" s="28" t="n"/>
+      <c r="I89" s="28" t="n"/>
+      <c r="J89" s="28" t="n"/>
+      <c r="K89" s="28" t="n"/>
+      <c r="L89" s="28" t="n"/>
+      <c r="M89" s="28" t="n"/>
+      <c r="N89" s="28" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>DSCR</t>
+          <t>Scheduled DS (for DSRA)</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="E90" s="28" t="inlineStr"/>
-      <c r="F90" s="28" t="inlineStr"/>
-      <c r="G90" s="28" t="inlineStr"/>
-      <c r="H90" s="28" t="inlineStr"/>
-      <c r="I90" s="28" t="inlineStr"/>
-      <c r="J90" s="28" t="inlineStr"/>
-      <c r="K90" s="28" t="inlineStr"/>
-      <c r="L90" s="28" t="inlineStr"/>
-      <c r="M90" s="28" t="inlineStr"/>
-      <c r="N90" s="28" t="inlineStr"/>
+          <t>Based on straight-line amort, no sweep</t>
+        </is>
+      </c>
+      <c r="E90" s="16">
+        <f>MAX(0,$D$60-(1-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
+      <c r="F90" s="16">
+        <f>MAX(0,$D$60-(2-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
+      <c r="G90" s="16">
+        <f>MAX(0,$D$60-(3-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
+      <c r="H90" s="16">
+        <f>MAX(0,$D$60-(4-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
+      <c r="I90" s="16">
+        <f>MAX(0,$D$60-(5-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
+      <c r="J90" s="16">
+        <f>MAX(0,$D$60-(6-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
+      <c r="K90" s="16">
+        <f>MAX(0,$D$60-(7-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
+      <c r="L90" s="16">
+        <f>MAX(0,$D$60-(8-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
+      <c r="M90" s="16">
+        <f>MAX(0,$D$60-(9-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
+      <c r="N90" s="16">
+        <f>MAX(0,$D$60-(10-1)*$D$62)*$D$48+$D$62</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>Scheduled DS (for DSRA)</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="E91" s="16" t="n"/>
+      <c r="F91" s="16" t="n"/>
+      <c r="G91" s="16" t="n"/>
+      <c r="H91" s="16" t="n"/>
+      <c r="I91" s="16" t="n"/>
+      <c r="J91" s="16" t="n"/>
+      <c r="K91" s="16" t="n"/>
+      <c r="L91" s="16" t="n"/>
+      <c r="M91" s="16" t="n"/>
+      <c r="N91" s="16" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>DSRA (Debt Service Reserve Account)</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="n"/>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="4" t="n"/>
+      <c r="H92" s="4" t="n"/>
+      <c r="I92" s="4" t="n"/>
+      <c r="J92" s="4" t="n"/>
+      <c r="K92" s="4" t="n"/>
+      <c r="L92" s="4" t="n"/>
+      <c r="M92" s="4" t="n"/>
+      <c r="N92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>DSRA Target</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>Based on straight-line amort, no sweep</t>
-        </is>
-      </c>
-      <c r="E91" s="16">
-        <f>MAX(0,$D$50-(1-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-      <c r="F91" s="16">
-        <f>MAX(0,$D$50-(2-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-      <c r="G91" s="16">
-        <f>MAX(0,$D$50-(3-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-      <c r="H91" s="16">
-        <f>MAX(0,$D$50-(4-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-      <c r="I91" s="16">
-        <f>MAX(0,$D$50-(5-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-      <c r="J91" s="16">
-        <f>MAX(0,$D$50-(6-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-      <c r="K91" s="16">
-        <f>MAX(0,$D$50-(7-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-      <c r="L91" s="16">
-        <f>MAX(0,$D$50-(8-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-      <c r="M91" s="16">
-        <f>MAX(0,$D$50-(9-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-      <c r="N91" s="16">
-        <f>MAX(0,$D$50-(10-1)*$D$52)*$D$38+$D$52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92"/>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>DSRA (Debt Service Reserve Account)</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="n"/>
-      <c r="C93" s="4" t="n"/>
-      <c r="D93" s="4" t="n"/>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="4" t="n"/>
-      <c r="G93" s="4" t="n"/>
-      <c r="H93" s="4" t="n"/>
-      <c r="I93" s="4" t="n"/>
-      <c r="J93" s="4" t="n"/>
-      <c r="K93" s="4" t="n"/>
-      <c r="L93" s="4" t="n"/>
-      <c r="M93" s="4" t="n"/>
-      <c r="N93" s="4" t="n"/>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
+        </is>
+      </c>
+      <c r="D93" s="16">
+        <f>E80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="E93" s="16">
+        <f>F80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="F93" s="16">
+        <f>G80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="G93" s="16">
+        <f>H80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="H93" s="16">
+        <f>I80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="I93" s="16">
+        <f>J80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="J93" s="16">
+        <f>K80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="K93" s="16">
+        <f>L80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="L93" s="16">
+        <f>M80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="M93" s="16">
+        <f>N80*$D$40/12</f>
+        <v/>
+      </c>
+      <c r="N93" s="16">
+        <f>0</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>DSRA Target</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
@@ -4977,60 +5230,55 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
-        </is>
-      </c>
+      <c r="C94" s="6" t="n"/>
       <c r="D94" s="16">
-        <f>E80*$D$40/12</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E94" s="16">
-        <f>F80*$D$40/12</f>
+        <f>F90*$D$50/12</f>
         <v/>
       </c>
       <c r="F94" s="16">
-        <f>G80*$D$40/12</f>
+        <f>G90*$D$50/12</f>
         <v/>
       </c>
       <c r="G94" s="16">
-        <f>H80*$D$40/12</f>
+        <f>H90*$D$50/12</f>
         <v/>
       </c>
       <c r="H94" s="16">
-        <f>I80*$D$40/12</f>
+        <f>I90*$D$50/12</f>
         <v/>
       </c>
       <c r="I94" s="16">
-        <f>J80*$D$40/12</f>
+        <f>J90*$D$50/12</f>
         <v/>
       </c>
       <c r="J94" s="16">
-        <f>K80*$D$40/12</f>
+        <f>K90*$D$50/12</f>
         <v/>
       </c>
       <c r="K94" s="16">
-        <f>L80*$D$40/12</f>
+        <f>L90*$D$50/12</f>
         <v/>
       </c>
       <c r="L94" s="16">
-        <f>M80*$D$40/12</f>
+        <f>M90*$D$50/12</f>
         <v/>
       </c>
       <c r="M94" s="16">
-        <f>N80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="N94" s="16">
-        <f>0</f>
-        <v/>
+        <f>N90*$D$50/12</f>
+        <v/>
+      </c>
+      <c r="N94" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Funding/(Release)</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
@@ -5038,56 +5286,59 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr"/>
-      <c r="D95" s="16">
-        <f>0</f>
-        <v/>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
+      <c r="D95" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="E95" s="16">
-        <f>D86</f>
+        <f>D108</f>
         <v/>
       </c>
       <c r="F95" s="16">
-        <f>E86</f>
+        <f>E97</f>
         <v/>
       </c>
       <c r="G95" s="16">
-        <f>F86</f>
+        <f>F97</f>
         <v/>
       </c>
       <c r="H95" s="16">
-        <f>G86</f>
+        <f>G97</f>
         <v/>
       </c>
       <c r="I95" s="16">
-        <f>H86</f>
+        <f>H97</f>
         <v/>
       </c>
       <c r="J95" s="16">
-        <f>I86</f>
+        <f>I97</f>
         <v/>
       </c>
       <c r="K95" s="16">
-        <f>J86</f>
+        <f>J97</f>
         <v/>
       </c>
       <c r="L95" s="16">
-        <f>K86</f>
+        <f>K97</f>
         <v/>
       </c>
       <c r="M95" s="16">
-        <f>L86</f>
+        <f>L97</f>
         <v/>
       </c>
       <c r="N95" s="16">
-        <f>M86</f>
+        <f>M97</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Ending</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -5097,281 +5348,375 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Target - Beginning</t>
+          <t>Beginning + Funding</t>
         </is>
       </c>
       <c r="D96" s="16">
-        <f>D83-D84</f>
+        <f>D84+D85</f>
         <v/>
       </c>
       <c r="E96" s="16">
-        <f>E83-E84</f>
+        <f>E94-E95</f>
         <v/>
       </c>
       <c r="F96" s="16">
-        <f>F83-F84</f>
+        <f>F94-F95</f>
         <v/>
       </c>
       <c r="G96" s="16">
-        <f>G83-G84</f>
+        <f>G94-G95</f>
         <v/>
       </c>
       <c r="H96" s="16">
-        <f>H83-H84</f>
+        <f>H94-H95</f>
         <v/>
       </c>
       <c r="I96" s="16">
-        <f>I83-I84</f>
+        <f>I94-I95</f>
         <v/>
       </c>
       <c r="J96" s="16">
-        <f>J83-J84</f>
+        <f>J94-J95</f>
         <v/>
       </c>
       <c r="K96" s="16">
-        <f>K83-K84</f>
+        <f>K94-K95</f>
         <v/>
       </c>
       <c r="L96" s="16">
-        <f>L83-L84</f>
+        <f>L94-L95</f>
         <v/>
       </c>
       <c r="M96" s="16">
-        <f>M83-M84</f>
+        <f>M94-M95</f>
         <v/>
       </c>
       <c r="N96" s="16">
-        <f>N83-N84</f>
+        <f>N94-N95</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Ending</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTION WATERFALL</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4">
+        <f>E95+E96</f>
+        <v/>
+      </c>
+      <c r="F97" s="4">
+        <f>F95+F96</f>
+        <v/>
+      </c>
+      <c r="G97" s="4">
+        <f>G95+G96</f>
+        <v/>
+      </c>
+      <c r="H97" s="4">
+        <f>H95+H96</f>
+        <v/>
+      </c>
+      <c r="I97" s="4">
+        <f>I95+I96</f>
+        <v/>
+      </c>
+      <c r="J97" s="4">
+        <f>J95+J96</f>
+        <v/>
+      </c>
+      <c r="K97" s="4">
+        <f>K95+K96</f>
+        <v/>
+      </c>
+      <c r="L97" s="4">
+        <f>L95+L96</f>
+        <v/>
+      </c>
+      <c r="M97" s="4">
+        <f>M95+M96</f>
+        <v/>
+      </c>
+      <c r="N97" s="4">
+        <f>N95+N96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Cash Available for Distribution</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>Beginning + Funding</t>
-        </is>
-      </c>
-      <c r="D97" s="16">
-        <f>D84+D85</f>
-        <v/>
-      </c>
-      <c r="E97" s="16">
-        <f>E84+E85</f>
-        <v/>
-      </c>
-      <c r="F97" s="16">
-        <f>F84+F85</f>
-        <v/>
-      </c>
-      <c r="G97" s="16">
-        <f>G84+G85</f>
-        <v/>
-      </c>
-      <c r="H97" s="16">
-        <f>H84+H85</f>
-        <v/>
-      </c>
-      <c r="I97" s="16">
-        <f>I84+I85</f>
-        <v/>
-      </c>
-      <c r="J97" s="16">
-        <f>J84+J85</f>
-        <v/>
-      </c>
-      <c r="K97" s="16">
-        <f>K84+K85</f>
-        <v/>
-      </c>
-      <c r="L97" s="16">
-        <f>L84+L85</f>
-        <v/>
-      </c>
-      <c r="M97" s="16">
-        <f>M84+M85</f>
-        <v/>
-      </c>
-      <c r="N97" s="16">
-        <f>N84+N85</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTION WATERFALL</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="n"/>
-      <c r="C98" s="4" t="n"/>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>CFADS - Total DS - DSRA Fund</t>
+        </is>
+      </c>
       <c r="D98" s="4" t="n"/>
-      <c r="E98" s="4" t="n"/>
-      <c r="F98" s="4" t="n"/>
-      <c r="G98" s="4" t="n"/>
-      <c r="H98" s="4" t="n"/>
-      <c r="I98" s="4" t="n"/>
-      <c r="J98" s="4" t="n"/>
-      <c r="K98" s="4" t="n"/>
-      <c r="L98" s="4" t="n"/>
-      <c r="M98" s="4" t="n"/>
-      <c r="N98" s="4" t="n"/>
+      <c r="E98" s="16">
+        <f>E68-(E72+E77)-E85</f>
+        <v/>
+      </c>
+      <c r="F98" s="16">
+        <f>F68-(F72+F77)-F85</f>
+        <v/>
+      </c>
+      <c r="G98" s="16">
+        <f>G68-(G72+G77)-G85</f>
+        <v/>
+      </c>
+      <c r="H98" s="16">
+        <f>H68-(H72+H77)-H85</f>
+        <v/>
+      </c>
+      <c r="I98" s="16">
+        <f>I68-(I72+I77)-I85</f>
+        <v/>
+      </c>
+      <c r="J98" s="16">
+        <f>J68-(J72+J77)-J85</f>
+        <v/>
+      </c>
+      <c r="K98" s="16">
+        <f>K68-(K72+K77)-K85</f>
+        <v/>
+      </c>
+      <c r="L98" s="16">
+        <f>L68-(L72+L77)-L85</f>
+        <v/>
+      </c>
+      <c r="M98" s="16">
+        <f>M68-(M72+M77)-M85</f>
+        <v/>
+      </c>
+      <c r="N98" s="16">
+        <f>N68-(N72+N77)-N85</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Cash Available for Distribution</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+          <t>Lock-up Test</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="n"/>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>CFADS - Total DS - DSRA Fund</t>
-        </is>
-      </c>
-      <c r="E99" s="16">
-        <f>E68-(E72+E77)-E85</f>
-        <v/>
-      </c>
-      <c r="F99" s="16">
-        <f>F68-(F72+F77)-F85</f>
-        <v/>
-      </c>
-      <c r="G99" s="16">
-        <f>G68-(G72+G77)-G85</f>
-        <v/>
-      </c>
-      <c r="H99" s="16">
-        <f>H68-(H72+H77)-H85</f>
-        <v/>
-      </c>
-      <c r="I99" s="16">
-        <f>I68-(I72+I77)-I85</f>
-        <v/>
-      </c>
-      <c r="J99" s="16">
-        <f>J68-(J72+J77)-J85</f>
-        <v/>
-      </c>
-      <c r="K99" s="16">
-        <f>K68-(K72+K77)-K85</f>
-        <v/>
-      </c>
-      <c r="L99" s="16">
-        <f>L68-(L72+L77)-L85</f>
-        <v/>
-      </c>
-      <c r="M99" s="16">
-        <f>M68-(M72+M77)-M85</f>
-        <v/>
-      </c>
-      <c r="N99" s="16">
-        <f>N68-(N72+N77)-N85</f>
+          <t>PASS if DSCR ≥ Lock-up</t>
+        </is>
+      </c>
+      <c r="E99" s="20">
+        <f>IF(E79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F99" s="20">
+        <f>IF(F79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G99" s="20">
+        <f>IF(G79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H99" s="20">
+        <f>IF(H79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I99" s="20">
+        <f>IF(I79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J99" s="20">
+        <f>IF(J79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K99" s="20">
+        <f>IF(K79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L99" s="20">
+        <f>IF(L79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M99" s="20">
+        <f>IF(M79&gt;=$D$42,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N99" s="20">
+        <f>IF(N79&gt;=$D$42,"PASS","LOCKED")</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr"/>
+          <t>Distributable Cash</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>PASS if DSCR ≥ Lock-up</t>
-        </is>
-      </c>
-      <c r="E100" s="20">
-        <f>IF(E79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F100" s="20">
-        <f>IF(F79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="G100" s="20">
-        <f>IF(G79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="H100" s="20">
-        <f>IF(H79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="I100" s="20">
-        <f>IF(I79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="J100" s="20">
-        <f>IF(J79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="K100" s="20">
-        <f>IF(K79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="L100" s="20">
-        <f>IF(L79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="M100" s="20">
-        <f>IF(M79&gt;=$D$42,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="N100" s="20">
-        <f>IF(N79&gt;=$D$42,"PASS","LOCKED")</f>
+          <t>If PASS, MAX(0, Cash Avail)</t>
+        </is>
+      </c>
+      <c r="E100" s="7">
+        <f>E77-E82-E87-E96</f>
+        <v/>
+      </c>
+      <c r="F100" s="7">
+        <f>F77-F82-F87-F96</f>
+        <v/>
+      </c>
+      <c r="G100" s="7">
+        <f>G77-G82-G87-G96</f>
+        <v/>
+      </c>
+      <c r="H100" s="7">
+        <f>H77-H82-H87-H96</f>
+        <v/>
+      </c>
+      <c r="I100" s="7">
+        <f>I77-I82-I87-I96</f>
+        <v/>
+      </c>
+      <c r="J100" s="7">
+        <f>J77-J82-J87-J96</f>
+        <v/>
+      </c>
+      <c r="K100" s="7">
+        <f>K77-K82-K87-K96</f>
+        <v/>
+      </c>
+      <c r="L100" s="7">
+        <f>L77-L82-L87-L96</f>
+        <v/>
+      </c>
+      <c r="M100" s="7">
+        <f>M77-M82-M87-M96</f>
+        <v/>
+      </c>
+      <c r="N100" s="7">
+        <f>N77-N82-N87-N96</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Distributable Cash</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>If PASS, MAX(0, Cash Avail)</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr"/>
-      <c r="F101" s="7" t="inlineStr"/>
-      <c r="G101" s="7" t="inlineStr"/>
-      <c r="H101" s="7" t="inlineStr"/>
-      <c r="I101" s="7" t="inlineStr"/>
-      <c r="J101" s="7" t="inlineStr"/>
-      <c r="K101" s="7" t="inlineStr"/>
-      <c r="L101" s="7" t="inlineStr"/>
-      <c r="M101" s="7" t="inlineStr"/>
-      <c r="N101" s="7" t="inlineStr"/>
-    </row>
-    <row r="102"/>
+      <c r="A101" s="5" t="n"/>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="E101" s="7">
+        <f>IF(E89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F101" s="7">
+        <f>IF(F89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G101" s="7">
+        <f>IF(G89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H101" s="7">
+        <f>IF(H89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I101" s="7">
+        <f>IF(I89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J101" s="7">
+        <f>IF(J89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K101" s="7">
+        <f>IF(K89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L101" s="7">
+        <f>IF(L89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M101" s="7">
+        <f>IF(M89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N101" s="7">
+        <f>IF(N89&gt;=$D$52,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; USES (Year 0)</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4">
+        <f>IF(E101="PASS",MAX(0,E100),0)</f>
+        <v/>
+      </c>
+      <c r="F102" s="4">
+        <f>IF(F101="PASS",MAX(0,F100),0)</f>
+        <v/>
+      </c>
+      <c r="G102" s="4">
+        <f>IF(G101="PASS",MAX(0,G100),0)</f>
+        <v/>
+      </c>
+      <c r="H102" s="4">
+        <f>IF(H101="PASS",MAX(0,H100),0)</f>
+        <v/>
+      </c>
+      <c r="I102" s="4">
+        <f>IF(I101="PASS",MAX(0,I100),0)</f>
+        <v/>
+      </c>
+      <c r="J102" s="4">
+        <f>IF(J101="PASS",MAX(0,J100),0)</f>
+        <v/>
+      </c>
+      <c r="K102" s="4">
+        <f>IF(K101="PASS",MAX(0,K100),0)</f>
+        <v/>
+      </c>
+      <c r="L102" s="4">
+        <f>IF(L101="PASS",MAX(0,L100),0)</f>
+        <v/>
+      </c>
+      <c r="M102" s="4">
+        <f>IF(M101="PASS",MAX(0,M100),0)</f>
+        <v/>
+      </c>
+      <c r="N102" s="4">
+        <f>IF(N101="PASS",MAX(0,N100),0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>SOURCES &amp; USES (Year 0)</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="n"/>
-      <c r="C103" s="4" t="n"/>
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>USES</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="n"/>
+      <c r="C103" s="6" t="n"/>
       <c r="D103" s="4" t="n"/>
       <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="n"/>
@@ -5385,18 +5730,26 @@
       <c r="N103" s="4" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="21" t="inlineStr">
-        <is>
-          <t>USES</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr"/>
-      <c r="C104" s="6" t="inlineStr"/>
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Purchase Price</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="16">
+        <f>$D$17</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Purchase Price</t>
+          <t xml:space="preserve">  Transaction Fees</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
@@ -5404,16 +5757,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr"/>
+      <c r="C105" s="6" t="n"/>
       <c r="D105" s="16">
-        <f>$D$17</f>
+        <f>$D$17*$D$18</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Transaction Fees</t>
+          <t xml:space="preserve">  DSRA Funding</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
@@ -5421,16 +5774,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr"/>
+      <c r="C106" s="6" t="n"/>
       <c r="D106" s="16">
-        <f>$D$17*$D$18</f>
+        <f>$D$27</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSRA Funding</t>
+          <t>Total Uses</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
@@ -5438,43 +5791,55 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr"/>
-      <c r="D107" s="16">
-        <f>D83</f>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="7">
+        <f>$D$27*$D$28</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Total Uses</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="A108" s="5" t="n"/>
+      <c r="B108" s="6" t="n"/>
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="7">
+        <f>E94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="21" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109">
+        <f>D106+D107+D108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Debt</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr"/>
-      <c r="D108" s="7">
-        <f>D94+D95+D96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109"/>
-    <row r="110">
-      <c r="A110" s="21" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr"/>
-      <c r="C110" s="6" t="inlineStr"/>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="16">
+        <f>$D$50</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Debt</t>
+          <t xml:space="preserve">  Equity</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -5482,16 +5847,20 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr"/>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>Plug to balance</t>
+        </is>
+      </c>
       <c r="D111" s="16">
-        <f>$D$50</f>
+        <f>D97-D100</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Equity</t>
+          <t>Total Sources</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
@@ -5499,63 +5868,84 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>Plug to balance</t>
-        </is>
-      </c>
-      <c r="D112" s="16">
-        <f>D97-D100</f>
+      <c r="C112" s="6" t="n"/>
+      <c r="D112" s="7">
+        <f>$D$27*$D$47</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Total Sources</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
+          <t>Balance Check</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="10">
+        <f>D109-D112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n"/>
+      <c r="B114" s="6" t="n"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="10">
+        <f>D112+D113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>EXIT CALCULATIONS</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="4" t="n"/>
+      <c r="J115" s="4" t="n"/>
+      <c r="K115" s="4" t="n"/>
+      <c r="L115" s="4" t="n"/>
+      <c r="M115" s="4" t="n"/>
+      <c r="N115" s="4" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Exit EV</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr"/>
-      <c r="D113" s="7">
-        <f>D100+D101</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>Balance Check</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr"/>
-      <c r="C114" s="6" t="inlineStr"/>
-      <c r="D114" s="10">
-        <f>IF(ABS(D97-D102)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115"/>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>EXIT CALCULATIONS</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="n"/>
-      <c r="C116" s="4" t="n"/>
-      <c r="D116" s="4" t="n"/>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>Exit Multiple × Exit Yr EBITDA</t>
+        </is>
+      </c>
+      <c r="D116" s="4">
+        <f>IF(ABS(D109-D114)&lt;0.01,"PASS","FAIL")</f>
+        <v/>
+      </c>
       <c r="E116" s="4" t="n"/>
       <c r="F116" s="4" t="n"/>
       <c r="G116" s="4" t="n"/>
       <c r="H116" s="4" t="n"/>
       <c r="I116" s="4" t="n"/>
       <c r="J116" s="4" t="n"/>
-      <c r="K116" s="4" t="n"/>
+      <c r="K116" s="16">
+        <f>$D$19*K62</f>
+        <v/>
+      </c>
       <c r="L116" s="4" t="n"/>
       <c r="M116" s="4" t="n"/>
       <c r="N116" s="4" t="n"/>
@@ -5563,7 +5953,7 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Exit EV</t>
+          <t>Exit Debt Payoff</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
@@ -5573,15 +5963,18 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Exit Multiple × Exit Yr EBITDA</t>
-        </is>
-      </c>
-      <c r="K117" s="16" t="inlineStr"/>
+          <t>Ending Bal at Exit</t>
+        </is>
+      </c>
+      <c r="K117" s="16">
+        <f>K78</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Exit Debt Payoff</t>
+          <t>DSRA Release</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
@@ -5591,18 +5984,18 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Ending Bal at Exit</t>
+          <t>DSRA Ending at Exit</t>
         </is>
       </c>
       <c r="K118" s="16">
-        <f>K78</f>
+        <f>K86</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>DSRA Release</t>
+          <t>Exit Equity Proceeds</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
@@ -5612,190 +6005,382 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>DSRA Ending at Exit</t>
-        </is>
-      </c>
-      <c r="K119" s="16">
-        <f>K86</f>
+          <t>Exit EV - Debt + DSRA</t>
+        </is>
+      </c>
+      <c r="D119">
+        <f>K72</f>
+        <v/>
+      </c>
+      <c r="K119" s="7">
+        <f>K106-K107+K108</f>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>Exit Equity Proceeds</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="A120" s="5" t="n"/>
+      <c r="B120" s="6" t="n"/>
+      <c r="C120" s="6" t="n"/>
+      <c r="D120">
+        <f>D119*$D$29</f>
+        <v/>
+      </c>
+      <c r="K120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>EQUITY RETURNS</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4">
+        <f>K88</f>
+        <v/>
+      </c>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="n"/>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="n"/>
+      <c r="J121" s="4" t="n"/>
+      <c r="K121" s="4" t="n"/>
+      <c r="L121" s="4" t="n"/>
+      <c r="M121" s="4" t="n"/>
+      <c r="N121" s="4" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Equity Cash Flow</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>Exit EV - Debt + DSRA</t>
-        </is>
-      </c>
-      <c r="K120" s="7" t="inlineStr"/>
-    </row>
-    <row r="121"/>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>EQUITY RETURNS</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="n"/>
-      <c r="C122" s="4" t="n"/>
-      <c r="D122" s="4" t="n"/>
-      <c r="E122" s="4" t="n"/>
-      <c r="F122" s="4" t="n"/>
-      <c r="G122" s="4" t="n"/>
-      <c r="H122" s="4" t="n"/>
-      <c r="I122" s="4" t="n"/>
-      <c r="J122" s="4" t="n"/>
-      <c r="K122" s="4" t="n"/>
-      <c r="L122" s="4" t="n"/>
-      <c r="M122" s="4" t="n"/>
-      <c r="N122" s="4" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="16">
+        <f>K97</f>
+        <v/>
+      </c>
+      <c r="E122" s="16">
+        <f>E90</f>
+        <v/>
+      </c>
+      <c r="F122" s="16">
+        <f>F90</f>
+        <v/>
+      </c>
+      <c r="G122" s="16">
+        <f>G90</f>
+        <v/>
+      </c>
+      <c r="H122" s="16">
+        <f>H90</f>
+        <v/>
+      </c>
+      <c r="I122" s="16">
+        <f>I90</f>
+        <v/>
+      </c>
+      <c r="J122" s="16">
+        <f>J90</f>
+        <v/>
+      </c>
+      <c r="K122" s="16">
+        <f>K90+K109</f>
+        <v/>
+      </c>
+      <c r="L122" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M122" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N122" s="16">
+        <f>0</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Equity Cash Flow</t>
+          <t>Levered IRR</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr"/>
-      <c r="D123" s="16" t="inlineStr"/>
-      <c r="E123" s="16" t="inlineStr"/>
-      <c r="F123" s="16" t="inlineStr"/>
-      <c r="G123" s="16" t="inlineStr"/>
-      <c r="H123" s="16" t="inlineStr"/>
-      <c r="I123" s="16" t="inlineStr"/>
-      <c r="J123" s="16" t="inlineStr"/>
-      <c r="K123" s="16" t="inlineStr"/>
-      <c r="L123" s="16" t="inlineStr"/>
-      <c r="M123" s="16" t="inlineStr"/>
-      <c r="N123" s="16" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
+      </c>
+      <c r="D123" s="29">
+        <f>D120-D121+D122</f>
+        <v/>
+      </c>
+      <c r="E123" s="16" t="n"/>
+      <c r="F123" s="16" t="n"/>
+      <c r="G123" s="16" t="n"/>
+      <c r="H123" s="16" t="n"/>
+      <c r="I123" s="16" t="n"/>
+      <c r="J123" s="16" t="n"/>
+      <c r="K123" s="16" t="n"/>
+      <c r="L123" s="16" t="n"/>
+      <c r="M123" s="16" t="n"/>
+      <c r="N123" s="16" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
+          <t>MOIC</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr"/>
-      <c r="D124" s="29" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>Sum inflows / outflow</t>
+        </is>
+      </c>
+      <c r="D124" s="28">
+        <f>SUMIF(D112:K112,"&gt;0")/ABS(D112)</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>Sum inflows / outflow</t>
-        </is>
-      </c>
-      <c r="D125" s="28" t="inlineStr"/>
-    </row>
-    <row r="126"/>
+      <c r="A125" s="5" t="n"/>
+      <c r="B125" s="6" t="n"/>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="28" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="21" t="inlineStr">
+        <is>
+          <t>Unlevered Returns (for reference)</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="n"/>
+      <c r="C126" s="6" t="n"/>
+      <c r="D126">
+        <f>-D113</f>
+        <v/>
+      </c>
+      <c r="E126">
+        <f>E102</f>
+        <v/>
+      </c>
+      <c r="F126">
+        <f>F102</f>
+        <v/>
+      </c>
+      <c r="G126">
+        <f>G102</f>
+        <v/>
+      </c>
+      <c r="H126">
+        <f>H102</f>
+        <v/>
+      </c>
+      <c r="I126">
+        <f>I102</f>
+        <v/>
+      </c>
+      <c r="J126">
+        <f>J102</f>
+        <v/>
+      </c>
+      <c r="K126">
+        <f>K102+D123</f>
+        <v/>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="127">
-      <c r="A127" s="21" t="inlineStr">
-        <is>
-          <t>Unlevered Returns (for reference)</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr"/>
-      <c r="C127" s="6" t="inlineStr"/>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="n"/>
+      <c r="D127" s="29" t="n"/>
+      <c r="E127" s="16">
+        <f>E68</f>
+        <v/>
+      </c>
+      <c r="F127" s="16">
+        <f>F68</f>
+        <v/>
+      </c>
+      <c r="G127" s="16">
+        <f>G68</f>
+        <v/>
+      </c>
+      <c r="H127" s="16">
+        <f>H68</f>
+        <v/>
+      </c>
+      <c r="I127" s="16">
+        <f>I68</f>
+        <v/>
+      </c>
+      <c r="J127" s="16">
+        <f>J68</f>
+        <v/>
+      </c>
+      <c r="K127" s="16">
+        <f>K68+K106</f>
+        <v/>
+      </c>
+      <c r="L127" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M127" s="16">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N127" s="16">
+        <f>0</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Unlevered Cash Flow</t>
+          <t>Unlevered IRR</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr"/>
-      <c r="D128" s="16">
-        <f>-$D$17-D95</f>
-        <v/>
-      </c>
-      <c r="E128" s="16">
-        <f>E68</f>
-        <v/>
-      </c>
-      <c r="F128" s="16">
-        <f>F68</f>
-        <v/>
-      </c>
-      <c r="G128" s="16">
-        <f>G68</f>
-        <v/>
-      </c>
-      <c r="H128" s="16">
-        <f>H68</f>
-        <v/>
-      </c>
-      <c r="I128" s="16">
-        <f>I68</f>
-        <v/>
-      </c>
-      <c r="J128" s="16">
-        <f>J68</f>
-        <v/>
-      </c>
-      <c r="K128" s="16">
-        <f>K68+K106</f>
-        <v/>
-      </c>
-      <c r="L128" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M128" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N128" s="16">
-        <f>0</f>
-        <v/>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
+      </c>
+      <c r="D128" s="28" t="n"/>
+      <c r="E128" s="16" t="n"/>
+      <c r="F128" s="16" t="n"/>
+      <c r="G128" s="16" t="n"/>
+      <c r="H128" s="16" t="n"/>
+      <c r="I128" s="16" t="n"/>
+      <c r="J128" s="16" t="n"/>
+      <c r="K128" s="16" t="n"/>
+      <c r="L128" s="16" t="n"/>
+      <c r="M128" s="16" t="n"/>
+      <c r="N128" s="16" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr"/>
-      <c r="D129" s="29" t="inlineStr"/>
-    </row>
+      <c r="A129" s="5" t="n"/>
+      <c r="B129" s="6" t="n"/>
+      <c r="C129" s="6" t="n"/>
+      <c r="D129" s="29" t="n"/>
+    </row>
+    <row r="130"/>
+    <row r="131">
+      <c r="D131">
+        <f>-$D$27-D107</f>
+        <v/>
+      </c>
+      <c r="E131">
+        <f>E77</f>
+        <v/>
+      </c>
+      <c r="F131">
+        <f>F77</f>
+        <v/>
+      </c>
+      <c r="G131">
+        <f>G77</f>
+        <v/>
+      </c>
+      <c r="H131">
+        <f>H77</f>
+        <v/>
+      </c>
+      <c r="I131">
+        <f>I77</f>
+        <v/>
+      </c>
+      <c r="J131">
+        <f>J77</f>
+        <v/>
+      </c>
+      <c r="K131">
+        <f>K77+D120</f>
+        <v/>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="D132" s="56">
+        <f>IRR(D131:N131)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -3082,7 +3082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3166,7 +3166,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>═══ DRILL MODE - Fill in yellow cells ═══</t>
+          <t>═══ AUDIT STRIP ═══</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4471,16 +4471,46 @@
           <t>Volume(Bcf) × Fee × 1000</t>
         </is>
       </c>
-      <c r="E69" s="16" t="n"/>
-      <c r="F69" s="16" t="n"/>
-      <c r="G69" s="16" t="n"/>
-      <c r="H69" s="16" t="n"/>
-      <c r="I69" s="16" t="n"/>
-      <c r="J69" s="16" t="n"/>
-      <c r="K69" s="16" t="n"/>
-      <c r="L69" s="16" t="n"/>
-      <c r="M69" s="16" t="n"/>
-      <c r="N69" s="16" t="n"/>
+      <c r="E69" s="16">
+        <f>E66*E67</f>
+        <v/>
+      </c>
+      <c r="F69" s="16">
+        <f>F66*F67</f>
+        <v/>
+      </c>
+      <c r="G69" s="16">
+        <f>G66*G67</f>
+        <v/>
+      </c>
+      <c r="H69" s="16">
+        <f>H66*H67</f>
+        <v/>
+      </c>
+      <c r="I69" s="16">
+        <f>I66*I67</f>
+        <v/>
+      </c>
+      <c r="J69" s="16">
+        <f>J66*J67</f>
+        <v/>
+      </c>
+      <c r="K69" s="16">
+        <f>K66*K67</f>
+        <v/>
+      </c>
+      <c r="L69" s="16">
+        <f>L66*L67</f>
+        <v/>
+      </c>
+      <c r="M69" s="16">
+        <f>M66*M67</f>
+        <v/>
+      </c>
+      <c r="N69" s="16">
+        <f>N66*N67</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -4498,16 +4528,46 @@
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E70" s="16" t="n"/>
-      <c r="F70" s="16" t="n"/>
-      <c r="G70" s="16" t="n"/>
-      <c r="H70" s="16" t="n"/>
-      <c r="I70" s="16" t="n"/>
-      <c r="J70" s="16" t="n"/>
-      <c r="K70" s="16" t="n"/>
-      <c r="L70" s="16" t="n"/>
-      <c r="M70" s="16" t="n"/>
-      <c r="N70" s="16" t="n"/>
+      <c r="E70" s="16">
+        <f>$D$42*(1+$D$43)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F70" s="16">
+        <f>$D$42*(1+$D$43)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G70" s="16">
+        <f>$D$42*(1+$D$43)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H70" s="16">
+        <f>$D$42*(1+$D$43)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I70" s="16">
+        <f>$D$42*(1+$D$43)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J70" s="16">
+        <f>$D$42*(1+$D$43)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K70" s="16">
+        <f>$D$42*(1+$D$43)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L70" s="16">
+        <f>$D$42*(1+$D$43)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M70" s="16">
+        <f>$D$42*(1+$D$43)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N70" s="16">
+        <f>$D$42*(1+$D$43)^(10-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -4540,16 +4600,46 @@
           <t>Revenue minus OpEx</t>
         </is>
       </c>
-      <c r="E72" s="7" t="n"/>
-      <c r="F72" s="7" t="n"/>
-      <c r="G72" s="7" t="n"/>
-      <c r="H72" s="7" t="n"/>
-      <c r="I72" s="7" t="n"/>
-      <c r="J72" s="7" t="n"/>
-      <c r="K72" s="7" t="n"/>
-      <c r="L72" s="7" t="n"/>
-      <c r="M72" s="7" t="n"/>
-      <c r="N72" s="7" t="n"/>
+      <c r="E72" s="7">
+        <f>E69-E70</f>
+        <v/>
+      </c>
+      <c r="F72" s="7">
+        <f>F69-F70</f>
+        <v/>
+      </c>
+      <c r="G72" s="7">
+        <f>G69-G70</f>
+        <v/>
+      </c>
+      <c r="H72" s="7">
+        <f>H69-H70</f>
+        <v/>
+      </c>
+      <c r="I72" s="7">
+        <f>I69-I70</f>
+        <v/>
+      </c>
+      <c r="J72" s="7">
+        <f>J69-J70</f>
+        <v/>
+      </c>
+      <c r="K72" s="7">
+        <f>K69-K70</f>
+        <v/>
+      </c>
+      <c r="L72" s="7">
+        <f>L69-L70</f>
+        <v/>
+      </c>
+      <c r="M72" s="7">
+        <f>M69-M70</f>
+        <v/>
+      </c>
+      <c r="N72" s="7">
+        <f>N69-N70</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
@@ -4603,16 +4693,46 @@
         </is>
       </c>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="16" t="n"/>
-      <c r="F75" s="16" t="n"/>
-      <c r="G75" s="16" t="n"/>
-      <c r="H75" s="16" t="n"/>
-      <c r="I75" s="16" t="n"/>
-      <c r="J75" s="16" t="n"/>
-      <c r="K75" s="16" t="n"/>
-      <c r="L75" s="16" t="n"/>
-      <c r="M75" s="16" t="n"/>
-      <c r="N75" s="16" t="n"/>
+      <c r="E75" s="16">
+        <f>E72-$D$61</f>
+        <v/>
+      </c>
+      <c r="F75" s="16">
+        <f>F72-$D$61</f>
+        <v/>
+      </c>
+      <c r="G75" s="16">
+        <f>G72-$D$61</f>
+        <v/>
+      </c>
+      <c r="H75" s="16">
+        <f>H72-$D$61</f>
+        <v/>
+      </c>
+      <c r="I75" s="16">
+        <f>I72-$D$61</f>
+        <v/>
+      </c>
+      <c r="J75" s="16">
+        <f>J72-$D$61</f>
+        <v/>
+      </c>
+      <c r="K75" s="16">
+        <f>K72-$D$61</f>
+        <v/>
+      </c>
+      <c r="L75" s="16">
+        <f>L72-$D$61</f>
+        <v/>
+      </c>
+      <c r="M75" s="16">
+        <f>M72-$D$61</f>
+        <v/>
+      </c>
+      <c r="N75" s="16">
+        <f>N72-$D$61</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -4631,43 +4751,43 @@
         </is>
       </c>
       <c r="E76" s="16">
-        <f>IF(1&lt;=5,$D$44,0)</f>
+        <f>MAX(0,E75)*$D$55</f>
         <v/>
       </c>
       <c r="F76" s="16">
-        <f>IF(2&lt;=5,$D$44,0)</f>
+        <f>MAX(0,F75)*$D$55</f>
         <v/>
       </c>
       <c r="G76" s="16">
-        <f>IF(3&lt;=5,$D$44,0)</f>
+        <f>MAX(0,G75)*$D$55</f>
         <v/>
       </c>
       <c r="H76" s="16">
-        <f>IF(4&lt;=5,$D$44,0)</f>
+        <f>MAX(0,H75)*$D$55</f>
         <v/>
       </c>
       <c r="I76" s="16">
-        <f>IF(5&lt;=5,$D$44,0)</f>
+        <f>MAX(0,I75)*$D$55</f>
         <v/>
       </c>
       <c r="J76" s="16">
-        <f>IF(6&lt;=5,$D$44,0)</f>
+        <f>MAX(0,J75)*$D$55</f>
         <v/>
       </c>
       <c r="K76" s="16">
-        <f>IF(7&lt;=5,$D$44,0)</f>
+        <f>MAX(0,K75)*$D$55</f>
         <v/>
       </c>
       <c r="L76" s="16">
-        <f>IF(8&lt;=5,$D$44,0)</f>
+        <f>MAX(0,L75)*$D$55</f>
         <v/>
       </c>
       <c r="M76" s="16">
-        <f>IF(9&lt;=5,$D$44,0)</f>
+        <f>MAX(0,M75)*$D$55</f>
         <v/>
       </c>
       <c r="N76" s="16">
-        <f>IF(10&lt;=5,$D$44,0)</f>
+        <f>MAX(0,N75)*$D$55</f>
         <v/>
       </c>
     </row>
@@ -4687,16 +4807,46 @@
           <t>Y1-Y5 only</t>
         </is>
       </c>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="7" t="n"/>
-      <c r="G77" s="7" t="n"/>
-      <c r="H77" s="7" t="n"/>
-      <c r="I77" s="7" t="n"/>
-      <c r="J77" s="7" t="n"/>
-      <c r="K77" s="7" t="n"/>
-      <c r="L77" s="7" t="n"/>
-      <c r="M77" s="7" t="n"/>
-      <c r="N77" s="7" t="n"/>
+      <c r="E77" s="7">
+        <f>IF(1&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="F77" s="7">
+        <f>IF(2&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="G77" s="7">
+        <f>IF(3&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="H77" s="7">
+        <f>IF(4&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="I77" s="7">
+        <f>IF(5&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="J77" s="7">
+        <f>IF(6&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="K77" s="7">
+        <f>IF(7&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="L77" s="7">
+        <f>IF(8&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="M77" s="7">
+        <f>IF(9&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
+      <c r="N77" s="7">
+        <f>IF(10&lt;=5,$D$44,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -4715,43 +4865,43 @@
         </is>
       </c>
       <c r="E78" s="7">
-        <f>E62-E66-E67</f>
+        <f>E72-E76-E77</f>
         <v/>
       </c>
       <c r="F78" s="7">
-        <f>F62-F66-F67</f>
+        <f>F72-F76-F77</f>
         <v/>
       </c>
       <c r="G78" s="7">
-        <f>G62-G66-G67</f>
+        <f>G72-G76-G77</f>
         <v/>
       </c>
       <c r="H78" s="7">
-        <f>H62-H66-H67</f>
+        <f>H72-H76-H77</f>
         <v/>
       </c>
       <c r="I78" s="7">
-        <f>I62-I66-I67</f>
+        <f>I72-I76-I77</f>
         <v/>
       </c>
       <c r="J78" s="7">
-        <f>J62-J66-J67</f>
+        <f>J72-J76-J77</f>
         <v/>
       </c>
       <c r="K78" s="7">
-        <f>K62-K66-K67</f>
+        <f>K72-K76-K77</f>
         <v/>
       </c>
       <c r="L78" s="7">
-        <f>L62-L66-L67</f>
+        <f>L72-L76-L77</f>
         <v/>
       </c>
       <c r="M78" s="7">
-        <f>M62-M66-M67</f>
+        <f>M72-M76-M77</f>
         <v/>
       </c>
       <c r="N78" s="7">
-        <f>N62-N66-N67</f>
+        <f>N72-N76-N77</f>
         <v/>
       </c>
     </row>
@@ -4805,16 +4955,46 @@
       <c r="D81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E81" s="16" t="n"/>
-      <c r="F81" s="16" t="n"/>
-      <c r="G81" s="16" t="n"/>
-      <c r="H81" s="16" t="n"/>
-      <c r="I81" s="16" t="n"/>
-      <c r="J81" s="16" t="n"/>
-      <c r="K81" s="16" t="n"/>
-      <c r="L81" s="16" t="n"/>
-      <c r="M81" s="16" t="n"/>
-      <c r="N81" s="16" t="n"/>
+      <c r="E81" s="16">
+        <f>$D$60</f>
+        <v/>
+      </c>
+      <c r="F81" s="16">
+        <f>E88</f>
+        <v/>
+      </c>
+      <c r="G81" s="16">
+        <f>F88</f>
+        <v/>
+      </c>
+      <c r="H81" s="16">
+        <f>G88</f>
+        <v/>
+      </c>
+      <c r="I81" s="16">
+        <f>H88</f>
+        <v/>
+      </c>
+      <c r="J81" s="16">
+        <f>I88</f>
+        <v/>
+      </c>
+      <c r="K81" s="16">
+        <f>J88</f>
+        <v/>
+      </c>
+      <c r="L81" s="16">
+        <f>K88</f>
+        <v/>
+      </c>
+      <c r="M81" s="16">
+        <f>L88</f>
+        <v/>
+      </c>
+      <c r="N81" s="16">
+        <f>M88</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -4832,16 +5012,46 @@
           <t>Beg Bal × Int Rate</t>
         </is>
       </c>
-      <c r="E82" s="16" t="n"/>
-      <c r="F82" s="16" t="n"/>
-      <c r="G82" s="16" t="n"/>
-      <c r="H82" s="16" t="n"/>
-      <c r="I82" s="16" t="n"/>
-      <c r="J82" s="16" t="n"/>
-      <c r="K82" s="16" t="n"/>
-      <c r="L82" s="16" t="n"/>
-      <c r="M82" s="16" t="n"/>
-      <c r="N82" s="16" t="n"/>
+      <c r="E82" s="16">
+        <f>E81*$D$48</f>
+        <v/>
+      </c>
+      <c r="F82" s="16">
+        <f>F81*$D$48</f>
+        <v/>
+      </c>
+      <c r="G82" s="16">
+        <f>G81*$D$48</f>
+        <v/>
+      </c>
+      <c r="H82" s="16">
+        <f>H81*$D$48</f>
+        <v/>
+      </c>
+      <c r="I82" s="16">
+        <f>I81*$D$48</f>
+        <v/>
+      </c>
+      <c r="J82" s="16">
+        <f>J81*$D$48</f>
+        <v/>
+      </c>
+      <c r="K82" s="16">
+        <f>K81*$D$48</f>
+        <v/>
+      </c>
+      <c r="L82" s="16">
+        <f>L81*$D$48</f>
+        <v/>
+      </c>
+      <c r="M82" s="16">
+        <f>M81*$D$48</f>
+        <v/>
+      </c>
+      <c r="N82" s="16">
+        <f>N81*$D$48</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -4859,16 +5069,46 @@
           <t>MIN(Sched, Beg Bal)</t>
         </is>
       </c>
-      <c r="E83" s="16" t="n"/>
-      <c r="F83" s="16" t="n"/>
-      <c r="G83" s="16" t="n"/>
-      <c r="H83" s="16" t="n"/>
-      <c r="I83" s="16" t="n"/>
-      <c r="J83" s="16" t="n"/>
-      <c r="K83" s="16" t="n"/>
-      <c r="L83" s="16" t="n"/>
-      <c r="M83" s="16" t="n"/>
-      <c r="N83" s="16" t="n"/>
+      <c r="E83" s="16">
+        <f>MIN($D$62,E81)</f>
+        <v/>
+      </c>
+      <c r="F83" s="16">
+        <f>MIN($D$62,F81)</f>
+        <v/>
+      </c>
+      <c r="G83" s="16">
+        <f>MIN($D$62,G81)</f>
+        <v/>
+      </c>
+      <c r="H83" s="16">
+        <f>MIN($D$62,H81)</f>
+        <v/>
+      </c>
+      <c r="I83" s="16">
+        <f>MIN($D$62,I81)</f>
+        <v/>
+      </c>
+      <c r="J83" s="16">
+        <f>MIN($D$62,J81)</f>
+        <v/>
+      </c>
+      <c r="K83" s="16">
+        <f>MIN($D$62,K81)</f>
+        <v/>
+      </c>
+      <c r="L83" s="16">
+        <f>MIN($D$62,L81)</f>
+        <v/>
+      </c>
+      <c r="M83" s="16">
+        <f>MIN($D$62,M81)</f>
+        <v/>
+      </c>
+      <c r="N83" s="16">
+        <f>MIN($D$62,N81)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -4886,16 +5126,46 @@
           <t>Interest + Sched Prin</t>
         </is>
       </c>
-      <c r="E84" s="16" t="n"/>
-      <c r="F84" s="16" t="n"/>
-      <c r="G84" s="16" t="n"/>
-      <c r="H84" s="16" t="n"/>
-      <c r="I84" s="16" t="n"/>
-      <c r="J84" s="16" t="n"/>
-      <c r="K84" s="16" t="n"/>
-      <c r="L84" s="16" t="n"/>
-      <c r="M84" s="16" t="n"/>
-      <c r="N84" s="16" t="n"/>
+      <c r="E84" s="16">
+        <f>E82+E83</f>
+        <v/>
+      </c>
+      <c r="F84" s="16">
+        <f>F82+F83</f>
+        <v/>
+      </c>
+      <c r="G84" s="16">
+        <f>G82+G83</f>
+        <v/>
+      </c>
+      <c r="H84" s="16">
+        <f>H82+H83</f>
+        <v/>
+      </c>
+      <c r="I84" s="16">
+        <f>I82+I83</f>
+        <v/>
+      </c>
+      <c r="J84" s="16">
+        <f>J82+J83</f>
+        <v/>
+      </c>
+      <c r="K84" s="16">
+        <f>K82+K83</f>
+        <v/>
+      </c>
+      <c r="L84" s="16">
+        <f>L82+L83</f>
+        <v/>
+      </c>
+      <c r="M84" s="16">
+        <f>M82+M83</f>
+        <v/>
+      </c>
+      <c r="N84" s="16">
+        <f>N82+N83</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -4970,16 +5240,46 @@
           <t>MIN(Excess×75%, Beg-Sched)</t>
         </is>
       </c>
-      <c r="E86" s="19" t="n"/>
-      <c r="F86" s="19" t="n"/>
-      <c r="G86" s="19" t="n"/>
-      <c r="H86" s="19" t="n"/>
-      <c r="I86" s="19" t="n"/>
-      <c r="J86" s="19" t="n"/>
-      <c r="K86" s="19" t="n"/>
-      <c r="L86" s="19" t="n"/>
-      <c r="M86" s="19" t="n"/>
-      <c r="N86" s="19" t="n"/>
+      <c r="E86" s="19">
+        <f>MIN(E85*$D$51,MAX(0,E81-E83))</f>
+        <v/>
+      </c>
+      <c r="F86" s="19">
+        <f>MIN(F85*$D$51,MAX(0,F81-F83))</f>
+        <v/>
+      </c>
+      <c r="G86" s="19">
+        <f>MIN(G85*$D$51,MAX(0,G81-G83))</f>
+        <v/>
+      </c>
+      <c r="H86" s="19">
+        <f>MIN(H85*$D$51,MAX(0,H81-H83))</f>
+        <v/>
+      </c>
+      <c r="I86" s="19">
+        <f>MIN(I85*$D$51,MAX(0,I81-I83))</f>
+        <v/>
+      </c>
+      <c r="J86" s="19">
+        <f>MIN(J85*$D$51,MAX(0,J81-J83))</f>
+        <v/>
+      </c>
+      <c r="K86" s="19">
+        <f>MIN(K85*$D$51,MAX(0,K81-K83))</f>
+        <v/>
+      </c>
+      <c r="L86" s="19">
+        <f>MIN(L85*$D$51,MAX(0,L81-L83))</f>
+        <v/>
+      </c>
+      <c r="M86" s="19">
+        <f>MIN(M85*$D$51,MAX(0,M81-M83))</f>
+        <v/>
+      </c>
+      <c r="N86" s="19">
+        <f>MIN(N85*$D$51,MAX(0,N81-N83))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -4997,16 +5297,46 @@
           <t>Scheduled + Sweep</t>
         </is>
       </c>
-      <c r="E87" s="16" t="n"/>
-      <c r="F87" s="16" t="n"/>
-      <c r="G87" s="16" t="n"/>
-      <c r="H87" s="16" t="n"/>
-      <c r="I87" s="16" t="n"/>
-      <c r="J87" s="16" t="n"/>
-      <c r="K87" s="16" t="n"/>
-      <c r="L87" s="16" t="n"/>
-      <c r="M87" s="16" t="n"/>
-      <c r="N87" s="16" t="n"/>
+      <c r="E87" s="16">
+        <f>E83+E86</f>
+        <v/>
+      </c>
+      <c r="F87" s="16">
+        <f>F83+F86</f>
+        <v/>
+      </c>
+      <c r="G87" s="16">
+        <f>G83+G86</f>
+        <v/>
+      </c>
+      <c r="H87" s="16">
+        <f>H83+H86</f>
+        <v/>
+      </c>
+      <c r="I87" s="16">
+        <f>I83+I86</f>
+        <v/>
+      </c>
+      <c r="J87" s="16">
+        <f>J83+J86</f>
+        <v/>
+      </c>
+      <c r="K87" s="16">
+        <f>K83+K86</f>
+        <v/>
+      </c>
+      <c r="L87" s="16">
+        <f>L83+L86</f>
+        <v/>
+      </c>
+      <c r="M87" s="16">
+        <f>M83+M86</f>
+        <v/>
+      </c>
+      <c r="N87" s="16">
+        <f>N83+N86</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -5028,16 +5358,46 @@
         <f>$D$60</f>
         <v/>
       </c>
-      <c r="E88" s="16" t="n"/>
-      <c r="F88" s="16" t="n"/>
-      <c r="G88" s="16" t="n"/>
-      <c r="H88" s="16" t="n"/>
-      <c r="I88" s="16" t="n"/>
-      <c r="J88" s="16" t="n"/>
-      <c r="K88" s="16" t="n"/>
-      <c r="L88" s="16" t="n"/>
-      <c r="M88" s="16" t="n"/>
-      <c r="N88" s="16" t="n"/>
+      <c r="E88" s="16">
+        <f>MAX(0,E81-E87)</f>
+        <v/>
+      </c>
+      <c r="F88" s="16">
+        <f>MAX(0,F81-F87)</f>
+        <v/>
+      </c>
+      <c r="G88" s="16">
+        <f>MAX(0,G81-G87)</f>
+        <v/>
+      </c>
+      <c r="H88" s="16">
+        <f>MAX(0,H81-H87)</f>
+        <v/>
+      </c>
+      <c r="I88" s="16">
+        <f>MAX(0,I81-I87)</f>
+        <v/>
+      </c>
+      <c r="J88" s="16">
+        <f>MAX(0,J81-J87)</f>
+        <v/>
+      </c>
+      <c r="K88" s="16">
+        <f>MAX(0,K81-K87)</f>
+        <v/>
+      </c>
+      <c r="L88" s="16">
+        <f>MAX(0,L81-L87)</f>
+        <v/>
+      </c>
+      <c r="M88" s="16">
+        <f>MAX(0,M81-M87)</f>
+        <v/>
+      </c>
+      <c r="N88" s="16">
+        <f>MAX(0,N81-N87)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -5055,16 +5415,46 @@
           <t>CFADS / Debt Service</t>
         </is>
       </c>
-      <c r="E89" s="28" t="n"/>
-      <c r="F89" s="28" t="n"/>
-      <c r="G89" s="28" t="n"/>
-      <c r="H89" s="28" t="n"/>
-      <c r="I89" s="28" t="n"/>
-      <c r="J89" s="28" t="n"/>
-      <c r="K89" s="28" t="n"/>
-      <c r="L89" s="28" t="n"/>
-      <c r="M89" s="28" t="n"/>
-      <c r="N89" s="28" t="n"/>
+      <c r="E89" s="28">
+        <f>IF(E84&gt;0,E77/E84,0)</f>
+        <v/>
+      </c>
+      <c r="F89" s="28">
+        <f>IF(F84&gt;0,F77/F84,0)</f>
+        <v/>
+      </c>
+      <c r="G89" s="28">
+        <f>IF(G84&gt;0,G77/G84,0)</f>
+        <v/>
+      </c>
+      <c r="H89" s="28">
+        <f>IF(H84&gt;0,H77/H84,0)</f>
+        <v/>
+      </c>
+      <c r="I89" s="28">
+        <f>IF(I84&gt;0,I77/I84,0)</f>
+        <v/>
+      </c>
+      <c r="J89" s="28">
+        <f>IF(J84&gt;0,J77/J84,0)</f>
+        <v/>
+      </c>
+      <c r="K89" s="28">
+        <f>IF(K84&gt;0,K77/K84,0)</f>
+        <v/>
+      </c>
+      <c r="L89" s="28">
+        <f>IF(L84&gt;0,L77/L84,0)</f>
+        <v/>
+      </c>
+      <c r="M89" s="28">
+        <f>IF(M84&gt;0,M77/M84,0)</f>
+        <v/>
+      </c>
+      <c r="N89" s="28">
+        <f>IF(N84&gt;0,N77/N84,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -5742,7 +6132,7 @@
       </c>
       <c r="C104" s="6" t="n"/>
       <c r="D104" s="16">
-        <f>$D$17</f>
+        <f>$D$27</f>
         <v/>
       </c>
     </row>
@@ -5759,7 +6149,7 @@
       </c>
       <c r="C105" s="6" t="n"/>
       <c r="D105" s="16">
-        <f>$D$17*$D$18</f>
+        <f>$D$27*$D$28</f>
         <v/>
       </c>
     </row>
@@ -5776,7 +6166,7 @@
       </c>
       <c r="C106" s="6" t="n"/>
       <c r="D106" s="16">
-        <f>$D$27</f>
+        <f>E94</f>
         <v/>
       </c>
     </row>
@@ -5793,7 +6183,7 @@
       </c>
       <c r="C107" s="6" t="n"/>
       <c r="D107" s="7">
-        <f>$D$27*$D$28</f>
+        <f>D104+D105+D106</f>
         <v/>
       </c>
     </row>
@@ -5832,7 +6222,7 @@
       </c>
       <c r="C110" s="6" t="n"/>
       <c r="D110" s="16">
-        <f>$D$50</f>
+        <f>$D$27*$D$47</f>
         <v/>
       </c>
     </row>
@@ -5853,7 +6243,7 @@
         </is>
       </c>
       <c r="D111" s="16">
-        <f>D97-D100</f>
+        <f>D107-D110</f>
         <v/>
       </c>
     </row>
@@ -5870,7 +6260,7 @@
       </c>
       <c r="C112" s="6" t="n"/>
       <c r="D112" s="7">
-        <f>$D$27*$D$47</f>
+        <f>D110+D111</f>
         <v/>
       </c>
     </row>
@@ -5883,7 +6273,7 @@
       <c r="B113" s="6" t="n"/>
       <c r="C113" s="6" t="n"/>
       <c r="D113" s="10">
-        <f>D109-D112</f>
+        <f>IF(ABS(D107-D112)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
@@ -5933,7 +6323,7 @@
         </is>
       </c>
       <c r="D116" s="4">
-        <f>IF(ABS(D109-D114)&lt;0.01,"PASS","FAIL")</f>
+        <f>K72*$D$29</f>
         <v/>
       </c>
       <c r="E116" s="4" t="n"/>
@@ -5966,6 +6356,10 @@
           <t>Ending Bal at Exit</t>
         </is>
       </c>
+      <c r="D117">
+        <f>K88</f>
+        <v/>
+      </c>
       <c r="K117" s="16">
         <f>K78</f>
         <v/>
@@ -5987,6 +6381,10 @@
           <t>DSRA Ending at Exit</t>
         </is>
       </c>
+      <c r="D118">
+        <f>K97</f>
+        <v/>
+      </c>
       <c r="K118" s="16">
         <f>K86</f>
         <v/>
@@ -6009,7 +6407,7 @@
         </is>
       </c>
       <c r="D119">
-        <f>K72</f>
+        <f>D116-D117+D118</f>
         <v/>
       </c>
       <c r="K119" s="7">
@@ -6063,48 +6461,45 @@
       </c>
       <c r="C122" s="6" t="n"/>
       <c r="D122" s="16">
-        <f>K97</f>
+        <f>-D111</f>
         <v/>
       </c>
       <c r="E122" s="16">
-        <f>E90</f>
+        <f>E100</f>
         <v/>
       </c>
       <c r="F122" s="16">
-        <f>F90</f>
+        <f>F100</f>
         <v/>
       </c>
       <c r="G122" s="16">
-        <f>G90</f>
+        <f>G100</f>
         <v/>
       </c>
       <c r="H122" s="16">
-        <f>H90</f>
+        <f>H100</f>
         <v/>
       </c>
       <c r="I122" s="16">
-        <f>I90</f>
+        <f>I100</f>
         <v/>
       </c>
       <c r="J122" s="16">
-        <f>J90</f>
+        <f>J100</f>
         <v/>
       </c>
       <c r="K122" s="16">
-        <f>K90+K109</f>
-        <v/>
-      </c>
-      <c r="L122" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M122" s="16">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N122" s="16">
-        <f>0</f>
-        <v/>
+        <f>K100+D119</f>
+        <v/>
+      </c>
+      <c r="L122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -6124,7 +6519,7 @@
         </is>
       </c>
       <c r="D123" s="29">
-        <f>D120-D121+D122</f>
+        <f>IRR(D122:N122)</f>
         <v/>
       </c>
       <c r="E123" s="16" t="n"/>
@@ -6155,7 +6550,7 @@
         </is>
       </c>
       <c r="D124" s="28">
-        <f>SUMIF(D112:K112,"&gt;0")/ABS(D112)</f>
+        <f>(SUM(E122:K122))/-D122</f>
         <v/>
       </c>
     </row>
@@ -6227,7 +6622,10 @@
         </is>
       </c>
       <c r="C127" s="6" t="n"/>
-      <c r="D127" s="29" t="n"/>
+      <c r="D127" s="29">
+        <f>IRR(D126:N126)</f>
+        <v/>
+      </c>
       <c r="E127" s="16">
         <f>E68</f>
         <v/>
@@ -6285,7 +6683,10 @@
           <t>IRR of Equity CFs</t>
         </is>
       </c>
-      <c r="D128" s="28" t="n"/>
+      <c r="D128" s="28">
+        <f>(SUM(E126:K126))/-D126</f>
+        <v/>
+      </c>
       <c r="E128" s="16" t="n"/>
       <c r="F128" s="16" t="n"/>
       <c r="G128" s="16" t="n"/>
@@ -6380,7 +6781,6 @@
     <row r="157"/>
     <row r="158"/>
     <row r="159"/>
-    <row r="160"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,6 +105,10 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -162,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -238,6 +242,13 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3082,7 +3093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3164,9 +3175,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>═══ AUDIT STRIP ═══</t>
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE: Rebuild formulas in highlighted cells ═══</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3186,7 +3197,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Entry EV</t>
+          <t>═══ AUDIT STRIP ═══</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -3512,7 +3523,6 @@
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -4471,46 +4481,16 @@
           <t>Volume(Bcf) × Fee × 1000</t>
         </is>
       </c>
-      <c r="E69" s="16">
-        <f>E66*E67</f>
-        <v/>
-      </c>
-      <c r="F69" s="16">
-        <f>F66*F67</f>
-        <v/>
-      </c>
-      <c r="G69" s="16">
-        <f>G66*G67</f>
-        <v/>
-      </c>
-      <c r="H69" s="16">
-        <f>H66*H67</f>
-        <v/>
-      </c>
-      <c r="I69" s="16">
-        <f>I66*I67</f>
-        <v/>
-      </c>
-      <c r="J69" s="16">
-        <f>J66*J67</f>
-        <v/>
-      </c>
-      <c r="K69" s="16">
-        <f>K66*K67</f>
-        <v/>
-      </c>
-      <c r="L69" s="16">
-        <f>L66*L67</f>
-        <v/>
-      </c>
-      <c r="M69" s="16">
-        <f>M66*M67</f>
-        <v/>
-      </c>
-      <c r="N69" s="16">
-        <f>N66*N67</f>
-        <v/>
-      </c>
+      <c r="E69" s="58" t="n"/>
+      <c r="F69" s="58" t="n"/>
+      <c r="G69" s="58" t="n"/>
+      <c r="H69" s="58" t="n"/>
+      <c r="I69" s="58" t="n"/>
+      <c r="J69" s="58" t="n"/>
+      <c r="K69" s="58" t="n"/>
+      <c r="L69" s="58" t="n"/>
+      <c r="M69" s="58" t="n"/>
+      <c r="N69" s="58" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -4528,46 +4508,16 @@
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E70" s="16">
-        <f>$D$42*(1+$D$43)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F70" s="16">
-        <f>$D$42*(1+$D$43)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G70" s="16">
-        <f>$D$42*(1+$D$43)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H70" s="16">
-        <f>$D$42*(1+$D$43)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I70" s="16">
-        <f>$D$42*(1+$D$43)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J70" s="16">
-        <f>$D$42*(1+$D$43)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16">
-        <f>$D$42*(1+$D$43)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L70" s="16">
-        <f>$D$42*(1+$D$43)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M70" s="16">
-        <f>$D$42*(1+$D$43)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N70" s="16">
-        <f>$D$42*(1+$D$43)^(10-1)</f>
-        <v/>
-      </c>
+      <c r="E70" s="58" t="n"/>
+      <c r="F70" s="58" t="n"/>
+      <c r="G70" s="58" t="n"/>
+      <c r="H70" s="58" t="n"/>
+      <c r="I70" s="58" t="n"/>
+      <c r="J70" s="58" t="n"/>
+      <c r="K70" s="58" t="n"/>
+      <c r="L70" s="58" t="n"/>
+      <c r="M70" s="58" t="n"/>
+      <c r="N70" s="58" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -4600,46 +4550,16 @@
           <t>Revenue minus OpEx</t>
         </is>
       </c>
-      <c r="E72" s="7">
-        <f>E69-E70</f>
-        <v/>
-      </c>
-      <c r="F72" s="7">
-        <f>F69-F70</f>
-        <v/>
-      </c>
-      <c r="G72" s="7">
-        <f>G69-G70</f>
-        <v/>
-      </c>
-      <c r="H72" s="7">
-        <f>H69-H70</f>
-        <v/>
-      </c>
-      <c r="I72" s="7">
-        <f>I69-I70</f>
-        <v/>
-      </c>
-      <c r="J72" s="7">
-        <f>J69-J70</f>
-        <v/>
-      </c>
-      <c r="K72" s="7">
-        <f>K69-K70</f>
-        <v/>
-      </c>
-      <c r="L72" s="7">
-        <f>L69-L70</f>
-        <v/>
-      </c>
-      <c r="M72" s="7">
-        <f>M69-M70</f>
-        <v/>
-      </c>
-      <c r="N72" s="7">
-        <f>N69-N70</f>
-        <v/>
-      </c>
+      <c r="E72" s="59" t="n"/>
+      <c r="F72" s="59" t="n"/>
+      <c r="G72" s="59" t="n"/>
+      <c r="H72" s="59" t="n"/>
+      <c r="I72" s="59" t="n"/>
+      <c r="J72" s="59" t="n"/>
+      <c r="K72" s="59" t="n"/>
+      <c r="L72" s="59" t="n"/>
+      <c r="M72" s="59" t="n"/>
+      <c r="N72" s="59" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
@@ -4693,46 +4613,16 @@
         </is>
       </c>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="16">
-        <f>E72-$D$61</f>
-        <v/>
-      </c>
-      <c r="F75" s="16">
-        <f>F72-$D$61</f>
-        <v/>
-      </c>
-      <c r="G75" s="16">
-        <f>G72-$D$61</f>
-        <v/>
-      </c>
-      <c r="H75" s="16">
-        <f>H72-$D$61</f>
-        <v/>
-      </c>
-      <c r="I75" s="16">
-        <f>I72-$D$61</f>
-        <v/>
-      </c>
-      <c r="J75" s="16">
-        <f>J72-$D$61</f>
-        <v/>
-      </c>
-      <c r="K75" s="16">
-        <f>K72-$D$61</f>
-        <v/>
-      </c>
-      <c r="L75" s="16">
-        <f>L72-$D$61</f>
-        <v/>
-      </c>
-      <c r="M75" s="16">
-        <f>M72-$D$61</f>
-        <v/>
-      </c>
-      <c r="N75" s="16">
-        <f>N72-$D$61</f>
-        <v/>
-      </c>
+      <c r="E75" s="58" t="n"/>
+      <c r="F75" s="58" t="n"/>
+      <c r="G75" s="58" t="n"/>
+      <c r="H75" s="58" t="n"/>
+      <c r="I75" s="58" t="n"/>
+      <c r="J75" s="58" t="n"/>
+      <c r="K75" s="58" t="n"/>
+      <c r="L75" s="58" t="n"/>
+      <c r="M75" s="58" t="n"/>
+      <c r="N75" s="58" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -4750,46 +4640,16 @@
           <t>MAX(0, EBIT) × Tax Rate</t>
         </is>
       </c>
-      <c r="E76" s="16">
-        <f>MAX(0,E75)*$D$55</f>
-        <v/>
-      </c>
-      <c r="F76" s="16">
-        <f>MAX(0,F75)*$D$55</f>
-        <v/>
-      </c>
-      <c r="G76" s="16">
-        <f>MAX(0,G75)*$D$55</f>
-        <v/>
-      </c>
-      <c r="H76" s="16">
-        <f>MAX(0,H75)*$D$55</f>
-        <v/>
-      </c>
-      <c r="I76" s="16">
-        <f>MAX(0,I75)*$D$55</f>
-        <v/>
-      </c>
-      <c r="J76" s="16">
-        <f>MAX(0,J75)*$D$55</f>
-        <v/>
-      </c>
-      <c r="K76" s="16">
-        <f>MAX(0,K75)*$D$55</f>
-        <v/>
-      </c>
-      <c r="L76" s="16">
-        <f>MAX(0,L75)*$D$55</f>
-        <v/>
-      </c>
-      <c r="M76" s="16">
-        <f>MAX(0,M75)*$D$55</f>
-        <v/>
-      </c>
-      <c r="N76" s="16">
-        <f>MAX(0,N75)*$D$55</f>
-        <v/>
-      </c>
+      <c r="E76" s="58" t="n"/>
+      <c r="F76" s="58" t="n"/>
+      <c r="G76" s="58" t="n"/>
+      <c r="H76" s="58" t="n"/>
+      <c r="I76" s="58" t="n"/>
+      <c r="J76" s="58" t="n"/>
+      <c r="K76" s="58" t="n"/>
+      <c r="L76" s="58" t="n"/>
+      <c r="M76" s="58" t="n"/>
+      <c r="N76" s="58" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -4807,46 +4667,16 @@
           <t>Y1-Y5 only</t>
         </is>
       </c>
-      <c r="E77" s="7">
-        <f>IF(1&lt;=5,$D$44,0)</f>
-        <v/>
-      </c>
-      <c r="F77" s="7">
-        <f>IF(2&lt;=5,$D$44,0)</f>
-        <v/>
-      </c>
-      <c r="G77" s="7">
-        <f>IF(3&lt;=5,$D$44,0)</f>
-        <v/>
-      </c>
-      <c r="H77" s="7">
-        <f>IF(4&lt;=5,$D$44,0)</f>
-        <v/>
-      </c>
-      <c r="I77" s="7">
-        <f>IF(5&lt;=5,$D$44,0)</f>
-        <v/>
-      </c>
-      <c r="J77" s="7">
-        <f>IF(6&lt;=5,$D$44,0)</f>
-        <v/>
-      </c>
-      <c r="K77" s="7">
-        <f>IF(7&lt;=5,$D$44,0)</f>
-        <v/>
-      </c>
-      <c r="L77" s="7">
-        <f>IF(8&lt;=5,$D$44,0)</f>
-        <v/>
-      </c>
-      <c r="M77" s="7">
-        <f>IF(9&lt;=5,$D$44,0)</f>
-        <v/>
-      </c>
-      <c r="N77" s="7">
-        <f>IF(10&lt;=5,$D$44,0)</f>
-        <v/>
-      </c>
+      <c r="E77" s="59" t="n"/>
+      <c r="F77" s="59" t="n"/>
+      <c r="G77" s="59" t="n"/>
+      <c r="H77" s="59" t="n"/>
+      <c r="I77" s="59" t="n"/>
+      <c r="J77" s="59" t="n"/>
+      <c r="K77" s="59" t="n"/>
+      <c r="L77" s="59" t="n"/>
+      <c r="M77" s="59" t="n"/>
+      <c r="N77" s="59" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -4864,46 +4694,16 @@
           <t>EBITDA - Taxes - Capex</t>
         </is>
       </c>
-      <c r="E78" s="7">
-        <f>E72-E76-E77</f>
-        <v/>
-      </c>
-      <c r="F78" s="7">
-        <f>F72-F76-F77</f>
-        <v/>
-      </c>
-      <c r="G78" s="7">
-        <f>G72-G76-G77</f>
-        <v/>
-      </c>
-      <c r="H78" s="7">
-        <f>H72-H76-H77</f>
-        <v/>
-      </c>
-      <c r="I78" s="7">
-        <f>I72-I76-I77</f>
-        <v/>
-      </c>
-      <c r="J78" s="7">
-        <f>J72-J76-J77</f>
-        <v/>
-      </c>
-      <c r="K78" s="7">
-        <f>K72-K76-K77</f>
-        <v/>
-      </c>
-      <c r="L78" s="7">
-        <f>L72-L76-L77</f>
-        <v/>
-      </c>
-      <c r="M78" s="7">
-        <f>M72-M76-M77</f>
-        <v/>
-      </c>
-      <c r="N78" s="7">
-        <f>N72-N76-N77</f>
-        <v/>
-      </c>
+      <c r="E78" s="59" t="n"/>
+      <c r="F78" s="59" t="n"/>
+      <c r="G78" s="59" t="n"/>
+      <c r="H78" s="59" t="n"/>
+      <c r="I78" s="59" t="n"/>
+      <c r="J78" s="59" t="n"/>
+      <c r="K78" s="59" t="n"/>
+      <c r="L78" s="59" t="n"/>
+      <c r="M78" s="59" t="n"/>
+      <c r="N78" s="59" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -4955,46 +4755,16 @@
       <c r="D81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E81" s="16">
-        <f>$D$60</f>
-        <v/>
-      </c>
-      <c r="F81" s="16">
-        <f>E88</f>
-        <v/>
-      </c>
-      <c r="G81" s="16">
-        <f>F88</f>
-        <v/>
-      </c>
-      <c r="H81" s="16">
-        <f>G88</f>
-        <v/>
-      </c>
-      <c r="I81" s="16">
-        <f>H88</f>
-        <v/>
-      </c>
-      <c r="J81" s="16">
-        <f>I88</f>
-        <v/>
-      </c>
-      <c r="K81" s="16">
-        <f>J88</f>
-        <v/>
-      </c>
-      <c r="L81" s="16">
-        <f>K88</f>
-        <v/>
-      </c>
-      <c r="M81" s="16">
-        <f>L88</f>
-        <v/>
-      </c>
-      <c r="N81" s="16">
-        <f>M88</f>
-        <v/>
-      </c>
+      <c r="E81" s="58" t="n"/>
+      <c r="F81" s="58" t="n"/>
+      <c r="G81" s="58" t="n"/>
+      <c r="H81" s="58" t="n"/>
+      <c r="I81" s="58" t="n"/>
+      <c r="J81" s="58" t="n"/>
+      <c r="K81" s="58" t="n"/>
+      <c r="L81" s="58" t="n"/>
+      <c r="M81" s="58" t="n"/>
+      <c r="N81" s="58" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -5012,46 +4782,16 @@
           <t>Beg Bal × Int Rate</t>
         </is>
       </c>
-      <c r="E82" s="16">
-        <f>E81*$D$48</f>
-        <v/>
-      </c>
-      <c r="F82" s="16">
-        <f>F81*$D$48</f>
-        <v/>
-      </c>
-      <c r="G82" s="16">
-        <f>G81*$D$48</f>
-        <v/>
-      </c>
-      <c r="H82" s="16">
-        <f>H81*$D$48</f>
-        <v/>
-      </c>
-      <c r="I82" s="16">
-        <f>I81*$D$48</f>
-        <v/>
-      </c>
-      <c r="J82" s="16">
-        <f>J81*$D$48</f>
-        <v/>
-      </c>
-      <c r="K82" s="16">
-        <f>K81*$D$48</f>
-        <v/>
-      </c>
-      <c r="L82" s="16">
-        <f>L81*$D$48</f>
-        <v/>
-      </c>
-      <c r="M82" s="16">
-        <f>M81*$D$48</f>
-        <v/>
-      </c>
-      <c r="N82" s="16">
-        <f>N81*$D$48</f>
-        <v/>
-      </c>
+      <c r="E82" s="58" t="n"/>
+      <c r="F82" s="58" t="n"/>
+      <c r="G82" s="58" t="n"/>
+      <c r="H82" s="58" t="n"/>
+      <c r="I82" s="58" t="n"/>
+      <c r="J82" s="58" t="n"/>
+      <c r="K82" s="58" t="n"/>
+      <c r="L82" s="58" t="n"/>
+      <c r="M82" s="58" t="n"/>
+      <c r="N82" s="58" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -5069,46 +4809,16 @@
           <t>MIN(Sched, Beg Bal)</t>
         </is>
       </c>
-      <c r="E83" s="16">
-        <f>MIN($D$62,E81)</f>
-        <v/>
-      </c>
-      <c r="F83" s="16">
-        <f>MIN($D$62,F81)</f>
-        <v/>
-      </c>
-      <c r="G83" s="16">
-        <f>MIN($D$62,G81)</f>
-        <v/>
-      </c>
-      <c r="H83" s="16">
-        <f>MIN($D$62,H81)</f>
-        <v/>
-      </c>
-      <c r="I83" s="16">
-        <f>MIN($D$62,I81)</f>
-        <v/>
-      </c>
-      <c r="J83" s="16">
-        <f>MIN($D$62,J81)</f>
-        <v/>
-      </c>
-      <c r="K83" s="16">
-        <f>MIN($D$62,K81)</f>
-        <v/>
-      </c>
-      <c r="L83" s="16">
-        <f>MIN($D$62,L81)</f>
-        <v/>
-      </c>
-      <c r="M83" s="16">
-        <f>MIN($D$62,M81)</f>
-        <v/>
-      </c>
-      <c r="N83" s="16">
-        <f>MIN($D$62,N81)</f>
-        <v/>
-      </c>
+      <c r="E83" s="58" t="n"/>
+      <c r="F83" s="58" t="n"/>
+      <c r="G83" s="58" t="n"/>
+      <c r="H83" s="58" t="n"/>
+      <c r="I83" s="58" t="n"/>
+      <c r="J83" s="58" t="n"/>
+      <c r="K83" s="58" t="n"/>
+      <c r="L83" s="58" t="n"/>
+      <c r="M83" s="58" t="n"/>
+      <c r="N83" s="58" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -5126,46 +4836,16 @@
           <t>Interest + Sched Prin</t>
         </is>
       </c>
-      <c r="E84" s="16">
-        <f>E82+E83</f>
-        <v/>
-      </c>
-      <c r="F84" s="16">
-        <f>F82+F83</f>
-        <v/>
-      </c>
-      <c r="G84" s="16">
-        <f>G82+G83</f>
-        <v/>
-      </c>
-      <c r="H84" s="16">
-        <f>H82+H83</f>
-        <v/>
-      </c>
-      <c r="I84" s="16">
-        <f>I82+I83</f>
-        <v/>
-      </c>
-      <c r="J84" s="16">
-        <f>J82+J83</f>
-        <v/>
-      </c>
-      <c r="K84" s="16">
-        <f>K82+K83</f>
-        <v/>
-      </c>
-      <c r="L84" s="16">
-        <f>L82+L83</f>
-        <v/>
-      </c>
-      <c r="M84" s="16">
-        <f>M82+M83</f>
-        <v/>
-      </c>
-      <c r="N84" s="16">
-        <f>N82+N83</f>
-        <v/>
-      </c>
+      <c r="E84" s="58" t="n"/>
+      <c r="F84" s="58" t="n"/>
+      <c r="G84" s="58" t="n"/>
+      <c r="H84" s="58" t="n"/>
+      <c r="I84" s="58" t="n"/>
+      <c r="J84" s="58" t="n"/>
+      <c r="K84" s="58" t="n"/>
+      <c r="L84" s="58" t="n"/>
+      <c r="M84" s="58" t="n"/>
+      <c r="N84" s="58" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -5240,46 +4920,16 @@
           <t>MIN(Excess×75%, Beg-Sched)</t>
         </is>
       </c>
-      <c r="E86" s="19">
-        <f>MIN(E85*$D$51,MAX(0,E81-E83))</f>
-        <v/>
-      </c>
-      <c r="F86" s="19">
-        <f>MIN(F85*$D$51,MAX(0,F81-F83))</f>
-        <v/>
-      </c>
-      <c r="G86" s="19">
-        <f>MIN(G85*$D$51,MAX(0,G81-G83))</f>
-        <v/>
-      </c>
-      <c r="H86" s="19">
-        <f>MIN(H85*$D$51,MAX(0,H81-H83))</f>
-        <v/>
-      </c>
-      <c r="I86" s="19">
-        <f>MIN(I85*$D$51,MAX(0,I81-I83))</f>
-        <v/>
-      </c>
-      <c r="J86" s="19">
-        <f>MIN(J85*$D$51,MAX(0,J81-J83))</f>
-        <v/>
-      </c>
-      <c r="K86" s="19">
-        <f>MIN(K85*$D$51,MAX(0,K81-K83))</f>
-        <v/>
-      </c>
-      <c r="L86" s="19">
-        <f>MIN(L85*$D$51,MAX(0,L81-L83))</f>
-        <v/>
-      </c>
-      <c r="M86" s="19">
-        <f>MIN(M85*$D$51,MAX(0,M81-M83))</f>
-        <v/>
-      </c>
-      <c r="N86" s="19">
-        <f>MIN(N85*$D$51,MAX(0,N81-N83))</f>
-        <v/>
-      </c>
+      <c r="E86" s="58" t="n"/>
+      <c r="F86" s="58" t="n"/>
+      <c r="G86" s="58" t="n"/>
+      <c r="H86" s="58" t="n"/>
+      <c r="I86" s="58" t="n"/>
+      <c r="J86" s="58" t="n"/>
+      <c r="K86" s="58" t="n"/>
+      <c r="L86" s="58" t="n"/>
+      <c r="M86" s="58" t="n"/>
+      <c r="N86" s="58" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -5297,46 +4947,16 @@
           <t>Scheduled + Sweep</t>
         </is>
       </c>
-      <c r="E87" s="16">
-        <f>E83+E86</f>
-        <v/>
-      </c>
-      <c r="F87" s="16">
-        <f>F83+F86</f>
-        <v/>
-      </c>
-      <c r="G87" s="16">
-        <f>G83+G86</f>
-        <v/>
-      </c>
-      <c r="H87" s="16">
-        <f>H83+H86</f>
-        <v/>
-      </c>
-      <c r="I87" s="16">
-        <f>I83+I86</f>
-        <v/>
-      </c>
-      <c r="J87" s="16">
-        <f>J83+J86</f>
-        <v/>
-      </c>
-      <c r="K87" s="16">
-        <f>K83+K86</f>
-        <v/>
-      </c>
-      <c r="L87" s="16">
-        <f>L83+L86</f>
-        <v/>
-      </c>
-      <c r="M87" s="16">
-        <f>M83+M86</f>
-        <v/>
-      </c>
-      <c r="N87" s="16">
-        <f>N83+N86</f>
-        <v/>
-      </c>
+      <c r="E87" s="58" t="n"/>
+      <c r="F87" s="58" t="n"/>
+      <c r="G87" s="58" t="n"/>
+      <c r="H87" s="58" t="n"/>
+      <c r="I87" s="58" t="n"/>
+      <c r="J87" s="58" t="n"/>
+      <c r="K87" s="58" t="n"/>
+      <c r="L87" s="58" t="n"/>
+      <c r="M87" s="58" t="n"/>
+      <c r="N87" s="58" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -5358,46 +4978,16 @@
         <f>$D$60</f>
         <v/>
       </c>
-      <c r="E88" s="16">
-        <f>MAX(0,E81-E87)</f>
-        <v/>
-      </c>
-      <c r="F88" s="16">
-        <f>MAX(0,F81-F87)</f>
-        <v/>
-      </c>
-      <c r="G88" s="16">
-        <f>MAX(0,G81-G87)</f>
-        <v/>
-      </c>
-      <c r="H88" s="16">
-        <f>MAX(0,H81-H87)</f>
-        <v/>
-      </c>
-      <c r="I88" s="16">
-        <f>MAX(0,I81-I87)</f>
-        <v/>
-      </c>
-      <c r="J88" s="16">
-        <f>MAX(0,J81-J87)</f>
-        <v/>
-      </c>
-      <c r="K88" s="16">
-        <f>MAX(0,K81-K87)</f>
-        <v/>
-      </c>
-      <c r="L88" s="16">
-        <f>MAX(0,L81-L87)</f>
-        <v/>
-      </c>
-      <c r="M88" s="16">
-        <f>MAX(0,M81-M87)</f>
-        <v/>
-      </c>
-      <c r="N88" s="16">
-        <f>MAX(0,N81-N87)</f>
-        <v/>
-      </c>
+      <c r="E88" s="58" t="n"/>
+      <c r="F88" s="58" t="n"/>
+      <c r="G88" s="58" t="n"/>
+      <c r="H88" s="58" t="n"/>
+      <c r="I88" s="58" t="n"/>
+      <c r="J88" s="58" t="n"/>
+      <c r="K88" s="58" t="n"/>
+      <c r="L88" s="58" t="n"/>
+      <c r="M88" s="58" t="n"/>
+      <c r="N88" s="58" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -5415,46 +5005,16 @@
           <t>CFADS / Debt Service</t>
         </is>
       </c>
-      <c r="E89" s="28">
-        <f>IF(E84&gt;0,E77/E84,0)</f>
-        <v/>
-      </c>
-      <c r="F89" s="28">
-        <f>IF(F84&gt;0,F77/F84,0)</f>
-        <v/>
-      </c>
-      <c r="G89" s="28">
-        <f>IF(G84&gt;0,G77/G84,0)</f>
-        <v/>
-      </c>
-      <c r="H89" s="28">
-        <f>IF(H84&gt;0,H77/H84,0)</f>
-        <v/>
-      </c>
-      <c r="I89" s="28">
-        <f>IF(I84&gt;0,I77/I84,0)</f>
-        <v/>
-      </c>
-      <c r="J89" s="28">
-        <f>IF(J84&gt;0,J77/J84,0)</f>
-        <v/>
-      </c>
-      <c r="K89" s="28">
-        <f>IF(K84&gt;0,K77/K84,0)</f>
-        <v/>
-      </c>
-      <c r="L89" s="28">
-        <f>IF(L84&gt;0,L77/L84,0)</f>
-        <v/>
-      </c>
-      <c r="M89" s="28">
-        <f>IF(M84&gt;0,M77/M84,0)</f>
-        <v/>
-      </c>
-      <c r="N89" s="28">
-        <f>IF(N84&gt;0,N77/N84,0)</f>
-        <v/>
-      </c>
+      <c r="E89" s="60" t="n"/>
+      <c r="F89" s="60" t="n"/>
+      <c r="G89" s="60" t="n"/>
+      <c r="H89" s="60" t="n"/>
+      <c r="I89" s="60" t="n"/>
+      <c r="J89" s="60" t="n"/>
+      <c r="K89" s="60" t="n"/>
+      <c r="L89" s="60" t="n"/>
+      <c r="M89" s="60" t="n"/>
+      <c r="N89" s="60" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -5568,46 +5128,16 @@
         <f>E80*$D$40/12</f>
         <v/>
       </c>
-      <c r="E93" s="16">
-        <f>F80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="F93" s="16">
-        <f>G80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="G93" s="16">
-        <f>H80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="H93" s="16">
-        <f>I80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="I93" s="16">
-        <f>J80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="J93" s="16">
-        <f>K80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="K93" s="16">
-        <f>L80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="L93" s="16">
-        <f>M80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="M93" s="16">
-        <f>N80*$D$40/12</f>
-        <v/>
-      </c>
-      <c r="N93" s="16">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="E93" s="58" t="n"/>
+      <c r="F93" s="58" t="n"/>
+      <c r="G93" s="58" t="n"/>
+      <c r="H93" s="58" t="n"/>
+      <c r="I93" s="58" t="n"/>
+      <c r="J93" s="58" t="n"/>
+      <c r="K93" s="58" t="n"/>
+      <c r="L93" s="58" t="n"/>
+      <c r="M93" s="58" t="n"/>
+      <c r="N93" s="58" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -5625,45 +5155,16 @@
         <f>0</f>
         <v/>
       </c>
-      <c r="E94" s="16">
-        <f>F90*$D$50/12</f>
-        <v/>
-      </c>
-      <c r="F94" s="16">
-        <f>G90*$D$50/12</f>
-        <v/>
-      </c>
-      <c r="G94" s="16">
-        <f>H90*$D$50/12</f>
-        <v/>
-      </c>
-      <c r="H94" s="16">
-        <f>I90*$D$50/12</f>
-        <v/>
-      </c>
-      <c r="I94" s="16">
-        <f>J90*$D$50/12</f>
-        <v/>
-      </c>
-      <c r="J94" s="16">
-        <f>K90*$D$50/12</f>
-        <v/>
-      </c>
-      <c r="K94" s="16">
-        <f>L90*$D$50/12</f>
-        <v/>
-      </c>
-      <c r="L94" s="16">
-        <f>M90*$D$50/12</f>
-        <v/>
-      </c>
-      <c r="M94" s="16">
-        <f>N90*$D$50/12</f>
-        <v/>
-      </c>
-      <c r="N94" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E94" s="58" t="n"/>
+      <c r="F94" s="58" t="n"/>
+      <c r="G94" s="58" t="n"/>
+      <c r="H94" s="58" t="n"/>
+      <c r="I94" s="58" t="n"/>
+      <c r="J94" s="58" t="n"/>
+      <c r="K94" s="58" t="n"/>
+      <c r="L94" s="58" t="n"/>
+      <c r="M94" s="58" t="n"/>
+      <c r="N94" s="58" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -5684,46 +5185,16 @@
       <c r="D95" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="16">
-        <f>D108</f>
-        <v/>
-      </c>
-      <c r="F95" s="16">
-        <f>E97</f>
-        <v/>
-      </c>
-      <c r="G95" s="16">
-        <f>F97</f>
-        <v/>
-      </c>
-      <c r="H95" s="16">
-        <f>G97</f>
-        <v/>
-      </c>
-      <c r="I95" s="16">
-        <f>H97</f>
-        <v/>
-      </c>
-      <c r="J95" s="16">
-        <f>I97</f>
-        <v/>
-      </c>
-      <c r="K95" s="16">
-        <f>J97</f>
-        <v/>
-      </c>
-      <c r="L95" s="16">
-        <f>K97</f>
-        <v/>
-      </c>
-      <c r="M95" s="16">
-        <f>L97</f>
-        <v/>
-      </c>
-      <c r="N95" s="16">
-        <f>M97</f>
-        <v/>
-      </c>
+      <c r="E95" s="58" t="n"/>
+      <c r="F95" s="58" t="n"/>
+      <c r="G95" s="58" t="n"/>
+      <c r="H95" s="58" t="n"/>
+      <c r="I95" s="58" t="n"/>
+      <c r="J95" s="58" t="n"/>
+      <c r="K95" s="58" t="n"/>
+      <c r="L95" s="58" t="n"/>
+      <c r="M95" s="58" t="n"/>
+      <c r="N95" s="58" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -5745,46 +5216,16 @@
         <f>D84+D85</f>
         <v/>
       </c>
-      <c r="E96" s="16">
-        <f>E94-E95</f>
-        <v/>
-      </c>
-      <c r="F96" s="16">
-        <f>F94-F95</f>
-        <v/>
-      </c>
-      <c r="G96" s="16">
-        <f>G94-G95</f>
-        <v/>
-      </c>
-      <c r="H96" s="16">
-        <f>H94-H95</f>
-        <v/>
-      </c>
-      <c r="I96" s="16">
-        <f>I94-I95</f>
-        <v/>
-      </c>
-      <c r="J96" s="16">
-        <f>J94-J95</f>
-        <v/>
-      </c>
-      <c r="K96" s="16">
-        <f>K94-K95</f>
-        <v/>
-      </c>
-      <c r="L96" s="16">
-        <f>L94-L95</f>
-        <v/>
-      </c>
-      <c r="M96" s="16">
-        <f>M94-M95</f>
-        <v/>
-      </c>
-      <c r="N96" s="16">
-        <f>N94-N95</f>
-        <v/>
-      </c>
+      <c r="E96" s="58" t="n"/>
+      <c r="F96" s="58" t="n"/>
+      <c r="G96" s="58" t="n"/>
+      <c r="H96" s="58" t="n"/>
+      <c r="I96" s="58" t="n"/>
+      <c r="J96" s="58" t="n"/>
+      <c r="K96" s="58" t="n"/>
+      <c r="L96" s="58" t="n"/>
+      <c r="M96" s="58" t="n"/>
+      <c r="N96" s="58" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -5963,46 +5404,16 @@
           <t>If PASS, MAX(0, Cash Avail)</t>
         </is>
       </c>
-      <c r="E100" s="7">
-        <f>E77-E82-E87-E96</f>
-        <v/>
-      </c>
-      <c r="F100" s="7">
-        <f>F77-F82-F87-F96</f>
-        <v/>
-      </c>
-      <c r="G100" s="7">
-        <f>G77-G82-G87-G96</f>
-        <v/>
-      </c>
-      <c r="H100" s="7">
-        <f>H77-H82-H87-H96</f>
-        <v/>
-      </c>
-      <c r="I100" s="7">
-        <f>I77-I82-I87-I96</f>
-        <v/>
-      </c>
-      <c r="J100" s="7">
-        <f>J77-J82-J87-J96</f>
-        <v/>
-      </c>
-      <c r="K100" s="7">
-        <f>K77-K82-K87-K96</f>
-        <v/>
-      </c>
-      <c r="L100" s="7">
-        <f>L77-L82-L87-L96</f>
-        <v/>
-      </c>
-      <c r="M100" s="7">
-        <f>M77-M82-M87-M96</f>
-        <v/>
-      </c>
-      <c r="N100" s="7">
-        <f>N77-N82-N87-N96</f>
-        <v/>
-      </c>
+      <c r="E100" s="59" t="n"/>
+      <c r="F100" s="59" t="n"/>
+      <c r="G100" s="59" t="n"/>
+      <c r="H100" s="59" t="n"/>
+      <c r="I100" s="59" t="n"/>
+      <c r="J100" s="59" t="n"/>
+      <c r="K100" s="59" t="n"/>
+      <c r="L100" s="59" t="n"/>
+      <c r="M100" s="59" t="n"/>
+      <c r="N100" s="59" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
@@ -6464,43 +5875,16 @@
         <f>-D111</f>
         <v/>
       </c>
-      <c r="E122" s="16">
-        <f>E100</f>
-        <v/>
-      </c>
-      <c r="F122" s="16">
-        <f>F100</f>
-        <v/>
-      </c>
-      <c r="G122" s="16">
-        <f>G100</f>
-        <v/>
-      </c>
-      <c r="H122" s="16">
-        <f>H100</f>
-        <v/>
-      </c>
-      <c r="I122" s="16">
-        <f>I100</f>
-        <v/>
-      </c>
-      <c r="J122" s="16">
-        <f>J100</f>
-        <v/>
-      </c>
-      <c r="K122" s="16">
-        <f>K100+D119</f>
-        <v/>
-      </c>
-      <c r="L122" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E122" s="58" t="n"/>
+      <c r="F122" s="58" t="n"/>
+      <c r="G122" s="58" t="n"/>
+      <c r="H122" s="58" t="n"/>
+      <c r="I122" s="58" t="n"/>
+      <c r="J122" s="58" t="n"/>
+      <c r="K122" s="58" t="n"/>
+      <c r="L122" s="58" t="n"/>
+      <c r="M122" s="58" t="n"/>
+      <c r="N122" s="58" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -6518,10 +5902,7 @@
           <t>IRR of Equity CFs</t>
         </is>
       </c>
-      <c r="D123" s="29">
-        <f>IRR(D122:N122)</f>
-        <v/>
-      </c>
+      <c r="D123" s="61" t="n"/>
       <c r="E123" s="16" t="n"/>
       <c r="F123" s="16" t="n"/>
       <c r="G123" s="16" t="n"/>
@@ -6549,10 +5930,7 @@
           <t>Sum inflows / outflow</t>
         </is>
       </c>
-      <c r="D124" s="28">
-        <f>(SUM(E122:K122))/-D122</f>
-        <v/>
-      </c>
+      <c r="D124" s="60" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n"/>
@@ -6563,13 +5941,13 @@
     <row r="126">
       <c r="A126" s="21" t="inlineStr">
         <is>
-          <t>Unlevered Returns (for reference)</t>
+          <t>Unlevered Cash Flow</t>
         </is>
       </c>
       <c r="B126" s="6" t="n"/>
       <c r="C126" s="6" t="n"/>
       <c r="D126">
-        <f>-D113</f>
+        <f>-D104</f>
         <v/>
       </c>
       <c r="E126">
@@ -6613,7 +5991,7 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Unlevered Cash Flow</t>
+          <t>Unlevered IRR</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
@@ -6670,7 +6048,7 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Unlevered IRR</t>
+          <t>Unlevered MOIC</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
@@ -6704,7 +6082,6 @@
       <c r="C129" s="6" t="n"/>
       <c r="D129" s="29" t="n"/>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="D131">
         <f>-$D$27-D107</f>
@@ -6754,33 +6131,6 @@
         <v/>
       </c>
     </row>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -3496,7 +3496,7 @@
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="10">
-        <f>IF(I78&lt;1,"PASS","FAIL")</f>
+        <f>IF(I88&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -3472,10 +3472,7 @@
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="10">
-        <f>D103</f>
-        <v/>
-      </c>
+      <c r="D21" s="10" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
@@ -3513,7 +3510,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
+        <f>IF(MINIFS(E89:I89,E89:I89,"&gt;0")&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_5_Midstream.xlsx
@@ -166,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -249,6 +249,7 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3271,10 +3272,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="n"/>
-      <c r="B6" s="47" t="n"/>
-      <c r="C6" s="47" t="n"/>
-      <c r="D6" s="47" t="n"/>
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>Minimum debt service coverage ratio</t>
+        </is>
+      </c>
+      <c r="D6" s="62">
+        <f>IF(COUNTIF(E89:I89,"&gt;0")&gt;0,MINIFS(E89:I89,E89:I89,"&gt;0"),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="48" t="inlineStr">
@@ -3510,7 +3526,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(MINIFS(E89:I89,E89:I89,"&gt;0")&gt;=1.25,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
